--- a/studyflow.xlsx
+++ b/studyflow.xlsx
@@ -1,13 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\puszt\Downloads\StudyFlow_GitHub\studyflow_github\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E6D4804-E5FF-4808-862D-04118445B29E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Munka1" sheetId="1" r:id="rId1"/>
+    <sheet name="szavak" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,8 +24,37 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>apple</t>
+  </si>
+  <si>
+    <t>alma</t>
+  </si>
+  <si>
+    <t>house</t>
+  </si>
+  <si>
+    <t>ház</t>
+  </si>
+  <si>
+    <t>learn</t>
+  </si>
+  <si>
+    <t>tanulni</t>
+  </si>
+  <si>
+    <t>beautiful</t>
+  </si>
+  <si>
+    <t>gyönyörű</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -53,7 +88,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +365,43 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/studyflow.xlsx
+++ b/studyflow.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\puszt\Downloads\StudyFlow_GitHub\studyflow_github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E6D4804-E5FF-4808-862D-04118445B29E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67EB4722-59D7-455B-A808-3393F39BC811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="szavak" sheetId="1" r:id="rId1"/>
+    <sheet name="words" sheetId="1" r:id="rId1"/>
+    <sheet name="10.26." sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,30 +26,621 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>apple</t>
-  </si>
-  <si>
-    <t>alma</t>
-  </si>
-  <si>
-    <t>house</t>
-  </si>
-  <si>
-    <t>ház</t>
-  </si>
-  <si>
-    <t>learn</t>
-  </si>
-  <si>
-    <t>tanulni</t>
-  </si>
-  <si>
-    <t>beautiful</t>
-  </si>
-  <si>
-    <t>gyönyörű</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="205">
+  <si>
+    <t>pantry</t>
+  </si>
+  <si>
+    <t>spejz</t>
+  </si>
+  <si>
+    <t>to pile up</t>
+  </si>
+  <si>
+    <t>összegyűlik, összeadódik</t>
+  </si>
+  <si>
+    <t>waterfall</t>
+  </si>
+  <si>
+    <t>vízesés</t>
+  </si>
+  <si>
+    <t>evidence</t>
+  </si>
+  <si>
+    <t>bizonyíték</t>
+  </si>
+  <si>
+    <t>trial</t>
+  </si>
+  <si>
+    <t>tárgyalás</t>
+  </si>
+  <si>
+    <t>to assume</t>
+  </si>
+  <si>
+    <t>feltételezni</t>
+  </si>
+  <si>
+    <t>guilty</t>
+  </si>
+  <si>
+    <t>bűnös</t>
+  </si>
+  <si>
+    <t>convincing</t>
+  </si>
+  <si>
+    <t>meggyőző</t>
+  </si>
+  <si>
+    <t>defence</t>
+  </si>
+  <si>
+    <t>védelmi, védő, védelem</t>
+  </si>
+  <si>
+    <t>frightened</t>
+  </si>
+  <si>
+    <t>ijedt, fél</t>
+  </si>
+  <si>
+    <t>to be accused of</t>
+  </si>
+  <si>
+    <t>megvádolva lenni vmivel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">justice </t>
+  </si>
+  <si>
+    <t>igazság</t>
+  </si>
+  <si>
+    <t>the young</t>
+  </si>
+  <si>
+    <t>a fiatalok - mindenkire vonatkoztatva, gyűjtőnév</t>
+  </si>
+  <si>
+    <t>no longer</t>
+  </si>
+  <si>
+    <t>többé nem</t>
+  </si>
+  <si>
+    <t>to discredit</t>
+  </si>
+  <si>
+    <t>elhitelteleníteni, lejáratni</t>
+  </si>
+  <si>
+    <t>to think about</t>
+  </si>
+  <si>
+    <t>gondolkodni valamin</t>
+  </si>
+  <si>
+    <t>to think of</t>
+  </si>
+  <si>
+    <t>kitalálni, kigondolni, eszébe jut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bilingual </t>
+  </si>
+  <si>
+    <t>kétnyelvű</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to pet </t>
+  </si>
+  <si>
+    <t>simogatni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to caress </t>
+  </si>
+  <si>
+    <t>simogatni </t>
+  </si>
+  <si>
+    <t xml:space="preserve">to stroke </t>
+  </si>
+  <si>
+    <t xml:space="preserve">suspicion </t>
+  </si>
+  <si>
+    <t>gyanú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upbringing </t>
+  </si>
+  <si>
+    <t>felnevelés, neveltetés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">awareness </t>
+  </si>
+  <si>
+    <t>tudatosság</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to be aware of </t>
+  </si>
+  <si>
+    <t>tudatában lenni vminek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to increase </t>
+  </si>
+  <si>
+    <t>emelkedni, növelni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brick </t>
+  </si>
+  <si>
+    <t>tégla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to mislead </t>
+  </si>
+  <si>
+    <t>félrevezetni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to edit out </t>
+  </si>
+  <si>
+    <t>kivágni, eltávolítani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to carry out </t>
+  </si>
+  <si>
+    <t>véghezvinni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">as well as </t>
+  </si>
+  <si>
+    <t>ugyanúgy, mint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to purchase </t>
+  </si>
+  <si>
+    <t>venni, vásárolni vmit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">field practice/fieldwork </t>
+  </si>
+  <si>
+    <t>terepgyakorlat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cautious </t>
+  </si>
+  <si>
+    <t>elővigyázatos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">surface - </t>
+  </si>
+  <si>
+    <t>felület</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to trap - </t>
+  </si>
+  <si>
+    <t>csapdába ejteni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absence - </t>
+  </si>
+  <si>
+    <t>hiány</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vastness -  </t>
+  </si>
+  <si>
+    <t>nagyság, hatalmasság</t>
+  </si>
+  <si>
+    <t xml:space="preserve">desolation - </t>
+  </si>
+  <si>
+    <t>elhagyatottság, magány</t>
+  </si>
+  <si>
+    <t>essential -</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> szükséges, alapvető</t>
+  </si>
+  <si>
+    <t xml:space="preserve">repeatedly - </t>
+  </si>
+  <si>
+    <t>ismételten, újra meg újra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to prove - </t>
+  </si>
+  <si>
+    <t>bizonyítani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to make/earn a living - </t>
+  </si>
+  <si>
+    <t>megélni vmiből, keresni pénzt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amazement - </t>
+  </si>
+  <si>
+    <t>megdöbbenés, csodálkozás</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gain - </t>
+  </si>
+  <si>
+    <t>megnyer, elnyer, gyarapodik, szerez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proof - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">demanding - </t>
+  </si>
+  <si>
+    <t>megterhelő</t>
+  </si>
+  <si>
+    <t xml:space="preserve">offered grade - </t>
+  </si>
+  <si>
+    <t>megajánlott jegy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">time-consuming - </t>
+  </si>
+  <si>
+    <t>időpazarló</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to wind down - </t>
+  </si>
+  <si>
+    <t>kikapcsolni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to take your mind off of things - </t>
+  </si>
+  <si>
+    <t>kikapcsolni, nem gondolni rá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assignment - </t>
+  </si>
+  <si>
+    <t>beadandó, nagyobb házi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the clock change - </t>
+  </si>
+  <si>
+    <t>óraátállítás</t>
+  </si>
+  <si>
+    <t xml:space="preserve">necessity - </t>
+  </si>
+  <si>
+    <t>szükségesség</t>
+  </si>
+  <si>
+    <t xml:space="preserve">congestion - </t>
+  </si>
+  <si>
+    <t>torlódás, dugulás, zsúfoltság</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to loosen - </t>
+  </si>
+  <si>
+    <t>lazítani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">theoretically - </t>
+  </si>
+  <si>
+    <t>elméleti szinten, elméletileg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">matter - </t>
+  </si>
+  <si>
+    <t>gond, probléma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to clamp - </t>
+  </si>
+  <si>
+    <t>szorítani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fortnight - </t>
+  </si>
+  <si>
+    <t>két hét</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pathetic sight - </t>
+  </si>
+  <si>
+    <t>szánalmas látvány</t>
+  </si>
+  <si>
+    <t xml:space="preserve">observer - </t>
+  </si>
+  <si>
+    <t>megfigyelő</t>
+  </si>
+  <si>
+    <t xml:space="preserve">juxtaposition - </t>
+  </si>
+  <si>
+    <t>egymás mellé helyezés</t>
+  </si>
+  <si>
+    <t>menace -</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> veszélyforrás, rossz viselkedésű valaki,  veszedelem</t>
+  </si>
+  <si>
+    <t>to take your mind off of (something) -</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> nem gondolni rá, eltávolodni tőle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mundanity - </t>
+  </si>
+  <si>
+    <t>hétköznapiság</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fencing - </t>
+  </si>
+  <si>
+    <t>vívás</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intimidating - </t>
+  </si>
+  <si>
+    <t>ijesztő, félelmet keltő</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cavalry - </t>
+  </si>
+  <si>
+    <t>lovasság</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loose - </t>
+  </si>
+  <si>
+    <t>laza, bő</t>
+  </si>
+  <si>
+    <t xml:space="preserve">steady - </t>
+  </si>
+  <si>
+    <t>stabil, biztos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tyre - </t>
+  </si>
+  <si>
+    <t>gumiabroncs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to injure – </t>
+  </si>
+  <si>
+    <t>megsérül, sérülést okoz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adjust - </t>
+  </si>
+  <si>
+    <t>alkalmazkodni, beállítani, megigazítani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avoidable - </t>
+  </si>
+  <si>
+    <t>elkerülhető</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avoidant - </t>
+  </si>
+  <si>
+    <t>elkerülő (ember)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">injuries - </t>
+  </si>
+  <si>
+    <t>sérülések</t>
+  </si>
+  <si>
+    <t xml:space="preserve">effectiveness - </t>
+  </si>
+  <si>
+    <t>hatékonyság</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to occur - </t>
+  </si>
+  <si>
+    <t>előfordulni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quirk - </t>
+  </si>
+  <si>
+    <t>furcsaság, különös szokás</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to resist - </t>
+  </si>
+  <si>
+    <t>ellenállni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to switch off - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">to switch on - </t>
+  </si>
+  <si>
+    <t>bekapcsolni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ought to - </t>
+  </si>
+  <si>
+    <t>kell, kellene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tights - </t>
+  </si>
+  <si>
+    <t>harisnya</t>
+  </si>
+  <si>
+    <t>paták</t>
+  </si>
+  <si>
+    <t>hoof</t>
+  </si>
+  <si>
+    <t>pata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hooves </t>
+  </si>
+  <si>
+    <t xml:space="preserve">enclosure </t>
+  </si>
+  <si>
+    <t>kifutó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for once </t>
+  </si>
+  <si>
+    <t>most az egyszer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to make matters worse </t>
+  </si>
+  <si>
+    <t>hogy még tovább rontsunk a helyzeten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to end up doing stg </t>
+  </si>
+  <si>
+    <t>az a vége hogy ő csinálja meg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to demand </t>
+  </si>
+  <si>
+    <t>követelni, igényelni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demand </t>
+  </si>
+  <si>
+    <t>követelés, igény</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to permit </t>
+  </si>
+  <si>
+    <t>engedni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">permissible </t>
+  </si>
+  <si>
+    <t>engedélyezett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">permit </t>
+  </si>
+  <si>
+    <t>engedély</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stiffer </t>
+  </si>
+  <si>
+    <t>merevebb, keményebb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">limbs </t>
+  </si>
+  <si>
+    <t>végtagok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trunk </t>
+  </si>
+  <si>
+    <t>törzs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foil </t>
+  </si>
+  <si>
+    <t>tőr</t>
+  </si>
+  <si>
+    <t>sword -</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> kard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">equivalent - </t>
+  </si>
+  <si>
+    <t>megfelelő(je)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">equivalence - </t>
+  </si>
+  <si>
+    <t>megfelelés, azzal egyenértékű </t>
+  </si>
+  <si>
+    <t xml:space="preserve">duel - </t>
+  </si>
+  <si>
+    <t>párbaj</t>
   </si>
 </sst>
 </file>
@@ -366,39 +958,1241 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="48.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
       </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>113</v>
+      </c>
+      <c r="B41" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>111</v>
+      </c>
+      <c r="B42" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>117</v>
+      </c>
+      <c r="B43" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>119</v>
+      </c>
+      <c r="B44" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>115</v>
+      </c>
+      <c r="B45" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>121</v>
+      </c>
+      <c r="B46" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>123</v>
+      </c>
+      <c r="B47" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>129</v>
+      </c>
+      <c r="B48" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>157</v>
+      </c>
+      <c r="B49" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>159</v>
+      </c>
+      <c r="B50" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>97</v>
+      </c>
+      <c r="B51" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B52" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>164</v>
+      </c>
+      <c r="B53" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>166</v>
+      </c>
+      <c r="B54" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>127</v>
+      </c>
+      <c r="B55" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>169</v>
+      </c>
+      <c r="B56" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>167</v>
+      </c>
+      <c r="B57" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>125</v>
+      </c>
+      <c r="B58" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>172</v>
+      </c>
+      <c r="B59" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>174</v>
+      </c>
+      <c r="B60" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B63" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>178</v>
+      </c>
+      <c r="B64" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>131</v>
+      </c>
+      <c r="B65" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>180</v>
+      </c>
+      <c r="B66" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>182</v>
+      </c>
+      <c r="B67" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>204</v>
+      </c>
+      <c r="B68" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>202</v>
+      </c>
+      <c r="B69" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>200</v>
+      </c>
+      <c r="B70" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>198</v>
+      </c>
+      <c r="B71" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>196</v>
+      </c>
+      <c r="B72" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>194</v>
+      </c>
+      <c r="B73" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>192</v>
+      </c>
+      <c r="B74" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>190</v>
+      </c>
+      <c r="B75" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B76" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>186</v>
+      </c>
+      <c r="B77" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>184</v>
+      </c>
+      <c r="B78" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>135</v>
+      </c>
+      <c r="B79" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>155</v>
+      </c>
+      <c r="B80" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>153</v>
+      </c>
+      <c r="B81" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>133</v>
+      </c>
+      <c r="B82" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>155</v>
+      </c>
+      <c r="B83" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>153</v>
+      </c>
+      <c r="B84" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>145</v>
+      </c>
+      <c r="B85" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>143</v>
+      </c>
+      <c r="B86" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>139</v>
+      </c>
+      <c r="B87" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>141</v>
+      </c>
+      <c r="B88" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>147</v>
+      </c>
+      <c r="B89" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>149</v>
+      </c>
+      <c r="B90" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>151</v>
+      </c>
+      <c r="B91" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>137</v>
+      </c>
+      <c r="B92" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>109</v>
+      </c>
+      <c r="B93" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>107</v>
+      </c>
+      <c r="B94" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>105</v>
+      </c>
+      <c r="B95" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>103</v>
+      </c>
+      <c r="B96" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>101</v>
+      </c>
+      <c r="B97" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>99</v>
+      </c>
+      <c r="B98" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>97</v>
+      </c>
+      <c r="B99" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>95</v>
+      </c>
+      <c r="B100" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>93</v>
+      </c>
+      <c r="B101" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>91</v>
+      </c>
+      <c r="B102" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>7</v>
+      </c>
+      <c r="B103" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>88</v>
+      </c>
+      <c r="B104" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>86</v>
+      </c>
+      <c r="B105" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>84</v>
+      </c>
+      <c r="B106" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>82</v>
+      </c>
+      <c r="B107" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>80</v>
+      </c>
+      <c r="B108" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17805C46-17C0-4B33-B5E8-FAC4E7BC2D5B}">
+  <dimension ref="A1:B46"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>180</v>
+      </c>
       <c r="B4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>196</v>
+      </c>
+      <c r="B10" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>192</v>
+      </c>
+      <c r="B12" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>190</v>
+      </c>
+      <c r="B13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>188</v>
+      </c>
+      <c r="B14" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>186</v>
+      </c>
+      <c r="B15" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>135</v>
+      </c>
+      <c r="B17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>155</v>
+      </c>
+      <c r="B18" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>155</v>
+      </c>
+      <c r="B21" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>143</v>
+      </c>
+      <c r="B24" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>139</v>
+      </c>
+      <c r="B25" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>141</v>
+      </c>
+      <c r="B26" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>147</v>
+      </c>
+      <c r="B27" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>149</v>
+      </c>
+      <c r="B28" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>151</v>
+      </c>
+      <c r="B29" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>109</v>
+      </c>
+      <c r="B31" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>105</v>
+      </c>
+      <c r="B33" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>101</v>
+      </c>
+      <c r="B35" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>88</v>
+      </c>
+      <c r="B42" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>86</v>
+      </c>
+      <c r="B43" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>80</v>
+      </c>
+      <c r="B46" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/studyflow.xlsx
+++ b/studyflow.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\puszt\Downloads\StudyFlow_GitHub\studyflow_github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67EB4722-59D7-455B-A808-3393F39BC811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB239F0-DDE4-44F9-85F4-1B27D5B87836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="words" sheetId="1" r:id="rId1"/>
     <sheet name="10.26." sheetId="2" r:id="rId2"/>
+    <sheet name="zöld fogalmak" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="207">
   <si>
     <t>pantry</t>
   </si>
@@ -641,19 +642,41 @@
   </si>
   <si>
     <t>párbaj</t>
+  </si>
+  <si>
+    <t>ZÖLDINFRASTRUKTÚRA</t>
+  </si>
+  <si>
+    <t>„Zöldinfrastruktúrának nevezzük azokat a természetes és félig természetes területeket, valamint egyéb növényzettel fedett és ökológiai funkciót betöltő területek stratégiailag megtervezett hálózatát, amelyet úgy terveztek és irányítanak, hogy széleskörű ökoszisztéma-szolgáltatások nyújtására legyenek képesek”.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -676,8 +699,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -961,856 +988,856 @@
   <dimension ref="A1:B108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
         <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
         <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
         <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
         <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
         <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
         <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
         <v>23</v>
-      </c>
-      <c r="B12" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
         <v>25</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
         <v>27</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
         <v>29</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
         <v>31</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
         <v>33</v>
-      </c>
-      <c r="B17" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
         <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
         <v>37</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
         <v>39</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
         <v>37</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
         <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
         <v>44</v>
-      </c>
-      <c r="B23" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" t="s">
         <v>46</v>
-      </c>
-      <c r="B24" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" t="s">
         <v>48</v>
-      </c>
-      <c r="B25" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" t="s">
         <v>50</v>
-      </c>
-      <c r="B26" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" t="s">
         <v>52</v>
-      </c>
-      <c r="B27" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" t="s">
         <v>54</v>
-      </c>
-      <c r="B28" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" t="s">
         <v>56</v>
-      </c>
-      <c r="B29" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" t="s">
         <v>58</v>
-      </c>
-      <c r="B30" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" t="s">
         <v>60</v>
-      </c>
-      <c r="B31" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" t="s">
         <v>62</v>
-      </c>
-      <c r="B32" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" t="s">
         <v>64</v>
-      </c>
-      <c r="B33" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" t="s">
         <v>66</v>
-      </c>
-      <c r="B34" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" t="s">
         <v>68</v>
-      </c>
-      <c r="B35" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" t="s">
         <v>70</v>
-      </c>
-      <c r="B36" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" t="s">
         <v>74</v>
-      </c>
-      <c r="B37" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" t="s">
         <v>72</v>
-      </c>
-      <c r="B38" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" t="s">
         <v>76</v>
-      </c>
-      <c r="B39" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" t="s">
         <v>78</v>
-      </c>
-      <c r="B40" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" t="s">
         <v>113</v>
-      </c>
-      <c r="B41" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>110</v>
+      </c>
+      <c r="B42" t="s">
         <v>111</v>
-      </c>
-      <c r="B42" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" t="s">
         <v>117</v>
-      </c>
-      <c r="B43" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" t="s">
         <v>119</v>
-      </c>
-      <c r="B44" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>114</v>
+      </c>
+      <c r="B45" t="s">
         <v>115</v>
-      </c>
-      <c r="B45" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>120</v>
+      </c>
+      <c r="B46" t="s">
         <v>121</v>
-      </c>
-      <c r="B46" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>122</v>
+      </c>
+      <c r="B47" t="s">
         <v>123</v>
-      </c>
-      <c r="B47" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>128</v>
+      </c>
+      <c r="B48" t="s">
         <v>129</v>
-      </c>
-      <c r="B48" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>156</v>
+      </c>
+      <c r="B49" t="s">
         <v>157</v>
-      </c>
-      <c r="B49" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>158</v>
+      </c>
+      <c r="B50" t="s">
         <v>159</v>
-      </c>
-      <c r="B50" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>160</v>
+      </c>
+      <c r="B51" t="s">
         <v>97</v>
-      </c>
-      <c r="B51" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>161</v>
+      </c>
+      <c r="B52" t="s">
         <v>162</v>
-      </c>
-      <c r="B52" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>163</v>
+      </c>
+      <c r="B53" t="s">
         <v>164</v>
-      </c>
-      <c r="B53" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>165</v>
+      </c>
+      <c r="B54" t="s">
         <v>166</v>
-      </c>
-      <c r="B54" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>126</v>
+      </c>
+      <c r="B55" t="s">
         <v>127</v>
-      </c>
-      <c r="B55" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>168</v>
+      </c>
+      <c r="B56" t="s">
         <v>169</v>
-      </c>
-      <c r="B56" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>170</v>
+      </c>
+      <c r="B57" t="s">
         <v>167</v>
-      </c>
-      <c r="B57" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>124</v>
+      </c>
+      <c r="B58" t="s">
         <v>125</v>
-      </c>
-      <c r="B58" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>171</v>
+      </c>
+      <c r="B59" t="s">
         <v>172</v>
-      </c>
-      <c r="B59" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>173</v>
+      </c>
+      <c r="B60" t="s">
         <v>174</v>
-      </c>
-      <c r="B60" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>175</v>
+      </c>
+      <c r="B63" t="s">
         <v>176</v>
-      </c>
-      <c r="B63" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>177</v>
+      </c>
+      <c r="B64" t="s">
         <v>178</v>
-      </c>
-      <c r="B64" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>130</v>
+      </c>
+      <c r="B65" t="s">
         <v>131</v>
-      </c>
-      <c r="B65" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>179</v>
+      </c>
+      <c r="B66" t="s">
         <v>180</v>
-      </c>
-      <c r="B66" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>181</v>
+      </c>
+      <c r="B67" t="s">
         <v>182</v>
-      </c>
-      <c r="B67" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>203</v>
+      </c>
+      <c r="B68" t="s">
         <v>204</v>
-      </c>
-      <c r="B68" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>201</v>
+      </c>
+      <c r="B69" t="s">
         <v>202</v>
-      </c>
-      <c r="B69" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>199</v>
+      </c>
+      <c r="B70" t="s">
         <v>200</v>
-      </c>
-      <c r="B70" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>197</v>
+      </c>
+      <c r="B71" t="s">
         <v>198</v>
-      </c>
-      <c r="B71" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>195</v>
+      </c>
+      <c r="B72" t="s">
         <v>196</v>
-      </c>
-      <c r="B72" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>193</v>
+      </c>
+      <c r="B73" t="s">
         <v>194</v>
-      </c>
-      <c r="B73" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>191</v>
+      </c>
+      <c r="B74" t="s">
         <v>192</v>
-      </c>
-      <c r="B74" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>189</v>
+      </c>
+      <c r="B75" t="s">
         <v>190</v>
-      </c>
-      <c r="B75" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>187</v>
+      </c>
+      <c r="B76" t="s">
         <v>188</v>
-      </c>
-      <c r="B76" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>185</v>
+      </c>
+      <c r="B77" t="s">
         <v>186</v>
-      </c>
-      <c r="B77" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>183</v>
+      </c>
+      <c r="B78" t="s">
         <v>184</v>
-      </c>
-      <c r="B78" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>134</v>
+      </c>
+      <c r="B79" t="s">
         <v>135</v>
-      </c>
-      <c r="B79" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>154</v>
+      </c>
+      <c r="B80" t="s">
         <v>155</v>
-      </c>
-      <c r="B80" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>152</v>
+      </c>
+      <c r="B81" t="s">
         <v>153</v>
-      </c>
-      <c r="B81" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>132</v>
+      </c>
+      <c r="B82" t="s">
         <v>133</v>
-      </c>
-      <c r="B82" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>154</v>
+      </c>
+      <c r="B83" t="s">
         <v>155</v>
-      </c>
-      <c r="B83" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>152</v>
+      </c>
+      <c r="B84" t="s">
         <v>153</v>
-      </c>
-      <c r="B84" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>144</v>
+      </c>
+      <c r="B85" t="s">
         <v>145</v>
-      </c>
-      <c r="B85" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>142</v>
+      </c>
+      <c r="B86" t="s">
         <v>143</v>
-      </c>
-      <c r="B86" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>138</v>
+      </c>
+      <c r="B87" t="s">
         <v>139</v>
-      </c>
-      <c r="B87" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>140</v>
+      </c>
+      <c r="B88" t="s">
         <v>141</v>
-      </c>
-      <c r="B88" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>146</v>
+      </c>
+      <c r="B89" t="s">
         <v>147</v>
-      </c>
-      <c r="B89" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>148</v>
+      </c>
+      <c r="B90" t="s">
         <v>149</v>
-      </c>
-      <c r="B90" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>150</v>
+      </c>
+      <c r="B91" t="s">
         <v>151</v>
-      </c>
-      <c r="B91" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>136</v>
+      </c>
+      <c r="B92" t="s">
         <v>137</v>
-      </c>
-      <c r="B92" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>108</v>
+      </c>
+      <c r="B93" t="s">
         <v>109</v>
-      </c>
-      <c r="B93" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>106</v>
+      </c>
+      <c r="B94" t="s">
         <v>107</v>
-      </c>
-      <c r="B94" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>104</v>
+      </c>
+      <c r="B95" t="s">
         <v>105</v>
-      </c>
-      <c r="B95" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" t="s">
         <v>103</v>
-      </c>
-      <c r="B96" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>100</v>
+      </c>
+      <c r="B97" t="s">
         <v>101</v>
-      </c>
-      <c r="B97" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>98</v>
+      </c>
+      <c r="B98" t="s">
         <v>99</v>
-      </c>
-      <c r="B98" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>96</v>
+      </c>
+      <c r="B99" t="s">
         <v>97</v>
-      </c>
-      <c r="B99" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>94</v>
+      </c>
+      <c r="B100" t="s">
         <v>95</v>
-      </c>
-      <c r="B100" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>92</v>
+      </c>
+      <c r="B101" t="s">
         <v>93</v>
-      </c>
-      <c r="B101" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>90</v>
+      </c>
+      <c r="B102" t="s">
         <v>91</v>
-      </c>
-      <c r="B102" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>89</v>
+      </c>
+      <c r="B103" t="s">
         <v>7</v>
-      </c>
-      <c r="B103" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>87</v>
+      </c>
+      <c r="B104" t="s">
         <v>88</v>
-      </c>
-      <c r="B104" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>85</v>
+      </c>
+      <c r="B105" t="s">
         <v>86</v>
-      </c>
-      <c r="B105" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>83</v>
+      </c>
+      <c r="B106" t="s">
         <v>84</v>
-      </c>
-      <c r="B106" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>81</v>
+      </c>
+      <c r="B107" t="s">
         <v>82</v>
-      </c>
-      <c r="B107" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>79</v>
+      </c>
+      <c r="B108" t="s">
         <v>80</v>
-      </c>
-      <c r="B108" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1820,379 +1847,466 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17805C46-17C0-4B33-B5E8-FAC4E7BC2D5B}">
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B9" t="s">
         <v>176</v>
       </c>
-      <c r="B1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B10" t="s">
         <v>178</v>
       </c>
-      <c r="B2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" t="s">
         <v>131</v>
       </c>
-      <c r="B3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B12" t="s">
         <v>180</v>
       </c>
-      <c r="B4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>181</v>
+      </c>
+      <c r="B13" t="s">
         <v>182</v>
       </c>
-      <c r="B5" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>203</v>
+      </c>
+      <c r="B14" t="s">
         <v>204</v>
       </c>
-      <c r="B6" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>201</v>
+      </c>
+      <c r="B15" t="s">
         <v>202</v>
       </c>
-      <c r="B7" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>199</v>
+      </c>
+      <c r="B16" t="s">
         <v>200</v>
-      </c>
-      <c r="B8" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>198</v>
-      </c>
-      <c r="B9" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>196</v>
-      </c>
-      <c r="B10" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B11" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>192</v>
-      </c>
-      <c r="B12" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>190</v>
-      </c>
-      <c r="B13" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>188</v>
-      </c>
-      <c r="B14" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>186</v>
-      </c>
-      <c r="B15" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>184</v>
-      </c>
-      <c r="B16" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>135</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s">
-        <v>134</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s">
-        <v>154</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>153</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="B20" t="s">
-        <v>132</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="B21" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="B23" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>143</v>
+        <v>183</v>
       </c>
       <c r="B24" t="s">
-        <v>142</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B25" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B26" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B27" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="B28" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B29" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="B30" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>101</v>
+        <v>146</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>97</v>
+        <v>150</v>
       </c>
       <c r="B37" t="s">
-        <v>96</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>7</v>
+        <v>104</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="B42" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="B44" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="B45" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>94</v>
+      </c>
+      <c r="B46" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>89</v>
+      </c>
+      <c r="B49" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>87</v>
+      </c>
+      <c r="B50" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>85</v>
+      </c>
+      <c r="B51" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>83</v>
+      </c>
+      <c r="B52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>81</v>
+      </c>
+      <c r="B53" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>79</v>
+      </c>
+      <c r="B54" t="s">
         <v>80</v>
       </c>
-      <c r="B46" t="s">
-        <v>79</v>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB7746A-7A09-4035-BC86-847147D175BE}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B1" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>

--- a/studyflow.xlsx
+++ b/studyflow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\puszt\Downloads\StudyFlow_GitHub\studyflow_github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925333BA-F70B-420B-A2A1-DDB3BDA94655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95A85DF-206E-4A77-A0DA-48ACA15E2F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10.26." sheetId="2" r:id="rId1"/>
@@ -988,445 +988,445 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17805C46-17C0-4B33-B5E8-FAC4E7BC2D5B}">
-  <dimension ref="A1:E54"/>
+  <dimension ref="A2:D55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" t="s">
         <v>67</v>
       </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" t="s">
         <v>71</v>
       </c>
-      <c r="B3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" t="s">
         <v>75</v>
       </c>
-      <c r="B4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" t="s">
         <v>120</v>
       </c>
-      <c r="B5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" t="s">
         <v>122</v>
       </c>
-      <c r="B6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B8" t="s">
         <v>163</v>
       </c>
-      <c r="B7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" t="s">
         <v>171</v>
       </c>
-      <c r="B8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" t="s">
         <v>175</v>
       </c>
-      <c r="B9" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>178</v>
+      </c>
+      <c r="B11" t="s">
         <v>177</v>
       </c>
-      <c r="B10" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" t="s">
         <v>130</v>
       </c>
-      <c r="B11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" t="s">
         <v>179</v>
       </c>
-      <c r="B12" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B14" t="s">
         <v>181</v>
       </c>
-      <c r="B13" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>204</v>
+      </c>
+      <c r="B15" t="s">
         <v>203</v>
       </c>
-      <c r="B14" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>202</v>
+      </c>
+      <c r="B16" t="s">
         <v>201</v>
-      </c>
-      <c r="B15" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>199</v>
-      </c>
-      <c r="B16" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B21" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B22" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B23" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B24" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="B25" t="s">
-        <v>135</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="B26" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B27" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="B28" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="B29" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B31" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B32" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B33" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B34" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B35" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B36" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B37" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="B39" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B42" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B43" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B46" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B48" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B49" t="s">
-        <v>7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B51" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B52" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B53" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>82</v>
+      </c>
+      <c r="B54" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>80</v>
+      </c>
+      <c r="B55" t="s">
         <v>79</v>
-      </c>
-      <c r="B54" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1436,859 +1436,859 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B108"/>
+  <dimension ref="A2:B109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B33" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B34" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B43" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B44" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B45" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B47" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B48" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="B49" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B50" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B51" t="s">
-        <v>97</v>
+        <v>158</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>161</v>
+        <v>97</v>
       </c>
       <c r="B52" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B53" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B54" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="B55" t="s">
-        <v>127</v>
+        <v>165</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="B56" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B57" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>124</v>
+        <v>167</v>
       </c>
       <c r="B58" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>171</v>
+        <v>125</v>
       </c>
       <c r="B59" t="s">
-        <v>172</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>172</v>
+      </c>
+      <c r="B60" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>174</v>
+      </c>
+      <c r="B61" t="s">
         <v>173</v>
-      </c>
-      <c r="B60" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>175</v>
-      </c>
-      <c r="B63" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B64" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>130</v>
+        <v>178</v>
       </c>
       <c r="B65" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="B66" t="s">
-        <v>180</v>
+        <v>130</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B67" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="B68" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B69" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B70" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B71" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B72" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B73" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B74" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B75" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B77" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B78" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="B79" t="s">
-        <v>135</v>
+        <v>183</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="B80" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B81" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="B82" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="B83" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B84" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B85" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B86" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B87" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B88" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B89" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B90" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B91" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B92" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="B93" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B94" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B95" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B96" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B97" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B98" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B99" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B100" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B101" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B102" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B103" t="s">
-        <v>7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B104" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B105" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B106" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B107" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>82</v>
+      </c>
+      <c r="B108" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>80</v>
+      </c>
+      <c r="B109" t="s">
         <v>79</v>
-      </c>
-      <c r="B108" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2298,17 +2298,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB7746A-7A09-4035-BC86-847147D175BE}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A2:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>206</v>
       </c>
     </row>

--- a/studyflow.xlsx
+++ b/studyflow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\puszt\Downloads\StudyFlow_GitHub\studyflow_github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95A85DF-206E-4A77-A0DA-48ACA15E2F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1F5E83-1074-4B2E-B191-C0B1BE63F0BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10.26." sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="211">
   <si>
     <t>pantry</t>
   </si>
@@ -648,6 +648,18 @@
   </si>
   <si>
     <t>„Zöldinfrastruktúrának nevezzük azokat a természetes és félig természetes területeket, valamint egyéb növényzettel fedett és ökológiai funkciót betöltő területek stratégiailag megtervezett hálózatát, amelyet úgy terveztek és irányítanak, hogy széleskörű ökoszisztéma-szolgáltatások nyújtására legyenek képesek”.</t>
+  </si>
+  <si>
+    <t>magyar</t>
+  </si>
+  <si>
+    <t>angol</t>
+  </si>
+  <si>
+    <t>fogalom</t>
+  </si>
+  <si>
+    <t>kifejtés</t>
   </si>
 </sst>
 </file>
@@ -988,7 +1000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17805C46-17C0-4B33-B5E8-FAC4E7BC2D5B}">
-  <dimension ref="A2:D55"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
@@ -996,6 +1008,14 @@
     <col min="4" max="4" width="41.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1" t="s">
+        <v>208</v>
+      </c>
+    </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
@@ -2298,12 +2318,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB7746A-7A09-4035-BC86-847147D175BE}">
-  <dimension ref="A2:B2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B1" t="s">
+        <v>210</v>
+      </c>
+    </row>
     <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>205</v>

--- a/studyflow.xlsx
+++ b/studyflow.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\puszt\Downloads\StudyFlow_GitHub\studyflow_github\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\puszt\Downloads\StudyFlow_GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1F5E83-1074-4B2E-B191-C0B1BE63F0BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BF6E98-6946-44C9-977D-A446D9744CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="250">
   <si>
     <t>pantry</t>
   </si>
@@ -660,6 +660,123 @@
   </si>
   <si>
     <t>kifejtés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">desolation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">observer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">juxtaposition </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ought to </t>
+  </si>
+  <si>
+    <t xml:space="preserve">surface </t>
+  </si>
+  <si>
+    <t xml:space="preserve">fencing </t>
+  </si>
+  <si>
+    <t xml:space="preserve">duel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">equivalence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">equivalent </t>
+  </si>
+  <si>
+    <t xml:space="preserve">sword </t>
+  </si>
+  <si>
+    <t xml:space="preserve">cavalry </t>
+  </si>
+  <si>
+    <t xml:space="preserve">to occur </t>
+  </si>
+  <si>
+    <t xml:space="preserve">effectiveness </t>
+  </si>
+  <si>
+    <t xml:space="preserve">intimidating </t>
+  </si>
+  <si>
+    <t xml:space="preserve">adjust </t>
+  </si>
+  <si>
+    <t xml:space="preserve">to injure </t>
+  </si>
+  <si>
+    <t xml:space="preserve">steady </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tyre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">avoidable </t>
+  </si>
+  <si>
+    <t xml:space="preserve">avoidant </t>
+  </si>
+  <si>
+    <t xml:space="preserve">injuries </t>
+  </si>
+  <si>
+    <t xml:space="preserve">loose </t>
+  </si>
+  <si>
+    <t xml:space="preserve">to loosen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">congestion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">necessity </t>
+  </si>
+  <si>
+    <t xml:space="preserve">the clock change </t>
+  </si>
+  <si>
+    <t xml:space="preserve">assignment </t>
+  </si>
+  <si>
+    <t xml:space="preserve">to take your mind off of things </t>
+  </si>
+  <si>
+    <t xml:space="preserve">to wind down </t>
+  </si>
+  <si>
+    <t xml:space="preserve">time-consuming </t>
+  </si>
+  <si>
+    <t xml:space="preserve">offered grade </t>
+  </si>
+  <si>
+    <t xml:space="preserve">demanding </t>
+  </si>
+  <si>
+    <t xml:space="preserve">proof </t>
+  </si>
+  <si>
+    <t xml:space="preserve">gain </t>
+  </si>
+  <si>
+    <t xml:space="preserve">amazement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">to make/earn a living </t>
+  </si>
+  <si>
+    <t xml:space="preserve">to prove </t>
+  </si>
+  <si>
+    <t xml:space="preserve">repeatedly </t>
   </si>
 </sst>
 </file>
@@ -1030,7 +1147,7 @@
         <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1038,7 +1155,7 @@
         <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1046,7 +1163,7 @@
         <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1054,7 +1171,7 @@
         <v>121</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1062,7 +1179,7 @@
         <v>123</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1070,7 +1187,7 @@
         <v>164</v>
       </c>
       <c r="B8" t="s">
-        <v>163</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1102,7 +1219,7 @@
         <v>131</v>
       </c>
       <c r="B12" t="s">
-        <v>130</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1126,7 +1243,7 @@
         <v>204</v>
       </c>
       <c r="B15" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1134,7 +1251,7 @@
         <v>202</v>
       </c>
       <c r="B16" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1142,7 +1259,7 @@
         <v>200</v>
       </c>
       <c r="B17" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1150,7 +1267,7 @@
         <v>198</v>
       </c>
       <c r="B18" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1214,7 +1331,7 @@
         <v>135</v>
       </c>
       <c r="B26" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1222,7 +1339,7 @@
         <v>155</v>
       </c>
       <c r="B27" t="s">
-        <v>154</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1230,7 +1347,7 @@
         <v>153</v>
       </c>
       <c r="B28" t="s">
-        <v>152</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1238,7 +1355,7 @@
         <v>133</v>
       </c>
       <c r="B29" t="s">
-        <v>132</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -1246,7 +1363,7 @@
         <v>155</v>
       </c>
       <c r="B30" t="s">
-        <v>154</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -1254,7 +1371,7 @@
         <v>153</v>
       </c>
       <c r="B31" t="s">
-        <v>152</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1262,7 +1379,7 @@
         <v>145</v>
       </c>
       <c r="B32" t="s">
-        <v>144</v>
+        <v>226</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -1270,7 +1387,7 @@
         <v>143</v>
       </c>
       <c r="B33" t="s">
-        <v>142</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -1278,7 +1395,7 @@
         <v>139</v>
       </c>
       <c r="B34" t="s">
-        <v>138</v>
+        <v>228</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -1286,7 +1403,7 @@
         <v>141</v>
       </c>
       <c r="B35" t="s">
-        <v>140</v>
+        <v>229</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1294,7 +1411,7 @@
         <v>147</v>
       </c>
       <c r="B36" t="s">
-        <v>146</v>
+        <v>230</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1302,7 +1419,7 @@
         <v>149</v>
       </c>
       <c r="B37" t="s">
-        <v>148</v>
+        <v>231</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -1310,7 +1427,7 @@
         <v>151</v>
       </c>
       <c r="B38" t="s">
-        <v>150</v>
+        <v>232</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -1318,7 +1435,7 @@
         <v>137</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>233</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -1326,7 +1443,7 @@
         <v>109</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>234</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -1334,7 +1451,7 @@
         <v>107</v>
       </c>
       <c r="B41" t="s">
-        <v>106</v>
+        <v>235</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -1342,7 +1459,7 @@
         <v>105</v>
       </c>
       <c r="B42" t="s">
-        <v>104</v>
+        <v>236</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -1350,7 +1467,7 @@
         <v>103</v>
       </c>
       <c r="B43" t="s">
-        <v>102</v>
+        <v>237</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -1358,7 +1475,7 @@
         <v>101</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
+        <v>238</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -1366,7 +1483,7 @@
         <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>239</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -1374,7 +1491,7 @@
         <v>97</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -1382,7 +1499,7 @@
         <v>95</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>241</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -1390,7 +1507,7 @@
         <v>93</v>
       </c>
       <c r="B48" t="s">
-        <v>92</v>
+        <v>242</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -1398,7 +1515,7 @@
         <v>91</v>
       </c>
       <c r="B49" t="s">
-        <v>90</v>
+        <v>243</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -1406,7 +1523,7 @@
         <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>89</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -1414,7 +1531,7 @@
         <v>88</v>
       </c>
       <c r="B51" t="s">
-        <v>87</v>
+        <v>245</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -1422,7 +1539,7 @@
         <v>86</v>
       </c>
       <c r="B52" t="s">
-        <v>85</v>
+        <v>246</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -1430,7 +1547,7 @@
         <v>84</v>
       </c>
       <c r="B53" t="s">
-        <v>83</v>
+        <v>247</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -1438,7 +1555,7 @@
         <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>81</v>
+        <v>248</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -1446,7 +1563,7 @@
         <v>80</v>
       </c>
       <c r="B55" t="s">
-        <v>79</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>

--- a/studyflow.xlsx
+++ b/studyflow.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\puszt\Downloads\StudyFlow_GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BF6E98-6946-44C9-977D-A446D9744CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C387F54-345E-4744-A4CB-8507942009FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10.26." sheetId="2" r:id="rId1"/>
     <sheet name="words" sheetId="1" r:id="rId2"/>
-    <sheet name="zöld fogalmak" sheetId="3" r:id="rId3"/>
+    <sheet name="jog" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="467">
   <si>
     <t>pantry</t>
   </si>
@@ -644,24 +644,12 @@
     <t>párbaj</t>
   </si>
   <si>
-    <t>ZÖLDINFRASTRUKTÚRA</t>
-  </si>
-  <si>
-    <t>„Zöldinfrastruktúrának nevezzük azokat a természetes és félig természetes területeket, valamint egyéb növényzettel fedett és ökológiai funkciót betöltő területek stratégiailag megtervezett hálózatát, amelyet úgy terveztek és irányítanak, hogy széleskörű ökoszisztéma-szolgáltatások nyújtására legyenek képesek”.</t>
-  </si>
-  <si>
     <t>magyar</t>
   </si>
   <si>
     <t>angol</t>
   </si>
   <si>
-    <t>fogalom</t>
-  </si>
-  <si>
-    <t>kifejtés</t>
-  </si>
-  <si>
     <t xml:space="preserve">absence </t>
   </si>
   <si>
@@ -777,13 +765,676 @@
   </si>
   <si>
     <t xml:space="preserve">repeatedly </t>
+  </si>
+  <si>
+    <t>Kérdés</t>
+  </si>
+  <si>
+    <t>Helyes válasz</t>
+  </si>
+  <si>
+    <t>1. Melyik kifejezés hiányzik? Ennek központi ________ a munkamegosztás, mely a közigazgatási szervek által elvégzendő feladatok és az ellátásukra hivatott szervezetek tagolását jelenti.</t>
+  </si>
+  <si>
+    <t>kategóriája</t>
+  </si>
+  <si>
+    <t>2. Melyik kifejezés hiányzik? A NAV hatásköre ________ kiterjed az adóhátralék bankszámláról történő letiltására, adóbírság kivetésére.</t>
+  </si>
+  <si>
+    <t>például</t>
+  </si>
+  <si>
+    <t>3. Melyik kifejezés hiányzik? Jegyezzük meg jól tehát, hogy ________ nélkül egy közigazgatási szerv feladatait nem képes hatékonyan ellátni!  Az illetékesség az adott hatóság földrajzi értelemben vett működési területét határozza meg.</t>
+  </si>
+  <si>
+    <t>hatáskör</t>
+  </si>
+  <si>
+    <t>4. Melyik kifejezés hiányzik? A KÖZIGAZGATÁSI SZERV MUNKASZERVEZETE A közigazgatási ________ jellemzője önálló munkaszervezet, hivatal működtetése, amelynek élén egyszemélyi felelős vezető (hivatalvezető) áll.</t>
+  </si>
+  <si>
+    <t>szervek</t>
+  </si>
+  <si>
+    <t>5. Melyik kifejezés hiányzik? A közintézetek ________ mindenekelőtt a tulajdonosi jogokat gyakorló (alapító) fenntartóval szemben biztosítja a jogi szabályozás.</t>
+  </si>
+  <si>
+    <t>autonómiáját</t>
+  </si>
+  <si>
+    <t>6. Melyik kifejezés hiányzik? Ezáltal a ________ hatásköre lesz a szolgáltatási jogviszony keretében az intézeti ellátottal összefüggésben döntéseket hozni, és ezek végrehatásáról gondoskodni.</t>
+  </si>
+  <si>
+    <t>közintézetnek</t>
+  </si>
+  <si>
+    <t>7. Melyik kifejezés hiányzik? Ezen belül a vezetőknek is ________ további vezetői és a beosztottaknak is lehetnek beosztottjaik, ugyanakkor aki nem vezető és nem beosztott, az nem tartozik a rendszerbe: kívülálló (ilyen például az ügyfél).</t>
+  </si>
+  <si>
+    <t>lehetnek</t>
+  </si>
+  <si>
+    <t>8. Melyik kifejezés hiányzik? A centralizáció mint ________ azt jelenti, hogy egy meghatározott szerv a közigazgatás szervezetének csúcsán helyezkedik el, s az irányítás innen történik.</t>
+  </si>
+  <si>
+    <t>központosítás</t>
+  </si>
+  <si>
+    <t>9. Melyik kifejezés hiányzik? A kirendeltség nem ________ önálló feladatés hatáskörrel rendelkező területi szervnek, csak az adott hatóság területileg kihelyezett belső szervezeti egységének.</t>
+  </si>
+  <si>
+    <t>minősül</t>
+  </si>
+  <si>
+    <t>10. Melyik kifejezés hiányzik? Az integráció ________, a részeknek egymáshoz illeszkedését jelenti, bizonyos értelemben a közigazgatás hierarchikusságát és centralizáltságát finomító, működését egységesítő elv.</t>
+  </si>
+  <si>
+    <t>egységesülést</t>
+  </si>
+  <si>
+    <t>11. Melyik kifejezés hiányzik? B) IRÁNYÍTÁS – Az ________ hierarchikus, alá-fölérendeltségi kapcsolatban álló közigazgatási szervek közötti hatalmi viszonyt irányításnak nevezzük.</t>
+  </si>
+  <si>
+    <t>egymással</t>
+  </si>
+  <si>
+    <t>12. Melyik kifejezés hiányzik? Az ellenőrzési ________ önálló gyakorlására nemcsak szervek közötti ún. belső viszonyban, hanem közigazgatási szerv és ügyfél között is találunk példákat (ezt nevezzük külső ellenőrzésnek).</t>
+  </si>
+  <si>
+    <t>funkció</t>
+  </si>
+  <si>
+    <t>13. Melyik kifejezés hiányzik? Megjegyezzük, hogy egyes ________ feladatok ellátása csak névlegesen valósul meg járási szinten, ugyanis számos ügykörben nem minden járási hivatal rendelkezik hatáskörrel.</t>
+  </si>
+  <si>
+    <t>hatósági</t>
+  </si>
+  <si>
+    <t>14. Melyik kifejezés hiányzik? A HELYI SZINT Magyarország ________ a települések típusai a következők: község, nagyközség, város, járásszékhely város, megyei jogú város, főváros és 23 kerülete.</t>
+  </si>
+  <si>
+    <t>területén</t>
+  </si>
+  <si>
+    <t>15. Melyik kifejezés hiányzik? Magyarországon – sok más ________ államhoz hasonlóan – a közigazgatásinak tekinthető feladatokat alapvetően az állam két szervezeti alrendszere, államigazgatási és önkormányzati szervek valósítják meg.</t>
+  </si>
+  <si>
+    <t>európai</t>
+  </si>
+  <si>
+    <t>16. Melyik kifejezés hiányzik? Ebben a részben ________ az egyes alrendszerek működésének főbb kapcsolódási pontjait.</t>
+  </si>
+  <si>
+    <t>áttekintjük</t>
+  </si>
+  <si>
+    <t>17. Melyik kifejezés hiányzik? Lényeges elem ________ a szolgáltató jellegű közigazgatás számára az ügyfél-közeliség érvényesülése.</t>
+  </si>
+  <si>
+    <t>ugyanis</t>
+  </si>
+  <si>
+    <t>18. Melyik kifejezés hiányzik? A középszinten belül a ________ igazgatás párhuzamos felépítésű, azaz önkormányzati és államigazgatási szervek egyaránt megtalálhatóak.</t>
+  </si>
+  <si>
+    <t>megyei</t>
+  </si>
+  <si>
+    <t>19. Melyik kifejezés hiányzik? Miniszterelnöknek ________ minden olyan személy, aki  büntetlen előéletű,  rendelkezik magyar állampolgársággal, és  az országgyűlési képviselők választásán passzív választójoga van (azaz választható).</t>
+  </si>
+  <si>
+    <t>javasolható</t>
+  </si>
+  <si>
+    <t>20. Melyik kifejezés hiányzik? Ez azt jelenti, hogy a kormányon belül csak a ________ az Országgyűlés által közvetlenül választott politikai vezető, vagyis a miniszterelnöknek van kormánya, nem pedig a kormánynak miniszterelnöke.</t>
+  </si>
+  <si>
+    <t>miniszterelnök</t>
+  </si>
+  <si>
+    <t>21. Melyik kifejezés hiányzik? A miniszter a ________ előírt feladatés hatáskörében önállóan jár el, és ezért felelősséggel tartozik (pl. az Országgyűlésben interpellálható).</t>
+  </si>
+  <si>
+    <t>jogszabályban</t>
+  </si>
+  <si>
+    <t>22. Melyik kifejezés hiányzik? Ez azt jelenti, hogy a miniszterelnök ________ függ, elfogadja-e azt, vagy sem.</t>
+  </si>
+  <si>
+    <t>mérlegelésétől</t>
+  </si>
+  <si>
+    <t>23. Melyik kifejezés hiányzik? A szakpolitikai ________ feladata az adott minisztériumhoz tartozó egyes szakterületi érdekek érvényesítése.</t>
+  </si>
+  <si>
+    <t>államtitkárok</t>
+  </si>
+  <si>
+    <t>24. Melyik kifejezés hiányzik? A járási ________ az a büntetlen előéletű, cselekvőképes és nagykorú magyar állampolgár nevezhető ki, aki felsőfokú végzettséggel és legalább 5 év közigazgatási gyakorlattal rendelkezik.</t>
+  </si>
+  <si>
+    <t>hivatalvezetőnek</t>
+  </si>
+  <si>
+    <t>25. Melyik kifejezés hiányzik? A bizalomvesztés miatt ________ tisztviselő jogosult végkielégítésre és 2 hónap felmentési idő letöltésére. c) Alkalmatlanság.</t>
+  </si>
+  <si>
+    <t>felmentett</t>
+  </si>
+  <si>
+    <t>26. Melyik kifejezés hiányzik? Vannak ________ a közigazgatásban, akik elvileg különböző területeken is képesek megállni a helyüket, őket nevezzük generalistáknak, ellentétben az egy területre szakosodott specialistákkal.</t>
+  </si>
+  <si>
+    <t>tisztviselők</t>
+  </si>
+  <si>
+    <t>27. Melyik kifejezés hiányzik? Ebbe a körbe tartozik a politikai ________ és főtanácsadók fizetésének megállapítása a központi államigazgatásban.  Vezetői munkakörök létesítése.</t>
+  </si>
+  <si>
+    <t>tanácsadók</t>
+  </si>
+  <si>
+    <t>28. Melyik kifejezés hiányzik? A fokozott ________ abban áll, hogy több bűncselekmény, mint például az emberölés vagy az emberrablás súlyosabban minősül, ha hivatalos személy sérelmére követik el.</t>
+  </si>
+  <si>
+    <t>védelem</t>
+  </si>
+  <si>
+    <t>29. Melyik kifejezés hiányzik? Azt jelenti, hogy a beosztott ________ a vezető által vallott értékekkel, célokkal, és munkáját ezek alapján végzi.</t>
+  </si>
+  <si>
+    <t>azonosul</t>
+  </si>
+  <si>
+    <t>30. Melyik kifejezés hiányzik? A törvény úgy ________, hogy a tisztviselő köteles felettese utasításait végrehajtani.</t>
+  </si>
+  <si>
+    <t>rendelkezik</t>
+  </si>
+  <si>
+    <t>31. Melyik kifejezés hiányzik? TÖRVÉNYESSÉGI ________ JOGKÖRÖK – A megyei kormányhivatal vezetőjének feladata a helyi és nemzetiségi önkormányzatok törvényességi felügyelete.</t>
+  </si>
+  <si>
+    <t>FELÜGYELETI</t>
+  </si>
+  <si>
+    <t>32. Melyik kifejezés hiányzik? Ezen felül speciális ________ minősül a főváros, ahol a koncentrált lakosságszám miatt kerületi hivatalok alakultak.</t>
+  </si>
+  <si>
+    <t>járásnak</t>
+  </si>
+  <si>
+    <t>33. Melyik kifejezés hiányzik? Ilyen szervnek ________ a Gazdasági Versenyhivatal Versenytanácsa, vagy a Közbeszerzési Döntőbizottság.</t>
+  </si>
+  <si>
+    <t>34. Melyik kifejezés hiányzik? Ilyen a Nemzeti ________ Testület (feladata a Magyar Szabványok /MSZ/ előírásainak meghatározása és közzététele).</t>
+  </si>
+  <si>
+    <t>Szabványügyi</t>
+  </si>
+  <si>
+    <t>35. Melyik kifejezés hiányzik? A gazdasági ________ feladata, hogy előmozdítsák a gazdaság fejlődését és szerveződését, a piaci magatartás tisztességét, a gazdasági tevékenységet folytatók általános, együttes érdekeinek érvényesítését.</t>
+  </si>
+  <si>
+    <t>kamarák</t>
+  </si>
+  <si>
+    <t>36. Melyik kifejezés hiányzik? Az elnökség ________ a küldöttgyűlések közötti időszakban a gazdasági kamara működésének irányítása.</t>
+  </si>
+  <si>
+    <t>feladata</t>
+  </si>
+  <si>
+    <t>37. Melyik kifejezés hiányzik? A KORMÁNY ________ HATÁSKÖRE A kormány a maga feladatkörében rendeleteket bocsát ki, és normatív határozatokat hoz, amelyeket a miniszterelnök ír alá.</t>
+  </si>
+  <si>
+    <t>JOGALKOTÁSI</t>
+  </si>
+  <si>
+    <t>38. Melyik kifejezés hiányzik? A MINISZTEREK ________ HATÁSKÖRE A kormány tagjai jogalkotási hatáskörrel rendelkeznek, feladatuk ellátása körében rendeleteket adhatnak ki.</t>
+  </si>
+  <si>
+    <t>39. Melyik kifejezés hiányzik? Amennyiben a ________ határidő eredménytelenül letelt, a kormányhivatal vezetője jogosult közvetlenül is összehívni a képviselő-testület ülését.</t>
+  </si>
+  <si>
+    <t>megadott</t>
+  </si>
+  <si>
+    <t>40. Melyik kifejezés hiányzik? A közmeghallgatás ________ ülésnek minősül, ezért azon a települési képviselő-testület tagjai határozatképes létszámban kötelesek megjelenni.</t>
+  </si>
+  <si>
+    <t>képviselő-testületi</t>
+  </si>
+  <si>
+    <t>41. Melyik kifejezés hiányzik? A HELYI NÉPSZAVAZÁS Helyi ________ minősül területi hatáskör alapján az a referendum, melyet egy településen vagy településrészen bonyolítanak le.</t>
+  </si>
+  <si>
+    <t>népszavazásnak</t>
+  </si>
+  <si>
+    <t>42. Melyik kifejezés hiányzik? Az önkormányzati ________ részletesen rendezi az első két területszervezési kérdés kezdeményezésének a feltételeit, a végleges döntés pedig a köztársasági elnök hatáskörébe tartozik.</t>
+  </si>
+  <si>
+    <t>törvény</t>
+  </si>
+  <si>
+    <t>43. Melyik kifejezés hiányzik? Természetesen a „________ felhasználás” elsősorban az önkormányzatok kötelező és fakultatív feladatainak ellátását jelenti, hiszen a vállalkozói tevékenység nem veszélyeztetheti ezek finanszírozását.</t>
+  </si>
+  <si>
+    <t>szabad</t>
+  </si>
+  <si>
+    <t>44. Melyik kifejezés hiányzik? Feladata a helyi ________ rendelkezésére álló források szabályszerű, gazdaságos, hatékony és eredményes felhasználásának ellenőrzése.</t>
+  </si>
+  <si>
+    <t>önkormányzat</t>
+  </si>
+  <si>
+    <t>45. Melyik kifejezés hiányzik? Ugyancsak ________ bevételnek minősül az adóbeszedés során kivetett bírságok és késedelmi pótlékok összege is.</t>
+  </si>
+  <si>
+    <t>osztott</t>
+  </si>
+  <si>
+    <t>46. Melyik kifejezés hiányzik? A fővárosi ________ és a kerületi önkormányzatokat megillető bevételek megosztási arányáról külön törvény rendelkezik.</t>
+  </si>
+  <si>
+    <t>önkormányzatot</t>
+  </si>
+  <si>
+    <t>47. Melyik kifejezés hiányzik? A nemzetiségi ________ használatába kell átadni a helyi önkormányzat tulajdonában levő, de a nemzetiségi önkormányzat feladatés hatásköre ellátásához szükséges vagyontárgyakat (pl. irodahelyiség).</t>
+  </si>
+  <si>
+    <t>48. Melyik kifejezés hiányzik? Ezzel biztosítja az adott szolgáltatáshoz való ________ hozzáférés lehetőségét és finanszírozását.</t>
+  </si>
+  <si>
+    <t>egyenlő</t>
+  </si>
+  <si>
+    <t>49. Melyik kifejezés hiányzik? Ha az ügyfél nem ________ eljárási képességgel, vagy ügyei vitelében akadályozott, képviseletet vehet igénybe.</t>
+  </si>
+  <si>
+    <t>50. Melyik kifejezés hiányzik? A támogató ________ jogosultsága azonban korlátozott, az általa támogatott személy helyett például nyilatkozattételre nem jogosult.</t>
+  </si>
+  <si>
+    <t>képviseleti</t>
+  </si>
+  <si>
+    <t>51. Melyik kifejezés hiányzik? AZ ÜGYFÉL JOGAI A ________ ELJÁRÁSBAN – Az ügyfél a következő főbb jogokkal rendelkezik az eljárás során.</t>
+  </si>
+  <si>
+    <t>HATÓSÁGI</t>
+  </si>
+  <si>
+    <t>52. Melyik kifejezés hiányzik? Az Ákr. biztosítja, hogy a közigazgatási eljárásban ________ szóban és írásban mindenki használhassa.</t>
+  </si>
+  <si>
+    <t>anyanyelvét</t>
+  </si>
+  <si>
+    <t>53. Melyik kifejezés hiányzik? Eljáró ________, mely esetben az érdemi döntés meghozatala a feladata.</t>
+  </si>
+  <si>
+    <t>hatóságként</t>
+  </si>
+  <si>
+    <t>54. Melyik kifejezés hiányzik? A hatáskör azt ________ meg, hogy egy ügyben milyen típusú és szintű szerv jogosult és egyben köteles döntést hozni.</t>
+  </si>
+  <si>
+    <t>mutatja</t>
+  </si>
+  <si>
+    <t>55. Melyik kifejezés hiányzik? Ezeket nem ________ határozatoknak nevezzük. a) Az egyszerűsített határozatokban a jogorvoslatra való figyelmeztetés és a határozat indokolása mellőzhető.</t>
+  </si>
+  <si>
+    <t>alakszerű</t>
+  </si>
+  <si>
+    <t>56. Melyik kifejezés hiányzik? Feladata, hogy az ________ tartózkodási helyét 15 napon belül lehetőség szerint felkutassa, és a határozatot számára átadja.</t>
+  </si>
+  <si>
+    <t>ügyfél</t>
+  </si>
+  <si>
+    <t>57. Melyik kifejezés hiányzik? A közigazgatási döntésekkel ________ jogorvoslatok típusai a következők: a) az ügyfél kérelme alapján kezdeményezett eljárások; b) a hivatalból lefolytatható döntés-felülvizsgálati eljárások.</t>
+  </si>
+  <si>
+    <t>összefüggő</t>
+  </si>
+  <si>
+    <t>58. Melyik kifejezés hiányzik? Ezeket a ________ egyedi ügyben hozott hatósági határozatoknak nevezzük.</t>
+  </si>
+  <si>
+    <t>döntéseket</t>
+  </si>
+  <si>
+    <t>59. Melyik kifejezés hiányzik? Az Ákr. rendelkezései szerint ________ joggal rendelkezik az ügyfél, valamint az, akire nézve a határozat rendelkezést tartalmaz.</t>
+  </si>
+  <si>
+    <t>fellebbezési</t>
+  </si>
+  <si>
+    <t>60. Melyik kifejezés hiányzik? A módosítás-visszavonási ________ lefolytatására a hatóság csak egy alkalommal, a határozat közlésétől számított egy éven belül jogosult.</t>
+  </si>
+  <si>
+    <t>eljárás</t>
+  </si>
+  <si>
+    <t>61. Melyik kifejezés hiányzik? A jog fogalma – A jog ________ funkciói • Konfliktusfeloldás • Reguláció • Integráció • Nevelő, szociális funkció • Hatalmi, ideológiai funkció 1.1.</t>
+  </si>
+  <si>
+    <t>társadalmi</t>
+  </si>
+  <si>
+    <t>62. Melyik kifejezés hiányzik? A jog fogalma – A jog ________ más normarendszerekhez Főbb társadalmi normarendszerek • Jog • Erkölcs • Szokás • Vallás 1.1.</t>
+  </si>
+  <si>
+    <t>viszonya</t>
+  </si>
+  <si>
+    <t>63. Melyik kifejezés hiányzik? A jog fogalma • ________ (jogalanyok) viselkedésére vonatkozó • az állam által alkotott, de /vagy/ legalább az állam által elismert és • az állam által végső soron kikényszerített • kötelező magatartási szabályok összessége.</t>
+  </si>
+  <si>
+    <t>személyek</t>
+  </si>
+  <si>
+    <t>64. Melyik kifejezés hiányzik? A jog fogalma – A ________ normarendszerek A társadalmi normák (normarendszerek) • célja az ismétlődő társadalmi jelenségek befolyásolása = szabályozás • előírják az általánosan követendőt és a helyesnek vélt magatartást • Közös sajátosságaik: a) Tartósság igénye: időben tartósan érvényesülnek.</t>
+  </si>
+  <si>
+    <t>65. Melyik kifejezés hiányzik? A jog fogalma – A jog ________ más normarendszerekhez Főbb társadalmi normarendszerek A vallás • A vallási norma, mint magatartásszabály általában a mindennapi életben beolvad a jogba, az erkölcsbe vagy a szokásba • Ezek közül valamelyik normájaként jelenik meg 1.1.</t>
+  </si>
+  <si>
+    <t>66. Melyik kifejezés hiányzik? A jog fogalma – A ________ szemben támasztott követelmények • Általános • Közzétett = nyilvános, megismerhető • Jövőbeli cselekvésre irányuló • Világos, egyértelmű • Ellentmondásmentes • Lehetségest követel • Bizonyos stabilitással rendelkezik • A kinyilvánított szabály és a hivatalos cselekvés egyezést mutat.</t>
+  </si>
+  <si>
+    <t>joggal</t>
+  </si>
+  <si>
+    <t>67. Melyik kifejezés hiányzik? Anyagi jogi norma – Alaki jogi norma (________ norma) 1.4 A jogviszony Fogalma: a jogviszony a jog által szabályozott társadalmi viszony.</t>
+  </si>
+  <si>
+    <t>eljárási</t>
+  </si>
+  <si>
+    <t>68. Melyik kifejezés hiányzik? A zálogjog, a ________ jogok. d) Kötelmi jog: szerződések közös szabályai (általános rész) és egyes szerződések (különös rész).</t>
+  </si>
+  <si>
+    <t>használati</t>
+  </si>
+  <si>
+    <t>69. Melyik kifejezés hiányzik? Kártérítési ________. e) Öröklési jog: a meghalt személy jogutódlása.</t>
+  </si>
+  <si>
+    <t>felelősség</t>
+  </si>
+  <si>
+    <t>70. Melyik kifejezés hiányzik? Végintézkedésen ________ és a törvényen alapuló öröklés rendje. f) A szellemi alkotások joga: szerzői jog (a szerző személyhez fűződő és vagyoni jogai).</t>
+  </si>
+  <si>
+    <t>alapuló</t>
+  </si>
+  <si>
+    <t>71. Melyik kifejezés hiányzik? Iparjogvédelem (________ megoldások, grafikailag ábrázolható jelzések alkotóinak jogai, szabadalmak, formatervezési minták, védjegyek).</t>
+  </si>
+  <si>
+    <t>műszaki</t>
+  </si>
+  <si>
+    <t>72. Melyik kifejezés hiányzik? 2.1 A jogforrások ________ és típusai M A G Y A R O R S Z Á G ALKOTMÁNYOZÁS Országgyűlés Alaptörvény I.</t>
+  </si>
+  <si>
+    <t>fogalma</t>
+  </si>
+  <si>
+    <t>73. Melyik kifejezés hiányzik? 2.1 A jogforrások ________ – a kormányrendelet Alaptörvény 15. cikk • (3) Feladatkörében eljárva a Kormány törvényben nem szabályozott tárgykörben, illetve törvényben kapott felhatalmazás alapján rendeletet alkot.</t>
+  </si>
+  <si>
+    <t>típusai</t>
+  </si>
+  <si>
+    <t>74. Melyik kifejezés hiányzik? A jogforrások ________ – MNB rendelet Alaptörvény 41. cikk (5) A Magyar Nemzeti Bank elnöke törvényben kapott felhatalmazás alapján, törvényben meghatározott feladatkörében rendeletet ad ki, amely törvénnyel nem lehet ellentétes.</t>
+  </si>
+  <si>
+    <t>75. Melyik kifejezés hiányzik? Alanyainak a ________ széles döntési jellemző. szabadságot biztosítanak.</t>
+  </si>
+  <si>
+    <t>jogszabályok</t>
+  </si>
+  <si>
+    <t>76. Melyik kifejezés hiányzik? A felek közös megegyezéssel el is ________ a jogszabályi rendelkezésektől, amíg valamilyen imperatív jellegű jogszabályba nem ütközik magatartásuk.</t>
+  </si>
+  <si>
+    <t>térhetnek</t>
+  </si>
+  <si>
+    <t>77. Melyik kifejezés hiányzik? 2.1 A jogforrások ________ – A közjogi szervezetszabályozó eszközök A jogalkotásról szóló 2010. évi CXXX. törvény (Jat.) 1. § (1) bek.</t>
+  </si>
+  <si>
+    <t>78. Melyik kifejezés hiányzik? E törvény ________ a) a jogszabályokra, valamint b) a normatív határozatra és normatív utasításra (a továbbiakban együtt: közjogi szervezetszabályozó eszköz) terjed ki.</t>
+  </si>
+  <si>
+    <t>hatálya</t>
+  </si>
+  <si>
+    <t>79. Melyik kifejezés hiányzik? A közjogi ________ eszközben jogszabály rendelkezése nem ismételhető meg.</t>
+  </si>
+  <si>
+    <t>szervezetszabályozó</t>
+  </si>
+  <si>
+    <t>80. Melyik kifejezés hiányzik? 2.1 A jogforrások – Az EU jog ________ • A közösségi jog – sui generis jogrend = különbözik a tagállamok jogrendszerétől és a nemzetközi közjogtól.</t>
+  </si>
+  <si>
+    <t>forrásai</t>
+  </si>
+  <si>
+    <t>81. Melyik kifejezés hiányzik? A közösségi ________ nemcsak a tagállamok, hanem az uniós természetes és jogi személyek is alanyai.</t>
+  </si>
+  <si>
+    <t>jognak</t>
+  </si>
+  <si>
+    <t>82. Melyik kifejezés hiányzik? Mikortól? – ________ lépés • A jogszabály saját maga határozza meg • Más jogszabály határozza meg Meddig?</t>
+  </si>
+  <si>
+    <t>hatályba</t>
+  </si>
+  <si>
+    <t>83. Melyik kifejezés hiányzik? 2.2 A jogszabályok ________ A jogszabály hatálya - a jogszabály alkalmazhatósága.</t>
+  </si>
+  <si>
+    <t>84. Melyik kifejezés hiányzik? Négy típusa a) ________ (földrajzi) hatály b) személyi (alanyi) hatály c) Időbeli hatály d) tárgyi hatály (alkalmazási kör). - Jat.</t>
+  </si>
+  <si>
+    <t>területi</t>
+  </si>
+  <si>
+    <t>85. Melyik kifejezés hiányzik? Fejezet 2.2 A ________ hatálya - A jogszabály területi hatálya – Hol kell/lehet alkalmazni?</t>
+  </si>
+  <si>
+    <t>86. Melyik kifejezés hiányzik? Helyi jogszabályok - Jat 6. § (1) – • A ________ területi hatálya Magyarország területére, az önkormányzati rendelet területi hatálya a helyi önkormányzat közigazgatási területére terjed ki.</t>
+  </si>
+  <si>
+    <t>jogszabály</t>
+  </si>
+  <si>
+    <t>87. Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma Az állam ________ (Georg Jellinek – Általános államtan) – az állam közjogi fogalmának ismérvei – az államiság feltételei: 1.</t>
+  </si>
+  <si>
+    <t>88. Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma – ________ Államforma – Kormányforma - Államszerkezet • Államforma – a közhatalom gyakorlásának módja 1.</t>
+  </si>
+  <si>
+    <t>Államforma</t>
+  </si>
+  <si>
+    <t>89. Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma - ________ Kormányforma – a törvényhozó és végrehajtó hatalom viszonya, a kormányzati hatalom gyakorlása 1.</t>
+  </si>
+  <si>
+    <t>kormányforma</t>
+  </si>
+  <si>
+    <t>90. Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma - ________ népesség - állampolgárság Állampolgárság szabályozási kérdései - Keletkezés 1.</t>
+  </si>
+  <si>
+    <t>Államalkotó</t>
+  </si>
+  <si>
+    <t>91. Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma - Az állam ________ Államszervezet – egy adott állam szerveinek összessége, amely révén az állam gyakorolja hatalmát, teljesíti céljait, ellátja feladatait.</t>
+  </si>
+  <si>
+    <t>szervezete</t>
+  </si>
+  <si>
+    <t>92. Melyik kifejezés hiányzik? A tisztviselő ________ annak a döntésnek a hatékony végrehajtása, amit a politikus hozott /Woodrow Wilson/ = a kormányzás és a közigazgatás szétválasztása.</t>
+  </si>
+  <si>
+    <t>93. Melyik kifejezés hiányzik? A közigazgatás ________ Negatív fogalommeghatározás : mi nem a közigazgatás? • Magáncselekvések – Közcselekvések - Az igazgatási tevékenység (szervezeti tevékenység) végezhető magán (pl. üzleti) és állami szervezeti keretek között (= közigazgatás) • Közcselekvések, ami nem közigazgatás - törvényalkotás - igazságszolgáltatás - politika - kormányzás 1.</t>
+  </si>
+  <si>
+    <t>94. Melyik kifejezés hiányzik? A közigazgatás ________ Negatív definíció A közigazgatás: az állam saját jogrendjének uralma alatt végbemenő azon állami ténykedés, amely az igazságszolgáltatás céljaitól különböző összes egyéb állami cél megvalósítását szolgálja. – Otto Mayer /1846 – 1924/ 1.</t>
+  </si>
+  <si>
+    <t>95. Melyik kifejezés hiányzik? A közigazgatási jog fogalma és ________ Közjog (pl.) Magánjog (pl.) Alkotmányjog Polgári jog Közigazgatási jog Családjog Pénzügyi jog Kereskedelmi (gazdasági) Büntetőjog jog Büntetővégrehajtási jog Eljárásjogok Vegyes jogágak (pl.): munkajog, agrárjog 2.</t>
+  </si>
+  <si>
+    <t>jellemzői</t>
+  </si>
+  <si>
+    <t>96. Melyik kifejezés hiányzik? A közigazgatási jog fogalma és ________ – a közigazgatási jog forrásai • Alaptörvény (?) • Törvények - A közigazgatás szervezete Jellemző: - Eljárási törvények • Rendeleti jog túlsúlya - Ágazati törvények • Nem jogszabályi jog • Rendeletek túlsúlya - Eredeti • Heterogenitás - Származékos - Önkormányzati rendeletek (!) • Alacsonyabb szintű jogforrások 3.</t>
+  </si>
+  <si>
+    <t>97. Melyik kifejezés hiányzik? A közigazgatás, mint ________ 4.2 Közigazgatási szerv, közigazgatási szervezet A szervezetrendszer • A jogi szabályozás sem a szervezetrendszer, sem a rendszer fogalmát nem határozza meg.</t>
+  </si>
+  <si>
+    <t>szervezet</t>
+  </si>
+  <si>
+    <t>98. Melyik kifejezés hiányzik? A közigazgatás, mint ________ 4.2 Közigazgatási szerv, közigazgatási szervezet • A közigazgatási szerv önállósága (jogi értelemben) = jogosult önállóan cselekedni. • Az önálló cselekvést az önálló hatáskör teszi lehetővé.</t>
+  </si>
+  <si>
+    <t>99. Melyik kifejezés hiányzik? A rendszer ________ fogalma: egymással funkcionálisan kapcsolatban álló, a környezettől e kapcsolatok és a kapcsolatrendszernek a környezet számára végzett funkciója által elhatároltható elemek összessége. • A közigazgatás szervezet és egyben rendszer. • Szervezetként az államszervezet része.</t>
+  </si>
+  <si>
+    <t>szociológiai</t>
+  </si>
+  <si>
+    <t>100. Melyik kifejezés hiányzik? Szakmai ________ elvek 2.1 Különös hatáskör – általános hatáskör 2.2 Ágazati elv – funkcionális elv 3.</t>
+  </si>
+  <si>
+    <t>munkamegosztási</t>
+  </si>
+  <si>
+    <t>101. Melyik kifejezés hiányzik? Rendszerként az állam ________ a része. • A közigazgatás viszonylag önállónak nevezhető rendszerekből áll (a közigazgatás alrendszerei).</t>
+  </si>
+  <si>
+    <t>szervezetrendszerének</t>
+  </si>
+  <si>
+    <t>102. Melyik kifejezés hiányzik? Jogi személyiséggel nem rendelkező ________ Akkor képes jogokat szerezni és kötelezettségeket vállalni, ha jogszabály így rendelkezik = polgári jogi jogalanyisággal ruházza fel.</t>
+  </si>
+  <si>
+    <t>103. Melyik kifejezés hiányzik? 7. § (1) bek. • Minden közigazgatási szerv, amely ________ szerv, egyúttal polgárjogi jogi személyiséggel is rendelkezik, de nem minden közigazgatási szerv költségvetési szerv 2.2 2.2 Egyéb: külön – általában az adott szervet létrehozó - jogszabály rendelkezhet arról, hogy egy szerv polgárjogi jogi személy. - Pl.</t>
+  </si>
+  <si>
+    <t>költségvetési</t>
+  </si>
+  <si>
+    <t>104. Melyik kifejezés hiányzik? A közigazgatási jog alanyai - Kinek, ________ a magatartását szabályozza a jog?</t>
+  </si>
+  <si>
+    <t>kiknek</t>
+  </si>
+  <si>
+    <t>105. Melyik kifejezés hiányzik? A közigazgatási jog alanyai Cél: a közigazgatási jog ________ a megismertetése Közigazgatási jogi jogalanyiság Polgári jogi jogalanyiság 6.</t>
+  </si>
+  <si>
+    <t>alanyainak</t>
+  </si>
+  <si>
+    <t>106. Melyik kifejezés hiányzik? Az ember, mint jogalany ________ személy „Minden ember jogképes: jogai és kötelezettségei lehetnek.” – Ptk.</t>
+  </si>
+  <si>
+    <t>természetes</t>
+  </si>
+  <si>
+    <t>107. Melyik kifejezés hiányzik? A szervezeti jog ________: viszonylag elkülönült joganyag a közigazgatási jogon belül, a közigazgatási jog egyik részterülete.</t>
+  </si>
+  <si>
+    <t>108. Melyik kifejezés hiányzik? Település • Az ________ területe településekre tagozódik. • Az ország teljes területe, valamennyi pontja közigazgatásilag egy (valamely) településhez tartozik, ami lehet - község, ezen belül nagyközség [Mötv.</t>
+  </si>
+  <si>
+    <t>ország</t>
+  </si>
+  <si>
+    <t>109. Melyik kifejezés hiányzik? A közigazgatás ________ joga A közigazgatási szerveket és szervezetüket, valamint feladatés hatáskörüket a jogi szabályozás, elsősorban jogszabályok hozzák létre és alakítják.</t>
+  </si>
+  <si>
+    <t>szervezeti</t>
+  </si>
+  <si>
+    <t>110. Melyik kifejezés hiányzik? A közigazgatás ________ joga szabályozza a közigazgatási szervek formáit, a szervek belső felépítésének rendjét, külső – akár a közigazgatáson belüli, akár a közigazgatáson kívüli – kapcsolati rendszerét.</t>
+  </si>
+  <si>
+    <t>111. Melyik kifejezés hiányzik? A közigazgatás ________ joga A közigazgatás szervezetrendszerét meghatározó joganyag A közigazgatási szervek csoportosítása szervezeti jogi szempontból A közigazgatás két nagy alrendszere: 1.</t>
+  </si>
+  <si>
+    <t>112. Melyik kifejezés hiányzik? A 2012. szeptember 1-jén ________ lépett nemzeti felsőoktatásról szóló törvény biztosítja az intézményalapítás szabadságát.</t>
+  </si>
+  <si>
+    <t>113. Melyik kifejezés hiányzik? A rektor ________ és képviseli az intézményt, egyben a szenátus elnöke is, így hatásköre a szenátus döntéseinek előkészítésére és végrehajtására is kiterjed.</t>
+  </si>
+  <si>
+    <t>vezeti</t>
+  </si>
+  <si>
+    <t>114. Melyik kifejezés hiányzik? A kancellár ________ és felmentésére a miniszterelnök jogosult.</t>
+  </si>
+  <si>
+    <t>megbízására</t>
+  </si>
+  <si>
+    <t>115. Melyik kifejezés hiányzik? A kancellári ________ e döntések érvényességének, illetve hatálybalépésének feltétele, tehát a kancellár széleskörű vétójoggal rendelkezik egyes döntések meghozatala során.</t>
+  </si>
+  <si>
+    <t>egyetértés</t>
+  </si>
+  <si>
+    <t>116. Melyik kifejezés hiányzik? Az igazgatási ________ a szervezetek (köztük a közigazgatási szerveknek is) olyan tudatos, tervszerű tevékenysége, amely biztosítja a szervezet céljainak eléréséhez szükséges személyi és dologi feltételeket, valamint a munka összhangját.</t>
+  </si>
+  <si>
+    <t>tevékenység</t>
+  </si>
+  <si>
+    <t>117. Melyik kifejezés hiányzik? KÖZIGAZGATÁSI SZERV ÖNÁLLÓ ________ EGYSÉGE – A közigazgatási szerv önálló szervezeti egysége ezzel szemben kizárólag közigazgatási jogképességgel rendelkezik, azaz önálló feladatköre van, amelynek részeként döntéseket hozhat, és azok betartatására nézve intézkedéseket tehet.</t>
+  </si>
+  <si>
+    <t>SZERVEZETI</t>
+  </si>
+  <si>
+    <t>118. Melyik kifejezés hiányzik? Ez utóbbi ________ ún. utólagos normakontroll eljárás indítványozására jogosult. (B) ÁLLAMI SZÁMVEVŐSZÉK – Az ÁSZ kizárólag az Országgyűlésnek alárendelt legfőbb pénzügyi ellenőrző szerv, ellenőrzéseit célszerűségi, eredményességi és törvényességi szempontok szerint végzi.</t>
+  </si>
+  <si>
+    <t>esetben</t>
+  </si>
+  <si>
+    <t>119. Melyik kifejezés hiányzik? A közigazgatási ügyekben ________ bíróságok hatásköre arra terjed ki, hogy az ügyfél keresete alapján megvizsgálják egy egyedi hatósági ügyben hozott közigazgatási határozat (döntés) jogszerűségét, és törvénysértés esetén megsemmisítsék vagy megváltoztassák azt.</t>
+  </si>
+  <si>
+    <t>eljáró</t>
+  </si>
+  <si>
+    <t>120. Melyik kifejezés hiányzik? Az Önkormányzati ________ jogosult az önkormányzat képviselő-testülete (közgyűlése) által elfogadott rendeletet megsemmisíteni, ha az magasabb szintű jogszabállyal ellentétes, vagy megállapíthatja a helyi önkormányzat jogalkotási kötelezettségének elmulasztását is.</t>
+  </si>
+  <si>
+    <t>Tanács</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -793,15 +1444,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -828,14 +1470,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1127,10 +1765,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1147,7 +1785,7 @@
         <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1155,7 +1793,7 @@
         <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1163,7 +1801,7 @@
         <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1171,7 +1809,7 @@
         <v>121</v>
       </c>
       <c r="B6" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1179,7 +1817,7 @@
         <v>123</v>
       </c>
       <c r="B7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1187,7 +1825,7 @@
         <v>164</v>
       </c>
       <c r="B8" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1219,7 +1857,7 @@
         <v>131</v>
       </c>
       <c r="B12" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1243,7 +1881,7 @@
         <v>204</v>
       </c>
       <c r="B15" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1251,7 +1889,7 @@
         <v>202</v>
       </c>
       <c r="B16" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1259,7 +1897,7 @@
         <v>200</v>
       </c>
       <c r="B17" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1267,7 +1905,7 @@
         <v>198</v>
       </c>
       <c r="B18" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1331,7 +1969,7 @@
         <v>135</v>
       </c>
       <c r="B26" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1339,7 +1977,7 @@
         <v>155</v>
       </c>
       <c r="B27" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1347,7 +1985,7 @@
         <v>153</v>
       </c>
       <c r="B28" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1355,7 +1993,7 @@
         <v>133</v>
       </c>
       <c r="B29" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -1363,7 +2001,7 @@
         <v>155</v>
       </c>
       <c r="B30" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -1371,7 +2009,7 @@
         <v>153</v>
       </c>
       <c r="B31" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1379,7 +2017,7 @@
         <v>145</v>
       </c>
       <c r="B32" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -1387,7 +2025,7 @@
         <v>143</v>
       </c>
       <c r="B33" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -1395,7 +2033,7 @@
         <v>139</v>
       </c>
       <c r="B34" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -1403,7 +2041,7 @@
         <v>141</v>
       </c>
       <c r="B35" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1411,7 +2049,7 @@
         <v>147</v>
       </c>
       <c r="B36" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1419,7 +2057,7 @@
         <v>149</v>
       </c>
       <c r="B37" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -1427,7 +2065,7 @@
         <v>151</v>
       </c>
       <c r="B38" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -1435,7 +2073,7 @@
         <v>137</v>
       </c>
       <c r="B39" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -1443,7 +2081,7 @@
         <v>109</v>
       </c>
       <c r="B40" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -1451,7 +2089,7 @@
         <v>107</v>
       </c>
       <c r="B41" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -1459,7 +2097,7 @@
         <v>105</v>
       </c>
       <c r="B42" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -1467,7 +2105,7 @@
         <v>103</v>
       </c>
       <c r="B43" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -1475,7 +2113,7 @@
         <v>101</v>
       </c>
       <c r="B44" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -1483,7 +2121,7 @@
         <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -1491,7 +2129,7 @@
         <v>97</v>
       </c>
       <c r="B46" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -1499,7 +2137,7 @@
         <v>95</v>
       </c>
       <c r="B47" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -1507,7 +2145,7 @@
         <v>93</v>
       </c>
       <c r="B48" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -1515,7 +2153,7 @@
         <v>91</v>
       </c>
       <c r="B49" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -1523,7 +2161,7 @@
         <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -1531,7 +2169,7 @@
         <v>88</v>
       </c>
       <c r="B51" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -1539,7 +2177,7 @@
         <v>86</v>
       </c>
       <c r="B52" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -1547,7 +2185,7 @@
         <v>84</v>
       </c>
       <c r="B53" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -1555,7 +2193,7 @@
         <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -1563,7 +2201,7 @@
         <v>80</v>
       </c>
       <c r="B55" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -2434,27 +3072,980 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB7746A-7A09-4035-BC86-847147D175BE}">
-  <dimension ref="A1:B2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2545C15C-6CAE-4C6C-B385-58D367835720}">
+  <dimension ref="A1:B121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="B1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>206</v>
+        <v>247</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B5" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>256</v>
+      </c>
+      <c r="B6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>258</v>
+      </c>
+      <c r="B7" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>260</v>
+      </c>
+      <c r="B8" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>264</v>
+      </c>
+      <c r="B10" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>266</v>
+      </c>
+      <c r="B11" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>270</v>
+      </c>
+      <c r="B13" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>272</v>
+      </c>
+      <c r="B14" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>274</v>
+      </c>
+      <c r="B15" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>276</v>
+      </c>
+      <c r="B16" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>278</v>
+      </c>
+      <c r="B17" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>280</v>
+      </c>
+      <c r="B18" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>282</v>
+      </c>
+      <c r="B19" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>284</v>
+      </c>
+      <c r="B20" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>286</v>
+      </c>
+      <c r="B21" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>288</v>
+      </c>
+      <c r="B22" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>290</v>
+      </c>
+      <c r="B23" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>292</v>
+      </c>
+      <c r="B24" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>294</v>
+      </c>
+      <c r="B25" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>296</v>
+      </c>
+      <c r="B26" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>298</v>
+      </c>
+      <c r="B27" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>300</v>
+      </c>
+      <c r="B28" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>302</v>
+      </c>
+      <c r="B29" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>304</v>
+      </c>
+      <c r="B30" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>306</v>
+      </c>
+      <c r="B31" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>308</v>
+      </c>
+      <c r="B32" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>310</v>
+      </c>
+      <c r="B33" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>312</v>
+      </c>
+      <c r="B34" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>313</v>
+      </c>
+      <c r="B35" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>315</v>
+      </c>
+      <c r="B36" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>317</v>
+      </c>
+      <c r="B37" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>319</v>
+      </c>
+      <c r="B38" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>321</v>
+      </c>
+      <c r="B39" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>322</v>
+      </c>
+      <c r="B40" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>324</v>
+      </c>
+      <c r="B41" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>326</v>
+      </c>
+      <c r="B42" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>328</v>
+      </c>
+      <c r="B43" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>330</v>
+      </c>
+      <c r="B44" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>332</v>
+      </c>
+      <c r="B45" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>334</v>
+      </c>
+      <c r="B46" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>336</v>
+      </c>
+      <c r="B47" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>338</v>
+      </c>
+      <c r="B48" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>339</v>
+      </c>
+      <c r="B49" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>341</v>
+      </c>
+      <c r="B50" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>342</v>
+      </c>
+      <c r="B51" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>344</v>
+      </c>
+      <c r="B52" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>346</v>
+      </c>
+      <c r="B53" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>348</v>
+      </c>
+      <c r="B54" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>350</v>
+      </c>
+      <c r="B55" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>352</v>
+      </c>
+      <c r="B56" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>354</v>
+      </c>
+      <c r="B57" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>356</v>
+      </c>
+      <c r="B58" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>358</v>
+      </c>
+      <c r="B59" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>360</v>
+      </c>
+      <c r="B60" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>362</v>
+      </c>
+      <c r="B61" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>364</v>
+      </c>
+      <c r="B62" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>366</v>
+      </c>
+      <c r="B63" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>368</v>
+      </c>
+      <c r="B64" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>370</v>
+      </c>
+      <c r="B65" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>371</v>
+      </c>
+      <c r="B66" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>372</v>
+      </c>
+      <c r="B67" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>374</v>
+      </c>
+      <c r="B68" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>376</v>
+      </c>
+      <c r="B69" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>378</v>
+      </c>
+      <c r="B70" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>380</v>
+      </c>
+      <c r="B71" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>382</v>
+      </c>
+      <c r="B72" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>384</v>
+      </c>
+      <c r="B73" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>386</v>
+      </c>
+      <c r="B74" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>388</v>
+      </c>
+      <c r="B75" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>389</v>
+      </c>
+      <c r="B76" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>391</v>
+      </c>
+      <c r="B77" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>393</v>
+      </c>
+      <c r="B78" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>394</v>
+      </c>
+      <c r="B79" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>396</v>
+      </c>
+      <c r="B80" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>398</v>
+      </c>
+      <c r="B81" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>400</v>
+      </c>
+      <c r="B82" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>402</v>
+      </c>
+      <c r="B83" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>404</v>
+      </c>
+      <c r="B84" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>405</v>
+      </c>
+      <c r="B85" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>407</v>
+      </c>
+      <c r="B86" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>408</v>
+      </c>
+      <c r="B87" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>410</v>
+      </c>
+      <c r="B88" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>411</v>
+      </c>
+      <c r="B89" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>413</v>
+      </c>
+      <c r="B90" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>415</v>
+      </c>
+      <c r="B91" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>417</v>
+      </c>
+      <c r="B92" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>419</v>
+      </c>
+      <c r="B93" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>420</v>
+      </c>
+      <c r="B94" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>421</v>
+      </c>
+      <c r="B95" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>422</v>
+      </c>
+      <c r="B96" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>424</v>
+      </c>
+      <c r="B97" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>425</v>
+      </c>
+      <c r="B98" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>427</v>
+      </c>
+      <c r="B99" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>428</v>
+      </c>
+      <c r="B100" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>430</v>
+      </c>
+      <c r="B101" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>432</v>
+      </c>
+      <c r="B102" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>434</v>
+      </c>
+      <c r="B103" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>435</v>
+      </c>
+      <c r="B104" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>437</v>
+      </c>
+      <c r="B105" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>439</v>
+      </c>
+      <c r="B106" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>441</v>
+      </c>
+      <c r="B107" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>443</v>
+      </c>
+      <c r="B108" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>444</v>
+      </c>
+      <c r="B109" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>446</v>
+      </c>
+      <c r="B110" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>448</v>
+      </c>
+      <c r="B111" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>449</v>
+      </c>
+      <c r="B112" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>450</v>
+      </c>
+      <c r="B113" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>451</v>
+      </c>
+      <c r="B114" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>453</v>
+      </c>
+      <c r="B115" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>455</v>
+      </c>
+      <c r="B116" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>457</v>
+      </c>
+      <c r="B117" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>459</v>
+      </c>
+      <c r="B118" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>461</v>
+      </c>
+      <c r="B119" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>463</v>
+      </c>
+      <c r="B120" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>465</v>
+      </c>
+      <c r="B121" t="s">
+        <v>466</v>
       </c>
     </row>
   </sheetData>

--- a/studyflow.xlsx
+++ b/studyflow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\puszt\Downloads\StudyFlow_GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C387F54-345E-4744-A4CB-8507942009FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2E0468-DDDA-409F-B301-982C9A755A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10.26." sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="467">
   <si>
     <t>pantry</t>
   </si>
@@ -2211,13 +2211,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:B109"/>
+  <dimension ref="A1:B109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B1" t="s">
+        <v>206</v>
+      </c>
+    </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>

--- a/studyflow.xlsx
+++ b/studyflow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\puszt\Downloads\StudyFlow_GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2E0468-DDDA-409F-B301-982C9A755A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCA89EA-EAF3-48B6-8C12-57B9D04F8487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10.26." sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="463">
   <si>
     <t>pantry</t>
   </si>
@@ -644,12 +644,6 @@
     <t>párbaj</t>
   </si>
   <si>
-    <t>magyar</t>
-  </si>
-  <si>
-    <t>angol</t>
-  </si>
-  <si>
     <t xml:space="preserve">absence </t>
   </si>
   <si>
@@ -767,667 +761,661 @@
     <t xml:space="preserve">repeatedly </t>
   </si>
   <si>
-    <t>Kérdés</t>
-  </si>
-  <si>
-    <t>Helyes válasz</t>
-  </si>
-  <si>
-    <t>1. Melyik kifejezés hiányzik? Ennek központi ________ a munkamegosztás, mely a közigazgatási szervek által elvégzendő feladatok és az ellátásukra hivatott szervezetek tagolását jelenti.</t>
-  </si>
-  <si>
     <t>kategóriája</t>
   </si>
   <si>
-    <t>2. Melyik kifejezés hiányzik? A NAV hatásköre ________ kiterjed az adóhátralék bankszámláról történő letiltására, adóbírság kivetésére.</t>
-  </si>
-  <si>
     <t>például</t>
   </si>
   <si>
-    <t>3. Melyik kifejezés hiányzik? Jegyezzük meg jól tehát, hogy ________ nélkül egy közigazgatási szerv feladatait nem képes hatékonyan ellátni!  Az illetékesség az adott hatóság földrajzi értelemben vett működési területét határozza meg.</t>
-  </si>
-  <si>
     <t>hatáskör</t>
   </si>
   <si>
-    <t>4. Melyik kifejezés hiányzik? A KÖZIGAZGATÁSI SZERV MUNKASZERVEZETE A közigazgatási ________ jellemzője önálló munkaszervezet, hivatal működtetése, amelynek élén egyszemélyi felelős vezető (hivatalvezető) áll.</t>
-  </si>
-  <si>
     <t>szervek</t>
   </si>
   <si>
-    <t>5. Melyik kifejezés hiányzik? A közintézetek ________ mindenekelőtt a tulajdonosi jogokat gyakorló (alapító) fenntartóval szemben biztosítja a jogi szabályozás.</t>
-  </si>
-  <si>
     <t>autonómiáját</t>
   </si>
   <si>
-    <t>6. Melyik kifejezés hiányzik? Ezáltal a ________ hatásköre lesz a szolgáltatási jogviszony keretében az intézeti ellátottal összefüggésben döntéseket hozni, és ezek végrehatásáról gondoskodni.</t>
-  </si>
-  <si>
     <t>közintézetnek</t>
   </si>
   <si>
-    <t>7. Melyik kifejezés hiányzik? Ezen belül a vezetőknek is ________ további vezetői és a beosztottaknak is lehetnek beosztottjaik, ugyanakkor aki nem vezető és nem beosztott, az nem tartozik a rendszerbe: kívülálló (ilyen például az ügyfél).</t>
-  </si>
-  <si>
     <t>lehetnek</t>
   </si>
   <si>
-    <t>8. Melyik kifejezés hiányzik? A centralizáció mint ________ azt jelenti, hogy egy meghatározott szerv a közigazgatás szervezetének csúcsán helyezkedik el, s az irányítás innen történik.</t>
-  </si>
-  <si>
     <t>központosítás</t>
   </si>
   <si>
-    <t>9. Melyik kifejezés hiányzik? A kirendeltség nem ________ önálló feladatés hatáskörrel rendelkező területi szervnek, csak az adott hatóság területileg kihelyezett belső szervezeti egységének.</t>
-  </si>
-  <si>
     <t>minősül</t>
   </si>
   <si>
-    <t>10. Melyik kifejezés hiányzik? Az integráció ________, a részeknek egymáshoz illeszkedését jelenti, bizonyos értelemben a közigazgatás hierarchikusságát és centralizáltságát finomító, működését egységesítő elv.</t>
-  </si>
-  <si>
     <t>egységesülést</t>
   </si>
   <si>
-    <t>11. Melyik kifejezés hiányzik? B) IRÁNYÍTÁS – Az ________ hierarchikus, alá-fölérendeltségi kapcsolatban álló közigazgatási szervek közötti hatalmi viszonyt irányításnak nevezzük.</t>
-  </si>
-  <si>
     <t>egymással</t>
   </si>
   <si>
-    <t>12. Melyik kifejezés hiányzik? Az ellenőrzési ________ önálló gyakorlására nemcsak szervek közötti ún. belső viszonyban, hanem közigazgatási szerv és ügyfél között is találunk példákat (ezt nevezzük külső ellenőrzésnek).</t>
-  </si>
-  <si>
     <t>funkció</t>
   </si>
   <si>
-    <t>13. Melyik kifejezés hiányzik? Megjegyezzük, hogy egyes ________ feladatok ellátása csak névlegesen valósul meg járási szinten, ugyanis számos ügykörben nem minden járási hivatal rendelkezik hatáskörrel.</t>
-  </si>
-  <si>
     <t>hatósági</t>
   </si>
   <si>
-    <t>14. Melyik kifejezés hiányzik? A HELYI SZINT Magyarország ________ a települések típusai a következők: község, nagyközség, város, járásszékhely város, megyei jogú város, főváros és 23 kerülete.</t>
-  </si>
-  <si>
     <t>területén</t>
   </si>
   <si>
-    <t>15. Melyik kifejezés hiányzik? Magyarországon – sok más ________ államhoz hasonlóan – a közigazgatásinak tekinthető feladatokat alapvetően az állam két szervezeti alrendszere, államigazgatási és önkormányzati szervek valósítják meg.</t>
-  </si>
-  <si>
     <t>európai</t>
   </si>
   <si>
-    <t>16. Melyik kifejezés hiányzik? Ebben a részben ________ az egyes alrendszerek működésének főbb kapcsolódási pontjait.</t>
-  </si>
-  <si>
     <t>áttekintjük</t>
   </si>
   <si>
-    <t>17. Melyik kifejezés hiányzik? Lényeges elem ________ a szolgáltató jellegű közigazgatás számára az ügyfél-közeliség érvényesülése.</t>
-  </si>
-  <si>
     <t>ugyanis</t>
   </si>
   <si>
-    <t>18. Melyik kifejezés hiányzik? A középszinten belül a ________ igazgatás párhuzamos felépítésű, azaz önkormányzati és államigazgatási szervek egyaránt megtalálhatóak.</t>
-  </si>
-  <si>
     <t>megyei</t>
   </si>
   <si>
-    <t>19. Melyik kifejezés hiányzik? Miniszterelnöknek ________ minden olyan személy, aki  büntetlen előéletű,  rendelkezik magyar állampolgársággal, és  az országgyűlési képviselők választásán passzív választójoga van (azaz választható).</t>
-  </si>
-  <si>
     <t>javasolható</t>
   </si>
   <si>
-    <t>20. Melyik kifejezés hiányzik? Ez azt jelenti, hogy a kormányon belül csak a ________ az Országgyűlés által közvetlenül választott politikai vezető, vagyis a miniszterelnöknek van kormánya, nem pedig a kormánynak miniszterelnöke.</t>
-  </si>
-  <si>
     <t>miniszterelnök</t>
   </si>
   <si>
-    <t>21. Melyik kifejezés hiányzik? A miniszter a ________ előírt feladatés hatáskörében önállóan jár el, és ezért felelősséggel tartozik (pl. az Országgyűlésben interpellálható).</t>
-  </si>
-  <si>
     <t>jogszabályban</t>
   </si>
   <si>
-    <t>22. Melyik kifejezés hiányzik? Ez azt jelenti, hogy a miniszterelnök ________ függ, elfogadja-e azt, vagy sem.</t>
-  </si>
-  <si>
     <t>mérlegelésétől</t>
   </si>
   <si>
-    <t>23. Melyik kifejezés hiányzik? A szakpolitikai ________ feladata az adott minisztériumhoz tartozó egyes szakterületi érdekek érvényesítése.</t>
-  </si>
-  <si>
     <t>államtitkárok</t>
   </si>
   <si>
-    <t>24. Melyik kifejezés hiányzik? A járási ________ az a büntetlen előéletű, cselekvőképes és nagykorú magyar állampolgár nevezhető ki, aki felsőfokú végzettséggel és legalább 5 év közigazgatási gyakorlattal rendelkezik.</t>
-  </si>
-  <si>
     <t>hivatalvezetőnek</t>
   </si>
   <si>
-    <t>25. Melyik kifejezés hiányzik? A bizalomvesztés miatt ________ tisztviselő jogosult végkielégítésre és 2 hónap felmentési idő letöltésére. c) Alkalmatlanság.</t>
-  </si>
-  <si>
     <t>felmentett</t>
   </si>
   <si>
-    <t>26. Melyik kifejezés hiányzik? Vannak ________ a közigazgatásban, akik elvileg különböző területeken is képesek megállni a helyüket, őket nevezzük generalistáknak, ellentétben az egy területre szakosodott specialistákkal.</t>
-  </si>
-  <si>
     <t>tisztviselők</t>
   </si>
   <si>
-    <t>27. Melyik kifejezés hiányzik? Ebbe a körbe tartozik a politikai ________ és főtanácsadók fizetésének megállapítása a központi államigazgatásban.  Vezetői munkakörök létesítése.</t>
-  </si>
-  <si>
     <t>tanácsadók</t>
   </si>
   <si>
-    <t>28. Melyik kifejezés hiányzik? A fokozott ________ abban áll, hogy több bűncselekmény, mint például az emberölés vagy az emberrablás súlyosabban minősül, ha hivatalos személy sérelmére követik el.</t>
-  </si>
-  <si>
     <t>védelem</t>
   </si>
   <si>
-    <t>29. Melyik kifejezés hiányzik? Azt jelenti, hogy a beosztott ________ a vezető által vallott értékekkel, célokkal, és munkáját ezek alapján végzi.</t>
-  </si>
-  <si>
     <t>azonosul</t>
   </si>
   <si>
-    <t>30. Melyik kifejezés hiányzik? A törvény úgy ________, hogy a tisztviselő köteles felettese utasításait végrehajtani.</t>
-  </si>
-  <si>
     <t>rendelkezik</t>
   </si>
   <si>
-    <t>31. Melyik kifejezés hiányzik? TÖRVÉNYESSÉGI ________ JOGKÖRÖK – A megyei kormányhivatal vezetőjének feladata a helyi és nemzetiségi önkormányzatok törvényességi felügyelete.</t>
-  </si>
-  <si>
     <t>FELÜGYELETI</t>
   </si>
   <si>
-    <t>32. Melyik kifejezés hiányzik? Ezen felül speciális ________ minősül a főváros, ahol a koncentrált lakosságszám miatt kerületi hivatalok alakultak.</t>
-  </si>
-  <si>
     <t>járásnak</t>
   </si>
   <si>
-    <t>33. Melyik kifejezés hiányzik? Ilyen szervnek ________ a Gazdasági Versenyhivatal Versenytanácsa, vagy a Közbeszerzési Döntőbizottság.</t>
-  </si>
-  <si>
-    <t>34. Melyik kifejezés hiányzik? Ilyen a Nemzeti ________ Testület (feladata a Magyar Szabványok /MSZ/ előírásainak meghatározása és közzététele).</t>
-  </si>
-  <si>
     <t>Szabványügyi</t>
   </si>
   <si>
-    <t>35. Melyik kifejezés hiányzik? A gazdasági ________ feladata, hogy előmozdítsák a gazdaság fejlődését és szerveződését, a piaci magatartás tisztességét, a gazdasági tevékenységet folytatók általános, együttes érdekeinek érvényesítését.</t>
-  </si>
-  <si>
     <t>kamarák</t>
   </si>
   <si>
-    <t>36. Melyik kifejezés hiányzik? Az elnökség ________ a küldöttgyűlések közötti időszakban a gazdasági kamara működésének irányítása.</t>
-  </si>
-  <si>
     <t>feladata</t>
   </si>
   <si>
-    <t>37. Melyik kifejezés hiányzik? A KORMÁNY ________ HATÁSKÖRE A kormány a maga feladatkörében rendeleteket bocsát ki, és normatív határozatokat hoz, amelyeket a miniszterelnök ír alá.</t>
-  </si>
-  <si>
     <t>JOGALKOTÁSI</t>
   </si>
   <si>
-    <t>38. Melyik kifejezés hiányzik? A MINISZTEREK ________ HATÁSKÖRE A kormány tagjai jogalkotási hatáskörrel rendelkeznek, feladatuk ellátása körében rendeleteket adhatnak ki.</t>
-  </si>
-  <si>
-    <t>39. Melyik kifejezés hiányzik? Amennyiben a ________ határidő eredménytelenül letelt, a kormányhivatal vezetője jogosult közvetlenül is összehívni a képviselő-testület ülését.</t>
-  </si>
-  <si>
     <t>megadott</t>
   </si>
   <si>
-    <t>40. Melyik kifejezés hiányzik? A közmeghallgatás ________ ülésnek minősül, ezért azon a települési képviselő-testület tagjai határozatképes létszámban kötelesek megjelenni.</t>
-  </si>
-  <si>
     <t>képviselő-testületi</t>
   </si>
   <si>
-    <t>41. Melyik kifejezés hiányzik? A HELYI NÉPSZAVAZÁS Helyi ________ minősül területi hatáskör alapján az a referendum, melyet egy településen vagy településrészen bonyolítanak le.</t>
-  </si>
-  <si>
     <t>népszavazásnak</t>
   </si>
   <si>
-    <t>42. Melyik kifejezés hiányzik? Az önkormányzati ________ részletesen rendezi az első két területszervezési kérdés kezdeményezésének a feltételeit, a végleges döntés pedig a köztársasági elnök hatáskörébe tartozik.</t>
-  </si>
-  <si>
     <t>törvény</t>
   </si>
   <si>
-    <t>43. Melyik kifejezés hiányzik? Természetesen a „________ felhasználás” elsősorban az önkormányzatok kötelező és fakultatív feladatainak ellátását jelenti, hiszen a vállalkozói tevékenység nem veszélyeztetheti ezek finanszírozását.</t>
-  </si>
-  <si>
     <t>szabad</t>
   </si>
   <si>
-    <t>44. Melyik kifejezés hiányzik? Feladata a helyi ________ rendelkezésére álló források szabályszerű, gazdaságos, hatékony és eredményes felhasználásának ellenőrzése.</t>
-  </si>
-  <si>
     <t>önkormányzat</t>
   </si>
   <si>
-    <t>45. Melyik kifejezés hiányzik? Ugyancsak ________ bevételnek minősül az adóbeszedés során kivetett bírságok és késedelmi pótlékok összege is.</t>
-  </si>
-  <si>
     <t>osztott</t>
   </si>
   <si>
-    <t>46. Melyik kifejezés hiányzik? A fővárosi ________ és a kerületi önkormányzatokat megillető bevételek megosztási arányáról külön törvény rendelkezik.</t>
-  </si>
-  <si>
     <t>önkormányzatot</t>
   </si>
   <si>
-    <t>47. Melyik kifejezés hiányzik? A nemzetiségi ________ használatába kell átadni a helyi önkormányzat tulajdonában levő, de a nemzetiségi önkormányzat feladatés hatásköre ellátásához szükséges vagyontárgyakat (pl. irodahelyiség).</t>
-  </si>
-  <si>
-    <t>48. Melyik kifejezés hiányzik? Ezzel biztosítja az adott szolgáltatáshoz való ________ hozzáférés lehetőségét és finanszírozását.</t>
-  </si>
-  <si>
     <t>egyenlő</t>
   </si>
   <si>
-    <t>49. Melyik kifejezés hiányzik? Ha az ügyfél nem ________ eljárási képességgel, vagy ügyei vitelében akadályozott, képviseletet vehet igénybe.</t>
-  </si>
-  <si>
-    <t>50. Melyik kifejezés hiányzik? A támogató ________ jogosultsága azonban korlátozott, az általa támogatott személy helyett például nyilatkozattételre nem jogosult.</t>
-  </si>
-  <si>
     <t>képviseleti</t>
   </si>
   <si>
-    <t>51. Melyik kifejezés hiányzik? AZ ÜGYFÉL JOGAI A ________ ELJÁRÁSBAN – Az ügyfél a következő főbb jogokkal rendelkezik az eljárás során.</t>
-  </si>
-  <si>
     <t>HATÓSÁGI</t>
   </si>
   <si>
-    <t>52. Melyik kifejezés hiányzik? Az Ákr. biztosítja, hogy a közigazgatási eljárásban ________ szóban és írásban mindenki használhassa.</t>
-  </si>
-  <si>
     <t>anyanyelvét</t>
   </si>
   <si>
-    <t>53. Melyik kifejezés hiányzik? Eljáró ________, mely esetben az érdemi döntés meghozatala a feladata.</t>
-  </si>
-  <si>
     <t>hatóságként</t>
   </si>
   <si>
-    <t>54. Melyik kifejezés hiányzik? A hatáskör azt ________ meg, hogy egy ügyben milyen típusú és szintű szerv jogosult és egyben köteles döntést hozni.</t>
-  </si>
-  <si>
     <t>mutatja</t>
   </si>
   <si>
-    <t>55. Melyik kifejezés hiányzik? Ezeket nem ________ határozatoknak nevezzük. a) Az egyszerűsített határozatokban a jogorvoslatra való figyelmeztetés és a határozat indokolása mellőzhető.</t>
-  </si>
-  <si>
     <t>alakszerű</t>
   </si>
   <si>
-    <t>56. Melyik kifejezés hiányzik? Feladata, hogy az ________ tartózkodási helyét 15 napon belül lehetőség szerint felkutassa, és a határozatot számára átadja.</t>
-  </si>
-  <si>
     <t>ügyfél</t>
   </si>
   <si>
-    <t>57. Melyik kifejezés hiányzik? A közigazgatási döntésekkel ________ jogorvoslatok típusai a következők: a) az ügyfél kérelme alapján kezdeményezett eljárások; b) a hivatalból lefolytatható döntés-felülvizsgálati eljárások.</t>
-  </si>
-  <si>
     <t>összefüggő</t>
   </si>
   <si>
-    <t>58. Melyik kifejezés hiányzik? Ezeket a ________ egyedi ügyben hozott hatósági határozatoknak nevezzük.</t>
-  </si>
-  <si>
     <t>döntéseket</t>
   </si>
   <si>
-    <t>59. Melyik kifejezés hiányzik? Az Ákr. rendelkezései szerint ________ joggal rendelkezik az ügyfél, valamint az, akire nézve a határozat rendelkezést tartalmaz.</t>
-  </si>
-  <si>
     <t>fellebbezési</t>
   </si>
   <si>
-    <t>60. Melyik kifejezés hiányzik? A módosítás-visszavonási ________ lefolytatására a hatóság csak egy alkalommal, a határozat közlésétől számított egy éven belül jogosult.</t>
-  </si>
-  <si>
     <t>eljárás</t>
   </si>
   <si>
-    <t>61. Melyik kifejezés hiányzik? A jog fogalma – A jog ________ funkciói • Konfliktusfeloldás • Reguláció • Integráció • Nevelő, szociális funkció • Hatalmi, ideológiai funkció 1.1.</t>
-  </si>
-  <si>
     <t>társadalmi</t>
   </si>
   <si>
-    <t>62. Melyik kifejezés hiányzik? A jog fogalma – A jog ________ más normarendszerekhez Főbb társadalmi normarendszerek • Jog • Erkölcs • Szokás • Vallás 1.1.</t>
-  </si>
-  <si>
     <t>viszonya</t>
   </si>
   <si>
-    <t>63. Melyik kifejezés hiányzik? A jog fogalma • ________ (jogalanyok) viselkedésére vonatkozó • az állam által alkotott, de /vagy/ legalább az állam által elismert és • az állam által végső soron kikényszerített • kötelező magatartási szabályok összessége.</t>
-  </si>
-  <si>
     <t>személyek</t>
   </si>
   <si>
-    <t>64. Melyik kifejezés hiányzik? A jog fogalma – A ________ normarendszerek A társadalmi normák (normarendszerek) • célja az ismétlődő társadalmi jelenségek befolyásolása = szabályozás • előírják az általánosan követendőt és a helyesnek vélt magatartást • Közös sajátosságaik: a) Tartósság igénye: időben tartósan érvényesülnek.</t>
-  </si>
-  <si>
-    <t>65. Melyik kifejezés hiányzik? A jog fogalma – A jog ________ más normarendszerekhez Főbb társadalmi normarendszerek A vallás • A vallási norma, mint magatartásszabály általában a mindennapi életben beolvad a jogba, az erkölcsbe vagy a szokásba • Ezek közül valamelyik normájaként jelenik meg 1.1.</t>
-  </si>
-  <si>
-    <t>66. Melyik kifejezés hiányzik? A jog fogalma – A ________ szemben támasztott követelmények • Általános • Közzétett = nyilvános, megismerhető • Jövőbeli cselekvésre irányuló • Világos, egyértelmű • Ellentmondásmentes • Lehetségest követel • Bizonyos stabilitással rendelkezik • A kinyilvánított szabály és a hivatalos cselekvés egyezést mutat.</t>
-  </si>
-  <si>
     <t>joggal</t>
   </si>
   <si>
-    <t>67. Melyik kifejezés hiányzik? Anyagi jogi norma – Alaki jogi norma (________ norma) 1.4 A jogviszony Fogalma: a jogviszony a jog által szabályozott társadalmi viszony.</t>
-  </si>
-  <si>
     <t>eljárási</t>
   </si>
   <si>
-    <t>68. Melyik kifejezés hiányzik? A zálogjog, a ________ jogok. d) Kötelmi jog: szerződések közös szabályai (általános rész) és egyes szerződések (különös rész).</t>
-  </si>
-  <si>
     <t>használati</t>
   </si>
   <si>
-    <t>69. Melyik kifejezés hiányzik? Kártérítési ________. e) Öröklési jog: a meghalt személy jogutódlása.</t>
-  </si>
-  <si>
     <t>felelősség</t>
   </si>
   <si>
-    <t>70. Melyik kifejezés hiányzik? Végintézkedésen ________ és a törvényen alapuló öröklés rendje. f) A szellemi alkotások joga: szerzői jog (a szerző személyhez fűződő és vagyoni jogai).</t>
-  </si>
-  <si>
     <t>alapuló</t>
   </si>
   <si>
-    <t>71. Melyik kifejezés hiányzik? Iparjogvédelem (________ megoldások, grafikailag ábrázolható jelzések alkotóinak jogai, szabadalmak, formatervezési minták, védjegyek).</t>
-  </si>
-  <si>
     <t>műszaki</t>
   </si>
   <si>
-    <t>72. Melyik kifejezés hiányzik? 2.1 A jogforrások ________ és típusai M A G Y A R O R S Z Á G ALKOTMÁNYOZÁS Országgyűlés Alaptörvény I.</t>
-  </si>
-  <si>
     <t>fogalma</t>
   </si>
   <si>
-    <t>73. Melyik kifejezés hiányzik? 2.1 A jogforrások ________ – a kormányrendelet Alaptörvény 15. cikk • (3) Feladatkörében eljárva a Kormány törvényben nem szabályozott tárgykörben, illetve törvényben kapott felhatalmazás alapján rendeletet alkot.</t>
-  </si>
-  <si>
     <t>típusai</t>
   </si>
   <si>
-    <t>74. Melyik kifejezés hiányzik? A jogforrások ________ – MNB rendelet Alaptörvény 41. cikk (5) A Magyar Nemzeti Bank elnöke törvényben kapott felhatalmazás alapján, törvényben meghatározott feladatkörében rendeletet ad ki, amely törvénnyel nem lehet ellentétes.</t>
-  </si>
-  <si>
-    <t>75. Melyik kifejezés hiányzik? Alanyainak a ________ széles döntési jellemző. szabadságot biztosítanak.</t>
-  </si>
-  <si>
     <t>jogszabályok</t>
   </si>
   <si>
-    <t>76. Melyik kifejezés hiányzik? A felek közös megegyezéssel el is ________ a jogszabályi rendelkezésektől, amíg valamilyen imperatív jellegű jogszabályba nem ütközik magatartásuk.</t>
-  </si>
-  <si>
     <t>térhetnek</t>
   </si>
   <si>
-    <t>77. Melyik kifejezés hiányzik? 2.1 A jogforrások ________ – A közjogi szervezetszabályozó eszközök A jogalkotásról szóló 2010. évi CXXX. törvény (Jat.) 1. § (1) bek.</t>
-  </si>
-  <si>
-    <t>78. Melyik kifejezés hiányzik? E törvény ________ a) a jogszabályokra, valamint b) a normatív határozatra és normatív utasításra (a továbbiakban együtt: közjogi szervezetszabályozó eszköz) terjed ki.</t>
-  </si>
-  <si>
     <t>hatálya</t>
   </si>
   <si>
-    <t>79. Melyik kifejezés hiányzik? A közjogi ________ eszközben jogszabály rendelkezése nem ismételhető meg.</t>
-  </si>
-  <si>
     <t>szervezetszabályozó</t>
   </si>
   <si>
-    <t>80. Melyik kifejezés hiányzik? 2.1 A jogforrások – Az EU jog ________ • A közösségi jog – sui generis jogrend = különbözik a tagállamok jogrendszerétől és a nemzetközi közjogtól.</t>
-  </si>
-  <si>
     <t>forrásai</t>
   </si>
   <si>
-    <t>81. Melyik kifejezés hiányzik? A közösségi ________ nemcsak a tagállamok, hanem az uniós természetes és jogi személyek is alanyai.</t>
-  </si>
-  <si>
     <t>jognak</t>
   </si>
   <si>
-    <t>82. Melyik kifejezés hiányzik? Mikortól? – ________ lépés • A jogszabály saját maga határozza meg • Más jogszabály határozza meg Meddig?</t>
-  </si>
-  <si>
     <t>hatályba</t>
   </si>
   <si>
-    <t>83. Melyik kifejezés hiányzik? 2.2 A jogszabályok ________ A jogszabály hatálya - a jogszabály alkalmazhatósága.</t>
-  </si>
-  <si>
-    <t>84. Melyik kifejezés hiányzik? Négy típusa a) ________ (földrajzi) hatály b) személyi (alanyi) hatály c) Időbeli hatály d) tárgyi hatály (alkalmazási kör). - Jat.</t>
-  </si>
-  <si>
     <t>területi</t>
   </si>
   <si>
-    <t>85. Melyik kifejezés hiányzik? Fejezet 2.2 A ________ hatálya - A jogszabály területi hatálya – Hol kell/lehet alkalmazni?</t>
-  </si>
-  <si>
-    <t>86. Melyik kifejezés hiányzik? Helyi jogszabályok - Jat 6. § (1) – • A ________ területi hatálya Magyarország területére, az önkormányzati rendelet területi hatálya a helyi önkormányzat közigazgatási területére terjed ki.</t>
-  </si>
-  <si>
     <t>jogszabály</t>
   </si>
   <si>
-    <t>87. Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma Az állam ________ (Georg Jellinek – Általános államtan) – az állam közjogi fogalmának ismérvei – az államiság feltételei: 1.</t>
-  </si>
-  <si>
-    <t>88. Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma – ________ Államforma – Kormányforma - Államszerkezet • Államforma – a közhatalom gyakorlásának módja 1.</t>
-  </si>
-  <si>
     <t>Államforma</t>
   </si>
   <si>
-    <t>89. Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma - ________ Kormányforma – a törvényhozó és végrehajtó hatalom viszonya, a kormányzati hatalom gyakorlása 1.</t>
-  </si>
-  <si>
     <t>kormányforma</t>
   </si>
   <si>
-    <t>90. Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma - ________ népesség - állampolgárság Állampolgárság szabályozási kérdései - Keletkezés 1.</t>
-  </si>
-  <si>
     <t>Államalkotó</t>
   </si>
   <si>
-    <t>91. Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma - Az állam ________ Államszervezet – egy adott állam szerveinek összessége, amely révén az állam gyakorolja hatalmát, teljesíti céljait, ellátja feladatait.</t>
-  </si>
-  <si>
     <t>szervezete</t>
   </si>
   <si>
-    <t>92. Melyik kifejezés hiányzik? A tisztviselő ________ annak a döntésnek a hatékony végrehajtása, amit a politikus hozott /Woodrow Wilson/ = a kormányzás és a közigazgatás szétválasztása.</t>
-  </si>
-  <si>
-    <t>93. Melyik kifejezés hiányzik? A közigazgatás ________ Negatív fogalommeghatározás : mi nem a közigazgatás? • Magáncselekvések – Közcselekvések - Az igazgatási tevékenység (szervezeti tevékenység) végezhető magán (pl. üzleti) és állami szervezeti keretek között (= közigazgatás) • Közcselekvések, ami nem közigazgatás - törvényalkotás - igazságszolgáltatás - politika - kormányzás 1.</t>
-  </si>
-  <si>
-    <t>94. Melyik kifejezés hiányzik? A közigazgatás ________ Negatív definíció A közigazgatás: az állam saját jogrendjének uralma alatt végbemenő azon állami ténykedés, amely az igazságszolgáltatás céljaitól különböző összes egyéb állami cél megvalósítását szolgálja. – Otto Mayer /1846 – 1924/ 1.</t>
-  </si>
-  <si>
-    <t>95. Melyik kifejezés hiányzik? A közigazgatási jog fogalma és ________ Közjog (pl.) Magánjog (pl.) Alkotmányjog Polgári jog Közigazgatási jog Családjog Pénzügyi jog Kereskedelmi (gazdasági) Büntetőjog jog Büntetővégrehajtási jog Eljárásjogok Vegyes jogágak (pl.): munkajog, agrárjog 2.</t>
-  </si>
-  <si>
     <t>jellemzői</t>
   </si>
   <si>
-    <t>96. Melyik kifejezés hiányzik? A közigazgatási jog fogalma és ________ – a közigazgatási jog forrásai • Alaptörvény (?) • Törvények - A közigazgatás szervezete Jellemző: - Eljárási törvények • Rendeleti jog túlsúlya - Ágazati törvények • Nem jogszabályi jog • Rendeletek túlsúlya - Eredeti • Heterogenitás - Származékos - Önkormányzati rendeletek (!) • Alacsonyabb szintű jogforrások 3.</t>
-  </si>
-  <si>
-    <t>97. Melyik kifejezés hiányzik? A közigazgatás, mint ________ 4.2 Közigazgatási szerv, közigazgatási szervezet A szervezetrendszer • A jogi szabályozás sem a szervezetrendszer, sem a rendszer fogalmát nem határozza meg.</t>
-  </si>
-  <si>
     <t>szervezet</t>
   </si>
   <si>
-    <t>98. Melyik kifejezés hiányzik? A közigazgatás, mint ________ 4.2 Közigazgatási szerv, közigazgatási szervezet • A közigazgatási szerv önállósága (jogi értelemben) = jogosult önállóan cselekedni. • Az önálló cselekvést az önálló hatáskör teszi lehetővé.</t>
-  </si>
-  <si>
-    <t>99. Melyik kifejezés hiányzik? A rendszer ________ fogalma: egymással funkcionálisan kapcsolatban álló, a környezettől e kapcsolatok és a kapcsolatrendszernek a környezet számára végzett funkciója által elhatároltható elemek összessége. • A közigazgatás szervezet és egyben rendszer. • Szervezetként az államszervezet része.</t>
-  </si>
-  <si>
     <t>szociológiai</t>
   </si>
   <si>
-    <t>100. Melyik kifejezés hiányzik? Szakmai ________ elvek 2.1 Különös hatáskör – általános hatáskör 2.2 Ágazati elv – funkcionális elv 3.</t>
-  </si>
-  <si>
     <t>munkamegosztási</t>
   </si>
   <si>
-    <t>101. Melyik kifejezés hiányzik? Rendszerként az állam ________ a része. • A közigazgatás viszonylag önállónak nevezhető rendszerekből áll (a közigazgatás alrendszerei).</t>
-  </si>
-  <si>
     <t>szervezetrendszerének</t>
   </si>
   <si>
-    <t>102. Melyik kifejezés hiányzik? Jogi személyiséggel nem rendelkező ________ Akkor képes jogokat szerezni és kötelezettségeket vállalni, ha jogszabály így rendelkezik = polgári jogi jogalanyisággal ruházza fel.</t>
-  </si>
-  <si>
-    <t>103. Melyik kifejezés hiányzik? 7. § (1) bek. • Minden közigazgatási szerv, amely ________ szerv, egyúttal polgárjogi jogi személyiséggel is rendelkezik, de nem minden közigazgatási szerv költségvetési szerv 2.2 2.2 Egyéb: külön – általában az adott szervet létrehozó - jogszabály rendelkezhet arról, hogy egy szerv polgárjogi jogi személy. - Pl.</t>
-  </si>
-  <si>
     <t>költségvetési</t>
   </si>
   <si>
-    <t>104. Melyik kifejezés hiányzik? A közigazgatási jog alanyai - Kinek, ________ a magatartását szabályozza a jog?</t>
-  </si>
-  <si>
     <t>kiknek</t>
   </si>
   <si>
-    <t>105. Melyik kifejezés hiányzik? A közigazgatási jog alanyai Cél: a közigazgatási jog ________ a megismertetése Közigazgatási jogi jogalanyiság Polgári jogi jogalanyiság 6.</t>
-  </si>
-  <si>
     <t>alanyainak</t>
   </si>
   <si>
-    <t>106. Melyik kifejezés hiányzik? Az ember, mint jogalany ________ személy „Minden ember jogképes: jogai és kötelezettségei lehetnek.” – Ptk.</t>
-  </si>
-  <si>
     <t>természetes</t>
   </si>
   <si>
-    <t>107. Melyik kifejezés hiányzik? A szervezeti jog ________: viszonylag elkülönült joganyag a közigazgatási jogon belül, a közigazgatási jog egyik részterülete.</t>
-  </si>
-  <si>
-    <t>108. Melyik kifejezés hiányzik? Település • Az ________ területe településekre tagozódik. • Az ország teljes területe, valamennyi pontja közigazgatásilag egy (valamely) településhez tartozik, ami lehet - község, ezen belül nagyközség [Mötv.</t>
-  </si>
-  <si>
     <t>ország</t>
   </si>
   <si>
-    <t>109. Melyik kifejezés hiányzik? A közigazgatás ________ joga A közigazgatási szerveket és szervezetüket, valamint feladatés hatáskörüket a jogi szabályozás, elsősorban jogszabályok hozzák létre és alakítják.</t>
-  </si>
-  <si>
     <t>szervezeti</t>
   </si>
   <si>
-    <t>110. Melyik kifejezés hiányzik? A közigazgatás ________ joga szabályozza a közigazgatási szervek formáit, a szervek belső felépítésének rendjét, külső – akár a közigazgatáson belüli, akár a közigazgatáson kívüli – kapcsolati rendszerét.</t>
-  </si>
-  <si>
-    <t>111. Melyik kifejezés hiányzik? A közigazgatás ________ joga A közigazgatás szervezetrendszerét meghatározó joganyag A közigazgatási szervek csoportosítása szervezeti jogi szempontból A közigazgatás két nagy alrendszere: 1.</t>
-  </si>
-  <si>
-    <t>112. Melyik kifejezés hiányzik? A 2012. szeptember 1-jén ________ lépett nemzeti felsőoktatásról szóló törvény biztosítja az intézményalapítás szabadságát.</t>
-  </si>
-  <si>
-    <t>113. Melyik kifejezés hiányzik? A rektor ________ és képviseli az intézményt, egyben a szenátus elnöke is, így hatásköre a szenátus döntéseinek előkészítésére és végrehajtására is kiterjed.</t>
-  </si>
-  <si>
     <t>vezeti</t>
   </si>
   <si>
-    <t>114. Melyik kifejezés hiányzik? A kancellár ________ és felmentésére a miniszterelnök jogosult.</t>
-  </si>
-  <si>
     <t>megbízására</t>
   </si>
   <si>
-    <t>115. Melyik kifejezés hiányzik? A kancellári ________ e döntések érvényességének, illetve hatálybalépésének feltétele, tehát a kancellár széleskörű vétójoggal rendelkezik egyes döntések meghozatala során.</t>
-  </si>
-  <si>
     <t>egyetértés</t>
   </si>
   <si>
-    <t>116. Melyik kifejezés hiányzik? Az igazgatási ________ a szervezetek (köztük a közigazgatási szerveknek is) olyan tudatos, tervszerű tevékenysége, amely biztosítja a szervezet céljainak eléréséhez szükséges személyi és dologi feltételeket, valamint a munka összhangját.</t>
-  </si>
-  <si>
     <t>tevékenység</t>
   </si>
   <si>
-    <t>117. Melyik kifejezés hiányzik? KÖZIGAZGATÁSI SZERV ÖNÁLLÓ ________ EGYSÉGE – A közigazgatási szerv önálló szervezeti egysége ezzel szemben kizárólag közigazgatási jogképességgel rendelkezik, azaz önálló feladatköre van, amelynek részeként döntéseket hozhat, és azok betartatására nézve intézkedéseket tehet.</t>
-  </si>
-  <si>
     <t>SZERVEZETI</t>
   </si>
   <si>
-    <t>118. Melyik kifejezés hiányzik? Ez utóbbi ________ ún. utólagos normakontroll eljárás indítványozására jogosult. (B) ÁLLAMI SZÁMVEVŐSZÉK – Az ÁSZ kizárólag az Országgyűlésnek alárendelt legfőbb pénzügyi ellenőrző szerv, ellenőrzéseit célszerűségi, eredményességi és törvényességi szempontok szerint végzi.</t>
-  </si>
-  <si>
     <t>esetben</t>
   </si>
   <si>
-    <t>119. Melyik kifejezés hiányzik? A közigazgatási ügyekben ________ bíróságok hatásköre arra terjed ki, hogy az ügyfél keresete alapján megvizsgálják egy egyedi hatósági ügyben hozott közigazgatási határozat (döntés) jogszerűségét, és törvénysértés esetén megsemmisítsék vagy megváltoztassák azt.</t>
-  </si>
-  <si>
     <t>eljáró</t>
   </si>
   <si>
-    <t>120. Melyik kifejezés hiányzik? Az Önkormányzati ________ jogosult az önkormányzat képviselő-testülete (közgyűlése) által elfogadott rendeletet megsemmisíteni, ha az magasabb szintű jogszabállyal ellentétes, vagy megállapíthatja a helyi önkormányzat jogalkotási kötelezettségének elmulasztását is.</t>
-  </si>
-  <si>
     <t>Tanács</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Ennek központi ________ a munkamegosztás, mely a közigazgatási szervek által elvégzendő feladatok és az ellátásukra hivatott szervezetek tagolását jelenti.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A NAV hatásköre ________ kiterjed az adóhátralék bankszámláról történő letiltására, adóbírság kivetésére.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Jegyezzük meg jól tehát, hogy ________ nélkül egy közigazgatási szerv feladatait nem képes hatékonyan ellátni!  Az illetékesség az adott hatóság földrajzi értelemben vett működési területét határozza meg.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A KÖZIGAZGATÁSI SZERV MUNKASZERVEZETE A közigazgatási ________ jellemzője önálló munkaszervezet, hivatal működtetése, amelynek élén egyszemélyi felelős vezető (hivatalvezető) áll.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A közintézetek ________ mindenekelőtt a tulajdonosi jogokat gyakorló (alapító) fenntartóval szemben biztosítja a jogi szabályozás.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Ezáltal a ________ hatásköre lesz a szolgáltatási jogviszony keretében az intézeti ellátottal összefüggésben döntéseket hozni, és ezek végrehatásáról gondoskodni.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? Ezen belül a vezetőknek is ________ további vezetői és a beosztottaknak is lehetnek beosztottjaik, ugyanakkor aki nem vezető és nem beosztott, az nem tartozik a rendszerbe: kívülálló (ilyen például az ügyfél).</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A centralizáció mint ________ azt jelenti, hogy egy meghatározott szerv a közigazgatás szervezetének csúcsán helyezkedik el, s az irányítás innen történik.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A kirendeltség nem ________ önálló feladatés hatáskörrel rendelkező területi szervnek, csak az adott hatóság területileg kihelyezett belső szervezeti egységének.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Az integráció ________, a részeknek egymáshoz illeszkedését jelenti, bizonyos értelemben a közigazgatás hierarchikusságát és centralizáltságát finomító, működését egységesítő elv.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? Az ellenőrzési ________ önálló gyakorlására nemcsak szervek közötti ún. belső viszonyban, hanem közigazgatási szerv és ügyfél között is találunk példákat (ezt nevezzük külső ellenőrzésnek).</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Megjegyezzük, hogy egyes ________ feladatok ellátása csak névlegesen valósul meg járási szinten, ugyanis számos ügykörben nem minden járási hivatal rendelkezik hatáskörrel.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Magyarországon – sok más ________ államhoz hasonlóan – a közigazgatásinak tekinthető feladatokat alapvetően az állam két szervezeti alrendszere, államigazgatási és önkormányzati szervek valósítják meg.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? Ebben a részben ________ az egyes alrendszerek működésének főbb kapcsolódási pontjait.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A középszinten belül a ________ igazgatás párhuzamos felépítésű, azaz önkormányzati és államigazgatási szervek egyaránt megtalálhatóak.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Miniszterelnöknek ________ minden olyan személy, aki  büntetlen előéletű,  rendelkezik magyar állampolgársággal, és  az országgyűlési képviselők választásán passzív választójoga van (azaz választható).</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A miniszter a ________ előírt feladatés hatáskörében önállóan jár el, és ezért felelősséggel tartozik (pl. az Országgyűlésben interpellálható).</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A járási ________ az a büntetlen előéletű, cselekvőképes és nagykorú magyar állampolgár nevezhető ki, aki felsőfokú végzettséggel és legalább 5 év közigazgatási gyakorlattal rendelkezik.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? B) IRÁNYÍTÁS – Az ________ hierarchikus, alá-fölérendeltségi kapcsolatban álló közigazgatási szervek közötti hatalmi viszonyt irányításnak nevezzük.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A HELYI SZINT Magyarország ________ a települések típusai a következők: község, nagyközség, város, járásszékhely város, megyei jogú város, főváros és 23 kerülete.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Lényeges elem ________ a szolgáltató jellegű közigazgatás számára az ügyfél-közeliség érvényesülése.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Ez azt jelenti, hogy a kormányon belül csak a ________ az Országgyűlés által közvetlenül választott politikai vezető, vagyis a miniszterelnöknek van kormánya, nem pedig a kormánynak miniszterelnöke.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Ez azt jelenti, hogy a miniszterelnök ________ függ, elfogadja-e azt, vagy sem.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A szakpolitikai ________ feladata az adott minisztériumhoz tartozó egyes szakterületi érdekek érvényesítése.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A bizalomvesztés miatt ________ tisztviselő jogosult végkielégítésre és 2 hónap felmentési idő letöltésére. c) Alkalmatlanság.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Vannak ________ a közigazgatásban, akik elvileg különböző területeken is képesek megállni a helyüket, őket nevezzük generalistáknak, ellentétben az egy területre szakosodott specialistákkal.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Ebbe a körbe tartozik a politikai ________ és főtanácsadók fizetésének megállapítása a központi államigazgatásban.  Vezetői munkakörök létesítése.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A fokozott ________ abban áll, hogy több bűncselekmény, mint például az emberölés vagy az emberrablás súlyosabban minősül, ha hivatalos személy sérelmére követik el.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Azt jelenti, hogy a beosztott ________ a vezető által vallott értékekkel, célokkal, és munkáját ezek alapján végzi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? A törvény úgy ________, hogy a tisztviselő köteles felettese utasításait végrehajtani.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? TÖRVÉNYESSÉGI ________ JOGKÖRÖK – A megyei kormányhivatal vezetőjének feladata a helyi és nemzetiségi önkormányzatok törvényességi felügyelete.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? Ilyen szervnek ________ a Gazdasági Versenyhivatal Versenytanácsa, vagy a Közbeszerzési Döntőbizottság.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? Ilyen a Nemzeti ________ Testület (feladata a Magyar Szabványok /MSZ/ előírásainak meghatározása és közzététele).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? A gazdasági ________ feladata, hogy előmozdítsák a gazdaság fejlődését és szerveződését, a piaci magatartás tisztességét, a gazdasági tevékenységet folytatók általános, együttes érdekeinek érvényesítését.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A közigazgatás ________ joga szabályozza a közigazgatási szervek formáit, a szervek belső felépítésének rendjét, külső – akár a közigazgatáson belüli, akár a közigazgatáson kívüli – kapcsolati rendszerét.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A közigazgatás ________ joga A közigazgatás szervezetrendszerét meghatározó joganyag A közigazgatási szervek csoportosítása szervezeti jogi szempontból A közigazgatás két nagy alrendszere: 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? A 2012. szeptember 1-jén ________ lépett nemzeti felsőoktatásról szóló törvény biztosítja az intézményalapítás szabadságát.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A rektor ________ és képviseli az intézményt, egyben a szenátus elnöke is, így hatásköre a szenátus döntéseinek előkészítésére és végrehajtására is kiterjed.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A kancellár ________ és felmentésére a miniszterelnök jogosult.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? A kancellári ________ e döntések érvényességének, illetve hatálybalépésének feltétele, tehát a kancellár széleskörű vétójoggal rendelkezik egyes döntések meghozatala során.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Az igazgatási ________ a szervezetek (köztük a közigazgatási szerveknek is) olyan tudatos, tervszerű tevékenysége, amely biztosítja a szervezet céljainak eléréséhez szükséges személyi és dologi feltételeket, valamint a munka összhangját.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? KÖZIGAZGATÁSI SZERV ÖNÁLLÓ ________ EGYSÉGE – A közigazgatási szerv önálló szervezeti egysége ezzel szemben kizárólag közigazgatási jogképességgel rendelkezik, azaz önálló feladatköre van, amelynek részeként döntéseket hozhat, és azok betartatására nézve intézkedéseket tehet.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Ez utóbbi ________ ún. utólagos normakontroll eljárás indítványozására jogosult. (B) ÁLLAMI SZÁMVEVŐSZÉK – Az ÁSZ kizárólag az Országgyűlésnek alárendelt legfőbb pénzügyi ellenőrző szerv, ellenőrzéseit célszerűségi, eredményességi és törvényességi szempontok szerint végzi.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A közigazgatási ügyekben ________ bíróságok hatásköre arra terjed ki, hogy az ügyfél keresete alapján megvizsgálják egy egyedi hatósági ügyben hozott közigazgatási határozat (döntés) jogszerűségét, és törvénysértés esetén megsemmisítsék vagy megváltoztassák azt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? Az Önkormányzati ________ jogosult az önkormányzat képviselő-testülete (közgyűlése) által elfogadott rendeletet megsemmisíteni, ha az magasabb szintű jogszabállyal ellentétes, vagy megállapíthatja a helyi önkormányzat jogalkotási kötelezettségének elmulasztását is.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? 2.1 A jogforrások ________ – A közjogi szervezetszabályozó eszközök A jogalkotásról szóló 2010. évi CXXX. törvény (Jat.) 1. § (1) bek.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? E törvény ________ a) a jogszabályokra, valamint b) a normatív határozatra és normatív utasításra (a továbbiakban együtt: közjogi szervezetszabályozó eszköz) terjed ki.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? A közjogi ________ eszközben jogszabály rendelkezése nem ismételhető meg.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? 2.1 A jogforrások – Az EU jog ________ • A közösségi jog – sui generis jogrend = különbözik a tagállamok jogrendszerétől és a nemzetközi közjogtól.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A közösségi ________ nemcsak a tagállamok, hanem az uniós természetes és jogi személyek is alanyai.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? 2.2 A jogszabályok ________ A jogszabály hatálya - a jogszabály alkalmazhatósága.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Négy típusa a) ________ (földrajzi) hatály b) személyi (alanyi) hatály c) Időbeli hatály d) tárgyi hatály (alkalmazási kör). - Jat.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Fejezet 2.2 A ________ hatálya - A jogszabály területi hatálya – Hol kell/lehet alkalmazni?</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Helyi jogszabályok - Jat 6. § (1) – • A ________ területi hatálya Magyarország területére, az önkormányzati rendelet területi hatálya a helyi önkormányzat közigazgatási területére terjed ki.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma Az állam ________ (Georg Jellinek – Általános államtan) – az állam közjogi fogalmának ismérvei – az államiság feltételei: 1.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma – ________ Államforma – Kormányforma - Államszerkezet • Államforma – a közhatalom gyakorlásának módja 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma - ________ Kormányforma – a törvényhozó és végrehajtó hatalom viszonya, a kormányzati hatalom gyakorlása 1.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma - ________ népesség - állampolgárság Állampolgárság szabályozási kérdései - Keletkezés 1.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Ezen felül speciális ________ minősül a főváros, ahol a koncentrált lakosságszám miatt kerületi hivatalok alakultak.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Az elnökség ________ a küldöttgyűlések közötti időszakban a gazdasági kamara működésének irányítása.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A KORMÁNY ________ HATÁSKÖRE A kormány a maga feladatkörében rendeleteket bocsát ki, és normatív határozatokat hoz, amelyeket a miniszterelnök ír alá.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A MINISZTEREK ________ HATÁSKÖRE A kormány tagjai jogalkotási hatáskörrel rendelkeznek, feladatuk ellátása körében rendeleteket adhatnak ki.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Amennyiben a ________ határidő eredménytelenül letelt, a kormányhivatal vezetője jogosult közvetlenül is összehívni a képviselő-testület ülését.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A közmeghallgatás ________ ülésnek minősül, ezért azon a települési képviselő-testület tagjai határozatképes létszámban kötelesek megjelenni.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? A HELYI NÉPSZAVAZÁS Helyi ________ minősül területi hatáskör alapján az a referendum, melyet egy településen vagy településrészen bonyolítanak le.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Az önkormányzati ________ részletesen rendezi az első két területszervezési kérdés kezdeményezésének a feltételeit, a végleges döntés pedig a köztársasági elnök hatáskörébe tartozik.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Természetesen a „________ felhasználás” elsősorban az önkormányzatok kötelező és fakultatív feladatainak ellátását jelenti, hiszen a vállalkozói tevékenység nem veszélyeztetheti ezek finanszírozását.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Feladata a helyi ________ rendelkezésére álló források szabályszerű, gazdaságos, hatékony és eredményes felhasználásának ellenőrzése.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? A nemzetiségi ________ használatába kell átadni a helyi önkormányzat tulajdonában levő, de a nemzetiségi önkormányzat feladatés hatásköre ellátásához szükséges vagyontárgyakat (pl. irodahelyiség).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? Ezzel biztosítja az adott szolgáltatáshoz való ________ hozzáférés lehetőségét és finanszírozását.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Az Ákr. biztosítja, hogy a közigazgatási eljárásban ________ szóban és írásban mindenki használhassa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? Eljáró ________, mely esetben az érdemi döntés meghozatala a feladata.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A hatáskör azt ________ meg, hogy egy ügyben milyen típusú és szintű szerv jogosult és egyben köteles döntést hozni.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? Ezeket nem ________ határozatoknak nevezzük. a) Az egyszerűsített határozatokban a jogorvoslatra való figyelmeztetés és a határozat indokolása mellőzhető.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Feladata, hogy az ________ tartózkodási helyét 15 napon belül lehetőség szerint felkutassa, és a határozatot számára átadja.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A közigazgatási döntésekkel ________ jogorvoslatok típusai a következők: a) az ügyfél kérelme alapján kezdeményezett eljárások; b) a hivatalból lefolytatható döntés-felülvizsgálati eljárások.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Ezeket a ________ egyedi ügyben hozott hatósági határozatoknak nevezzük.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? A módosítás-visszavonási ________ lefolytatására a hatóság csak egy alkalommal, a határozat közlésétől számított egy éven belül jogosult.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? A jog fogalma – A jog ________ más normarendszerekhez Főbb társadalmi normarendszerek • Jog • Erkölcs • Szokás • Vallás 1.1.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A jog fogalma • ________ (jogalanyok) viselkedésére vonatkozó • az állam által alkotott, de /vagy/ legalább az állam által elismert és • az állam által végső soron kikényszerített • kötelező magatartási szabályok összessége.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A jog fogalma – A jog ________ funkciói • Konfliktusfeloldás • Reguláció • Integráció • Nevelő, szociális funkció • Hatalmi, ideológiai funkció 1.1.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Az Ákr. rendelkezései szerint ________ joggal rendelkezik az ügyfél, valamint az, akire nézve a határozat rendelkezést tartalmaz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? Ugyancsak ________ bevételnek minősül az adóbeszedés során kivetett bírságok és késedelmi pótlékok összege is.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? A fővárosi ________ és a kerületi önkormányzatokat megillető bevételek megosztási arányáról külön törvény rendelkezik.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Ha az ügyfél nem ________ eljárási képességgel, vagy ügyei vitelében akadályozott, képviseletet vehet igénybe.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A támogató ________ jogosultsága azonban korlátozott, az általa támogatott személy helyett például nyilatkozattételre nem jogosult.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? AZ ÜGYFÉL JOGAI A ________ ELJÁRÁSBAN – Az ügyfél a következő főbb jogokkal rendelkezik az eljárás során.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? A jog fogalma – A ________ normarendszerek A társadalmi normák (normarendszerek) • célja az ismétlődő társadalmi jelenségek befolyásolása = szabályozás • előírják az általánosan követendőt és a helyesnek vélt magatartást • Közös sajátosságaik: a) Tartósság igénye: időben tartósan érvényesülnek.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A jog fogalma – A jog ________ más normarendszerekhez Főbb társadalmi normarendszerek A vallás • A vallási norma, mint magatartásszabály általában a mindennapi életben beolvad a jogba, az erkölcsbe vagy a szokásba • Ezek közül valamelyik normájaként jelenik meg 1.1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? A jog fogalma – A ________ szemben támasztott követelmények • Általános • Közzétett = nyilvános, megismerhető • Jövőbeli cselekvésre irányuló • Világos, egyértelmű • Ellentmondásmentes • Lehetségest követel • Bizonyos stabilitással rendelkezik • A kinyilvánított szabály és a hivatalos cselekvés egyezést mutat.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Anyagi jogi norma – Alaki jogi norma (________ norma) 1.4 A jogviszony Fogalma: a jogviszony a jog által szabályozott társadalmi viszony.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A zálogjog, a ________ jogok. d) Kötelmi jog: szerződések közös szabályai (általános rész) és egyes szerződések (különös rész).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? Végintézkedésen ________ és a törvényen alapuló öröklés rendje. f) A szellemi alkotások joga: szerzői jog (a szerző személyhez fűződő és vagyoni jogai).</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Kártérítési ________. e) Öröklési jog: a meghalt személy jogutódlása.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? 2.1 A jogforrások ________ és típusai M A G Y A R O R S Z Á G ALKOTMÁNYOZÁS Országgyűlés Alaptörvény I.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Iparjogvédelem (________ megoldások, grafikailag ábrázolható jelzések alkotóinak jogai, szabadalmak, formatervezési minták, védjegyek).</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? 2.1 A jogforrások ________ – a kormányrendelet Alaptörvény 15. cikk • (3) Feladatkörében eljárva a Kormány törvényben nem szabályozott tárgykörben, illetve törvényben kapott felhatalmazás alapján rendeletet alkot.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A jogforrások ________ – MNB rendelet Alaptörvény 41. cikk (5) A Magyar Nemzeti Bank elnöke törvényben kapott felhatalmazás alapján, törvényben meghatározott feladatkörében rendeletet ad ki, amely törvénnyel nem lehet ellentétes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? A felek közös megegyezéssel el is ________ a jogszabályi rendelkezésektől, amíg valamilyen imperatív jellegű jogszabályba nem ütközik magatartásuk.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Alanyainak a ________ széles döntési jellemző. szabadságot biztosítanak.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Mikortól? – ________ lépés • A jogszabály saját maga határozza meg • Más jogszabály határozza meg Meddig?</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma - Az állam ________ Államszervezet – egy adott állam szerveinek összessége, amely révén az állam gyakorolja hatalmát, teljesíti céljait, ellátja feladatait.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A tisztviselő ________ annak a döntésnek a hatékony végrehajtása, amit a politikus hozott /Woodrow Wilson/ = a kormányzás és a közigazgatás szétválasztása.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A közigazgatás ________ Negatív fogalommeghatározás : mi nem a közigazgatás? • Magáncselekvések – Közcselekvések - Az igazgatási tevékenység (szervezeti tevékenység) végezhető magán (pl. üzleti) és állami szervezeti keretek között (= közigazgatás) • Közcselekvések, ami nem közigazgatás - törvényalkotás - igazságszolgáltatás - politika - kormányzás 1.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A közigazgatás ________ Negatív definíció A közigazgatás: az állam saját jogrendjének uralma alatt végbemenő azon állami ténykedés, amely az igazságszolgáltatás céljaitól különböző összes egyéb állami cél megvalósítását szolgálja. – Otto Mayer /1846 – 1924/ 1.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A közigazgatási jog fogalma és ________ Közjog (pl.) Magánjog (pl.) Alkotmányjog Polgári jog Közigazgatási jog Családjog Pénzügyi jog Kereskedelmi (gazdasági) Büntetőjog jog Büntetővégrehajtási jog Eljárásjogok Vegyes jogágak (pl.): munkajog, agrárjog 2.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A közigazgatási jog fogalma és ________ – a közigazgatási jog forrásai • Alaptörvény (?) • Törvények - A közigazgatás szervezete Jellemző: - Eljárási törvények • Rendeleti jog túlsúlya - Ágazati törvények • Nem jogszabályi jog • Rendeletek túlsúlya - Eredeti • Heterogenitás - Származékos - Önkormányzati rendeletek (!) • Alacsonyabb szintű jogforrások 3.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A közigazgatás, mint ________ 4.2 Közigazgatási szerv, közigazgatási szervezet A szervezetrendszer • A jogi szabályozás sem a szervezetrendszer, sem a rendszer fogalmát nem határozza meg.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? A közigazgatás, mint ________ 4.2 Közigazgatási szerv, közigazgatási szervezet • A közigazgatási szerv önállósága (jogi értelemben) = jogosult önállóan cselekedni. • Az önálló cselekvést az önálló hatáskör teszi lehetővé.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? A rendszer ________ fogalma: egymással funkcionálisan kapcsolatban álló, a környezettől e kapcsolatok és a kapcsolatrendszernek a környezet számára végzett funkciója által elhatároltható elemek összessége. • A közigazgatás szervezet és egyben rendszer. • Szervezetként az államszervezet része.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? Szakmai ________ elvek 2.1 Különös hatáskör – általános hatáskör 2.2 Ágazati elv – funkcionális elv 3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? Rendszerként az állam ________ a része. • A közigazgatás viszonylag önállónak nevezhető rendszerekből áll (a közigazgatás alrendszerei).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? Jogi személyiséggel nem rendelkező ________ Akkor képes jogokat szerezni és kötelezettségeket vállalni, ha jogszabály így rendelkezik = polgári jogi jogalanyisággal ruházza fel.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? 7. § (1) bek. • Minden közigazgatási szerv, amely ________ szerv, egyúttal polgárjogi jogi személyiséggel is rendelkezik, de nem minden közigazgatási szerv költségvetési szerv 2.2 2.2 Egyéb: külön – általában az adott szervet létrehozó - jogszabály rendelkezhet arról, hogy egy szerv polgárjogi jogi személy. - Pl.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? A közigazgatási jog alanyai - Kinek, ________ a magatartását szabályozza a jog?</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A közigazgatási jog alanyai Cél: a közigazgatási jog ________ a megismertetése Közigazgatási jogi jogalanyiság Polgári jogi jogalanyiság 6.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? Az ember, mint jogalany ________ személy „Minden ember jogképes: jogai és kötelezettségei lehetnek.” – Ptk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? A szervezeti jog ________: viszonylag elkülönült joganyag a közigazgatási jogon belül, a közigazgatási jog egyik részterülete.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Melyik kifejezés hiányzik? Település • Az ________ területe településekre tagozódik. • Az ország teljes területe, valamennyi pontja közigazgatásilag egy (valamely) településhez tartozik, ami lehet - község, ezen belül nagyközség [Mötv.</t>
+  </si>
+  <si>
+    <t>Melyik kifejezés hiányzik? A közigazgatás ________ joga A közigazgatási szerveket és szervezetüket, valamint feladatés hatáskörüket a jogi szabályozás, elsősorban jogszabályok hozzák létre és alakítják.</t>
   </si>
 </sst>
 </file>
@@ -1755,7 +1743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17805C46-17C0-4B33-B5E8-FAC4E7BC2D5B}">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A2:D55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
@@ -1763,14 +1751,6 @@
     <col min="4" max="4" width="41.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B1" t="s">
-        <v>206</v>
-      </c>
-    </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
@@ -1785,7 +1765,7 @@
         <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1793,7 +1773,7 @@
         <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1801,7 +1781,7 @@
         <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1809,7 +1789,7 @@
         <v>121</v>
       </c>
       <c r="B6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1817,7 +1797,7 @@
         <v>123</v>
       </c>
       <c r="B7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1825,7 +1805,7 @@
         <v>164</v>
       </c>
       <c r="B8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1857,7 +1837,7 @@
         <v>131</v>
       </c>
       <c r="B12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1881,7 +1861,7 @@
         <v>204</v>
       </c>
       <c r="B15" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1889,7 +1869,7 @@
         <v>202</v>
       </c>
       <c r="B16" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1897,7 +1877,7 @@
         <v>200</v>
       </c>
       <c r="B17" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1905,7 +1885,7 @@
         <v>198</v>
       </c>
       <c r="B18" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1969,7 +1949,7 @@
         <v>135</v>
       </c>
       <c r="B26" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1977,7 +1957,7 @@
         <v>155</v>
       </c>
       <c r="B27" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1985,7 +1965,7 @@
         <v>153</v>
       </c>
       <c r="B28" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1993,7 +1973,7 @@
         <v>133</v>
       </c>
       <c r="B29" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -2001,7 +1981,7 @@
         <v>155</v>
       </c>
       <c r="B30" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -2009,7 +1989,7 @@
         <v>153</v>
       </c>
       <c r="B31" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -2017,7 +1997,7 @@
         <v>145</v>
       </c>
       <c r="B32" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -2025,7 +2005,7 @@
         <v>143</v>
       </c>
       <c r="B33" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -2033,7 +2013,7 @@
         <v>139</v>
       </c>
       <c r="B34" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -2041,7 +2021,7 @@
         <v>141</v>
       </c>
       <c r="B35" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -2049,7 +2029,7 @@
         <v>147</v>
       </c>
       <c r="B36" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -2057,7 +2037,7 @@
         <v>149</v>
       </c>
       <c r="B37" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -2065,7 +2045,7 @@
         <v>151</v>
       </c>
       <c r="B38" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -2073,7 +2053,7 @@
         <v>137</v>
       </c>
       <c r="B39" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -2081,7 +2061,7 @@
         <v>109</v>
       </c>
       <c r="B40" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -2089,7 +2069,7 @@
         <v>107</v>
       </c>
       <c r="B41" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -2097,7 +2077,7 @@
         <v>105</v>
       </c>
       <c r="B42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -2105,7 +2085,7 @@
         <v>103</v>
       </c>
       <c r="B43" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -2113,7 +2093,7 @@
         <v>101</v>
       </c>
       <c r="B44" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -2121,7 +2101,7 @@
         <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -2129,7 +2109,7 @@
         <v>97</v>
       </c>
       <c r="B46" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -2137,7 +2117,7 @@
         <v>95</v>
       </c>
       <c r="B47" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -2145,7 +2125,7 @@
         <v>93</v>
       </c>
       <c r="B48" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -2153,7 +2133,7 @@
         <v>91</v>
       </c>
       <c r="B49" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -2161,7 +2141,7 @@
         <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -2169,7 +2149,7 @@
         <v>88</v>
       </c>
       <c r="B51" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -2177,7 +2157,7 @@
         <v>86</v>
       </c>
       <c r="B52" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -2185,7 +2165,7 @@
         <v>84</v>
       </c>
       <c r="B53" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -2193,7 +2173,7 @@
         <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -2201,7 +2181,7 @@
         <v>80</v>
       </c>
       <c r="B55" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -2211,21 +2191,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B109"/>
+  <dimension ref="A2:B109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B1" t="s">
-        <v>206</v>
-      </c>
-    </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
@@ -3081,979 +3053,971 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2545C15C-6CAE-4C6C-B385-58D367835720}">
-  <dimension ref="A1:B121"/>
+  <dimension ref="A2:B121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="255.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B1" t="s">
-        <v>247</v>
-      </c>
-    </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>248</v>
+        <v>343</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>250</v>
+        <v>344</v>
       </c>
       <c r="B3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>252</v>
+        <v>345</v>
       </c>
       <c r="B4" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>254</v>
+        <v>346</v>
       </c>
       <c r="B5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>256</v>
+        <v>347</v>
       </c>
       <c r="B6" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>258</v>
+        <v>348</v>
       </c>
       <c r="B7" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>260</v>
+        <v>349</v>
       </c>
       <c r="B8" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>262</v>
+        <v>350</v>
       </c>
       <c r="B9" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>264</v>
+        <v>351</v>
       </c>
       <c r="B10" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>266</v>
+        <v>352</v>
       </c>
       <c r="B11" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>268</v>
+        <v>361</v>
       </c>
       <c r="B12" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>270</v>
+        <v>353</v>
       </c>
       <c r="B13" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>272</v>
+        <v>354</v>
       </c>
       <c r="B14" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>274</v>
+        <v>362</v>
       </c>
       <c r="B15" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>276</v>
+        <v>355</v>
       </c>
       <c r="B16" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>278</v>
+        <v>356</v>
       </c>
       <c r="B17" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>280</v>
+        <v>363</v>
       </c>
       <c r="B18" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>282</v>
+        <v>357</v>
       </c>
       <c r="B19" t="s">
-        <v>283</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>284</v>
+        <v>358</v>
       </c>
       <c r="B20" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>286</v>
+        <v>364</v>
       </c>
       <c r="B21" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>288</v>
+        <v>359</v>
       </c>
       <c r="B22" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>290</v>
+        <v>365</v>
       </c>
       <c r="B23" t="s">
-        <v>291</v>
+        <v>265</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>292</v>
+        <v>366</v>
       </c>
       <c r="B24" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>294</v>
+        <v>360</v>
       </c>
       <c r="B25" t="s">
-        <v>295</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>296</v>
+        <v>367</v>
       </c>
       <c r="B26" t="s">
-        <v>297</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>298</v>
+        <v>368</v>
       </c>
       <c r="B27" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>300</v>
+        <v>369</v>
       </c>
       <c r="B28" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>302</v>
+        <v>370</v>
       </c>
       <c r="B29" t="s">
-        <v>303</v>
+        <v>271</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>304</v>
+        <v>371</v>
       </c>
       <c r="B30" t="s">
-        <v>305</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>306</v>
+        <v>372</v>
       </c>
       <c r="B31" t="s">
-        <v>307</v>
+        <v>273</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>308</v>
+        <v>373</v>
       </c>
       <c r="B32" t="s">
-        <v>309</v>
+        <v>274</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>310</v>
+        <v>401</v>
       </c>
       <c r="B33" t="s">
-        <v>311</v>
+        <v>275</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>312</v>
+        <v>374</v>
       </c>
       <c r="B34" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>313</v>
+        <v>375</v>
       </c>
       <c r="B35" t="s">
-        <v>314</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>315</v>
+        <v>376</v>
       </c>
       <c r="B36" t="s">
-        <v>316</v>
+        <v>277</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>317</v>
+        <v>402</v>
       </c>
       <c r="B37" t="s">
-        <v>318</v>
+        <v>278</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>319</v>
+        <v>403</v>
       </c>
       <c r="B38" t="s">
-        <v>320</v>
+        <v>279</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>321</v>
+        <v>404</v>
       </c>
       <c r="B39" t="s">
-        <v>320</v>
+        <v>279</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>322</v>
+        <v>405</v>
       </c>
       <c r="B40" t="s">
-        <v>323</v>
+        <v>280</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>324</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s">
-        <v>325</v>
+        <v>281</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>326</v>
+        <v>407</v>
       </c>
       <c r="B42" t="s">
-        <v>327</v>
+        <v>282</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>328</v>
+        <v>408</v>
       </c>
       <c r="B43" t="s">
-        <v>329</v>
+        <v>283</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>330</v>
+        <v>409</v>
       </c>
       <c r="B44" t="s">
-        <v>331</v>
+        <v>284</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>332</v>
+        <v>410</v>
       </c>
       <c r="B45" t="s">
-        <v>333</v>
+        <v>285</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>334</v>
+        <v>425</v>
       </c>
       <c r="B46" t="s">
-        <v>335</v>
+        <v>286</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>336</v>
+        <v>426</v>
       </c>
       <c r="B47" t="s">
-        <v>337</v>
+        <v>287</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>338</v>
+        <v>411</v>
       </c>
       <c r="B48" t="s">
-        <v>333</v>
+        <v>285</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>339</v>
+        <v>412</v>
       </c>
       <c r="B49" t="s">
-        <v>340</v>
+        <v>288</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>341</v>
+        <v>427</v>
       </c>
       <c r="B50" t="s">
-        <v>307</v>
+        <v>273</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>342</v>
+        <v>428</v>
       </c>
       <c r="B51" t="s">
-        <v>343</v>
+        <v>289</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>344</v>
+        <v>429</v>
       </c>
       <c r="B52" t="s">
-        <v>345</v>
+        <v>290</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>346</v>
+        <v>413</v>
       </c>
       <c r="B53" t="s">
-        <v>347</v>
+        <v>291</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>348</v>
+        <v>414</v>
       </c>
       <c r="B54" t="s">
-        <v>349</v>
+        <v>292</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>350</v>
+        <v>415</v>
       </c>
       <c r="B55" t="s">
-        <v>351</v>
+        <v>293</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>352</v>
+        <v>416</v>
       </c>
       <c r="B56" t="s">
-        <v>353</v>
+        <v>294</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>354</v>
+        <v>417</v>
       </c>
       <c r="B57" t="s">
-        <v>355</v>
+        <v>295</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>356</v>
+        <v>418</v>
       </c>
       <c r="B58" t="s">
-        <v>357</v>
+        <v>296</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>358</v>
+        <v>419</v>
       </c>
       <c r="B59" t="s">
-        <v>359</v>
+        <v>297</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>360</v>
+        <v>424</v>
       </c>
       <c r="B60" t="s">
-        <v>361</v>
+        <v>298</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>362</v>
+        <v>420</v>
       </c>
       <c r="B61" t="s">
-        <v>363</v>
+        <v>299</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>364</v>
+        <v>423</v>
       </c>
       <c r="B62" t="s">
-        <v>365</v>
+        <v>300</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>366</v>
+        <v>421</v>
       </c>
       <c r="B63" t="s">
-        <v>367</v>
+        <v>301</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>368</v>
+        <v>422</v>
       </c>
       <c r="B64" t="s">
-        <v>369</v>
+        <v>302</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>370</v>
+        <v>430</v>
       </c>
       <c r="B65" t="s">
-        <v>365</v>
+        <v>300</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>371</v>
+        <v>431</v>
       </c>
       <c r="B66" t="s">
-        <v>367</v>
+        <v>301</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>372</v>
+        <v>432</v>
       </c>
       <c r="B67" t="s">
-        <v>373</v>
+        <v>303</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>374</v>
+        <v>433</v>
       </c>
       <c r="B68" t="s">
-        <v>375</v>
+        <v>304</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>376</v>
+        <v>434</v>
       </c>
       <c r="B69" t="s">
-        <v>377</v>
+        <v>305</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>378</v>
+        <v>436</v>
       </c>
       <c r="B70" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>380</v>
+        <v>435</v>
       </c>
       <c r="B71" t="s">
-        <v>381</v>
+        <v>307</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>382</v>
+        <v>438</v>
       </c>
       <c r="B72" t="s">
-        <v>383</v>
+        <v>308</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>384</v>
+        <v>437</v>
       </c>
       <c r="B73" t="s">
-        <v>385</v>
+        <v>309</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>386</v>
+        <v>439</v>
       </c>
       <c r="B74" t="s">
-        <v>387</v>
+        <v>310</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>388</v>
+        <v>440</v>
       </c>
       <c r="B75" t="s">
-        <v>387</v>
+        <v>310</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>389</v>
+        <v>442</v>
       </c>
       <c r="B76" t="s">
-        <v>390</v>
+        <v>311</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>391</v>
+        <v>441</v>
       </c>
       <c r="B77" t="s">
-        <v>392</v>
+        <v>312</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B78" t="s">
-        <v>387</v>
+        <v>310</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B79" t="s">
-        <v>395</v>
+        <v>313</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B80" t="s">
-        <v>397</v>
+        <v>314</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B81" t="s">
-        <v>399</v>
+        <v>315</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="B82" t="s">
-        <v>401</v>
+        <v>316</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>402</v>
+        <v>443</v>
       </c>
       <c r="B83" t="s">
-        <v>403</v>
+        <v>317</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="B84" t="s">
-        <v>395</v>
+        <v>313</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="B85" t="s">
-        <v>406</v>
+        <v>318</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="B86" t="s">
-        <v>390</v>
+        <v>311</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="B87" t="s">
-        <v>409</v>
+        <v>319</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="B88" t="s">
-        <v>385</v>
+        <v>309</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="B89" t="s">
-        <v>412</v>
+        <v>320</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="B90" t="s">
-        <v>414</v>
+        <v>321</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="B91" t="s">
-        <v>416</v>
+        <v>322</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="B92" t="s">
-        <v>418</v>
+        <v>323</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="B93" t="s">
-        <v>318</v>
+        <v>278</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="B94" t="s">
-        <v>385</v>
+        <v>309</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="B95" t="s">
-        <v>385</v>
+        <v>309</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="B96" t="s">
-        <v>423</v>
+        <v>324</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="B97" t="s">
-        <v>423</v>
+        <v>324</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="B98" t="s">
-        <v>426</v>
+        <v>325</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>427</v>
+        <v>451</v>
       </c>
       <c r="B99" t="s">
-        <v>426</v>
+        <v>325</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="B100" t="s">
-        <v>429</v>
+        <v>326</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>430</v>
+        <v>453</v>
       </c>
       <c r="B101" t="s">
-        <v>431</v>
+        <v>327</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B102" t="s">
-        <v>433</v>
+        <v>328</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="B103" t="s">
-        <v>426</v>
+        <v>325</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="B104" t="s">
-        <v>436</v>
+        <v>329</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="B105" t="s">
-        <v>438</v>
+        <v>330</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="B106" t="s">
-        <v>440</v>
+        <v>331</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="B107" t="s">
-        <v>442</v>
+        <v>332</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="B108" t="s">
-        <v>385</v>
+        <v>309</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="B109" t="s">
-        <v>445</v>
+        <v>333</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="B110" t="s">
-        <v>447</v>
+        <v>334</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>448</v>
+        <v>377</v>
       </c>
       <c r="B111" t="s">
-        <v>447</v>
+        <v>334</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>449</v>
+        <v>378</v>
       </c>
       <c r="B112" t="s">
-        <v>447</v>
+        <v>334</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>450</v>
+        <v>379</v>
       </c>
       <c r="B113" t="s">
-        <v>403</v>
+        <v>317</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>451</v>
+        <v>380</v>
       </c>
       <c r="B114" t="s">
-        <v>452</v>
+        <v>335</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>453</v>
+        <v>381</v>
       </c>
       <c r="B115" t="s">
-        <v>454</v>
+        <v>336</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>455</v>
+        <v>382</v>
       </c>
       <c r="B116" t="s">
-        <v>456</v>
+        <v>337</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>457</v>
+        <v>383</v>
       </c>
       <c r="B117" t="s">
-        <v>458</v>
+        <v>338</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>459</v>
+        <v>384</v>
       </c>
       <c r="B118" t="s">
-        <v>460</v>
+        <v>339</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>461</v>
+        <v>385</v>
       </c>
       <c r="B119" t="s">
-        <v>462</v>
+        <v>340</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>463</v>
+        <v>386</v>
       </c>
       <c r="B120" t="s">
-        <v>464</v>
+        <v>341</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>465</v>
+        <v>387</v>
       </c>
       <c r="B121" t="s">
-        <v>466</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>

--- a/studyflow.xlsx
+++ b/studyflow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\puszt\Downloads\StudyFlow_GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCA89EA-EAF3-48B6-8C12-57B9D04F8487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1000054D-D5F7-4897-84C3-69149FB44BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,10 +17,21 @@
     <sheet name="words" sheetId="1" r:id="rId2"/>
     <sheet name="jog" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1058,371 +1069,371 @@
     <t>Tanács</t>
   </si>
   <si>
-    <t>Melyik kifejezés hiányzik? Ennek központi ________ a munkamegosztás, mely a közigazgatási szervek által elvégzendő feladatok és az ellátásukra hivatott szervezetek tagolását jelenti.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A NAV hatásköre ________ kiterjed az adóhátralék bankszámláról történő letiltására, adóbírság kivetésére.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Jegyezzük meg jól tehát, hogy ________ nélkül egy közigazgatási szerv feladatait nem képes hatékonyan ellátni!  Az illetékesség az adott hatóság földrajzi értelemben vett működési területét határozza meg.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A KÖZIGAZGATÁSI SZERV MUNKASZERVEZETE A közigazgatási ________ jellemzője önálló munkaszervezet, hivatal működtetése, amelynek élén egyszemélyi felelős vezető (hivatalvezető) áll.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A közintézetek ________ mindenekelőtt a tulajdonosi jogokat gyakorló (alapító) fenntartóval szemben biztosítja a jogi szabályozás.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Ezáltal a ________ hatásköre lesz a szolgáltatási jogviszony keretében az intézeti ellátottal összefüggésben döntéseket hozni, és ezek végrehatásáról gondoskodni.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? Ezen belül a vezetőknek is ________ további vezetői és a beosztottaknak is lehetnek beosztottjaik, ugyanakkor aki nem vezető és nem beosztott, az nem tartozik a rendszerbe: kívülálló (ilyen például az ügyfél).</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A centralizáció mint ________ azt jelenti, hogy egy meghatározott szerv a közigazgatás szervezetének csúcsán helyezkedik el, s az irányítás innen történik.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A kirendeltség nem ________ önálló feladatés hatáskörrel rendelkező területi szervnek, csak az adott hatóság területileg kihelyezett belső szervezeti egységének.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Az integráció ________, a részeknek egymáshoz illeszkedését jelenti, bizonyos értelemben a közigazgatás hierarchikusságát és centralizáltságát finomító, működését egységesítő elv.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? Az ellenőrzési ________ önálló gyakorlására nemcsak szervek közötti ún. belső viszonyban, hanem közigazgatási szerv és ügyfél között is találunk példákat (ezt nevezzük külső ellenőrzésnek).</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Megjegyezzük, hogy egyes ________ feladatok ellátása csak névlegesen valósul meg járási szinten, ugyanis számos ügykörben nem minden járási hivatal rendelkezik hatáskörrel.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Magyarországon – sok más ________ államhoz hasonlóan – a közigazgatásinak tekinthető feladatokat alapvetően az állam két szervezeti alrendszere, államigazgatási és önkormányzati szervek valósítják meg.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? Ebben a részben ________ az egyes alrendszerek működésének főbb kapcsolódási pontjait.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A középszinten belül a ________ igazgatás párhuzamos felépítésű, azaz önkormányzati és államigazgatási szervek egyaránt megtalálhatóak.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Miniszterelnöknek ________ minden olyan személy, aki  büntetlen előéletű,  rendelkezik magyar állampolgársággal, és  az országgyűlési képviselők választásán passzív választójoga van (azaz választható).</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A miniszter a ________ előírt feladatés hatáskörében önállóan jár el, és ezért felelősséggel tartozik (pl. az Országgyűlésben interpellálható).</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A járási ________ az a büntetlen előéletű, cselekvőképes és nagykorú magyar állampolgár nevezhető ki, aki felsőfokú végzettséggel és legalább 5 év közigazgatási gyakorlattal rendelkezik.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? B) IRÁNYÍTÁS – Az ________ hierarchikus, alá-fölérendeltségi kapcsolatban álló közigazgatási szervek közötti hatalmi viszonyt irányításnak nevezzük.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A HELYI SZINT Magyarország ________ a települések típusai a következők: község, nagyközség, város, járásszékhely város, megyei jogú város, főváros és 23 kerülete.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Lényeges elem ________ a szolgáltató jellegű közigazgatás számára az ügyfél-közeliség érvényesülése.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Ez azt jelenti, hogy a kormányon belül csak a ________ az Országgyűlés által közvetlenül választott politikai vezető, vagyis a miniszterelnöknek van kormánya, nem pedig a kormánynak miniszterelnöke.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Ez azt jelenti, hogy a miniszterelnök ________ függ, elfogadja-e azt, vagy sem.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A szakpolitikai ________ feladata az adott minisztériumhoz tartozó egyes szakterületi érdekek érvényesítése.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A bizalomvesztés miatt ________ tisztviselő jogosult végkielégítésre és 2 hónap felmentési idő letöltésére. c) Alkalmatlanság.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Vannak ________ a közigazgatásban, akik elvileg különböző területeken is képesek megállni a helyüket, őket nevezzük generalistáknak, ellentétben az egy területre szakosodott specialistákkal.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Ebbe a körbe tartozik a politikai ________ és főtanácsadók fizetésének megállapítása a központi államigazgatásban.  Vezetői munkakörök létesítése.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A fokozott ________ abban áll, hogy több bűncselekmény, mint például az emberölés vagy az emberrablás súlyosabban minősül, ha hivatalos személy sérelmére követik el.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Azt jelenti, hogy a beosztott ________ a vezető által vallott értékekkel, célokkal, és munkáját ezek alapján végzi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? A törvény úgy ________, hogy a tisztviselő köteles felettese utasításait végrehajtani.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? TÖRVÉNYESSÉGI ________ JOGKÖRÖK – A megyei kormányhivatal vezetőjének feladata a helyi és nemzetiségi önkormányzatok törvényességi felügyelete.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? Ilyen szervnek ________ a Gazdasági Versenyhivatal Versenytanácsa, vagy a Közbeszerzési Döntőbizottság.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? Ilyen a Nemzeti ________ Testület (feladata a Magyar Szabványok /MSZ/ előírásainak meghatározása és közzététele).</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? A gazdasági ________ feladata, hogy előmozdítsák a gazdaság fejlődését és szerveződését, a piaci magatartás tisztességét, a gazdasági tevékenységet folytatók általános, együttes érdekeinek érvényesítését.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A közigazgatás ________ joga szabályozza a közigazgatási szervek formáit, a szervek belső felépítésének rendjét, külső – akár a közigazgatáson belüli, akár a közigazgatáson kívüli – kapcsolati rendszerét.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A közigazgatás ________ joga A közigazgatás szervezetrendszerét meghatározó joganyag A közigazgatási szervek csoportosítása szervezeti jogi szempontból A közigazgatás két nagy alrendszere: 1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? A 2012. szeptember 1-jén ________ lépett nemzeti felsőoktatásról szóló törvény biztosítja az intézményalapítás szabadságát.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A rektor ________ és képviseli az intézményt, egyben a szenátus elnöke is, így hatásköre a szenátus döntéseinek előkészítésére és végrehajtására is kiterjed.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A kancellár ________ és felmentésére a miniszterelnök jogosult.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? A kancellári ________ e döntések érvényességének, illetve hatálybalépésének feltétele, tehát a kancellár széleskörű vétójoggal rendelkezik egyes döntések meghozatala során.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Az igazgatási ________ a szervezetek (köztük a közigazgatási szerveknek is) olyan tudatos, tervszerű tevékenysége, amely biztosítja a szervezet céljainak eléréséhez szükséges személyi és dologi feltételeket, valamint a munka összhangját.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? KÖZIGAZGATÁSI SZERV ÖNÁLLÓ ________ EGYSÉGE – A közigazgatási szerv önálló szervezeti egysége ezzel szemben kizárólag közigazgatási jogképességgel rendelkezik, azaz önálló feladatköre van, amelynek részeként döntéseket hozhat, és azok betartatására nézve intézkedéseket tehet.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Ez utóbbi ________ ún. utólagos normakontroll eljárás indítványozására jogosult. (B) ÁLLAMI SZÁMVEVŐSZÉK – Az ÁSZ kizárólag az Országgyűlésnek alárendelt legfőbb pénzügyi ellenőrző szerv, ellenőrzéseit célszerűségi, eredményességi és törvényességi szempontok szerint végzi.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A közigazgatási ügyekben ________ bíróságok hatásköre arra terjed ki, hogy az ügyfél keresete alapján megvizsgálják egy egyedi hatósági ügyben hozott közigazgatási határozat (döntés) jogszerűségét, és törvénysértés esetén megsemmisítsék vagy megváltoztassák azt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? Az Önkormányzati ________ jogosult az önkormányzat képviselő-testülete (közgyűlése) által elfogadott rendeletet megsemmisíteni, ha az magasabb szintű jogszabállyal ellentétes, vagy megállapíthatja a helyi önkormányzat jogalkotási kötelezettségének elmulasztását is.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? 2.1 A jogforrások ________ – A közjogi szervezetszabályozó eszközök A jogalkotásról szóló 2010. évi CXXX. törvény (Jat.) 1. § (1) bek.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? E törvény ________ a) a jogszabályokra, valamint b) a normatív határozatra és normatív utasításra (a továbbiakban együtt: közjogi szervezetszabályozó eszköz) terjed ki.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? A közjogi ________ eszközben jogszabály rendelkezése nem ismételhető meg.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? 2.1 A jogforrások – Az EU jog ________ • A közösségi jog – sui generis jogrend = különbözik a tagállamok jogrendszerétől és a nemzetközi közjogtól.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A közösségi ________ nemcsak a tagállamok, hanem az uniós természetes és jogi személyek is alanyai.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? 2.2 A jogszabályok ________ A jogszabály hatálya - a jogszabály alkalmazhatósága.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Négy típusa a) ________ (földrajzi) hatály b) személyi (alanyi) hatály c) Időbeli hatály d) tárgyi hatály (alkalmazási kör). - Jat.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Fejezet 2.2 A ________ hatálya - A jogszabály területi hatálya – Hol kell/lehet alkalmazni?</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Helyi jogszabályok - Jat 6. § (1) – • A ________ területi hatálya Magyarország területére, az önkormányzati rendelet területi hatálya a helyi önkormányzat közigazgatási területére terjed ki.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma Az állam ________ (Georg Jellinek – Általános államtan) – az állam közjogi fogalmának ismérvei – az államiság feltételei: 1.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma – ________ Államforma – Kormányforma - Államszerkezet • Államforma – a közhatalom gyakorlásának módja 1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma - ________ Kormányforma – a törvényhozó és végrehajtó hatalom viszonya, a kormányzati hatalom gyakorlása 1.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma - ________ népesség - állampolgárság Állampolgárság szabályozási kérdései - Keletkezés 1.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Ezen felül speciális ________ minősül a főváros, ahol a koncentrált lakosságszám miatt kerületi hivatalok alakultak.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Az elnökség ________ a küldöttgyűlések közötti időszakban a gazdasági kamara működésének irányítása.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A KORMÁNY ________ HATÁSKÖRE A kormány a maga feladatkörében rendeleteket bocsát ki, és normatív határozatokat hoz, amelyeket a miniszterelnök ír alá.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A MINISZTEREK ________ HATÁSKÖRE A kormány tagjai jogalkotási hatáskörrel rendelkeznek, feladatuk ellátása körében rendeleteket adhatnak ki.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Amennyiben a ________ határidő eredménytelenül letelt, a kormányhivatal vezetője jogosult közvetlenül is összehívni a képviselő-testület ülését.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A közmeghallgatás ________ ülésnek minősül, ezért azon a települési képviselő-testület tagjai határozatképes létszámban kötelesek megjelenni.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? A HELYI NÉPSZAVAZÁS Helyi ________ minősül területi hatáskör alapján az a referendum, melyet egy településen vagy településrészen bonyolítanak le.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Az önkormányzati ________ részletesen rendezi az első két területszervezési kérdés kezdeményezésének a feltételeit, a végleges döntés pedig a köztársasági elnök hatáskörébe tartozik.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Természetesen a „________ felhasználás” elsősorban az önkormányzatok kötelező és fakultatív feladatainak ellátását jelenti, hiszen a vállalkozói tevékenység nem veszélyeztetheti ezek finanszírozását.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Feladata a helyi ________ rendelkezésére álló források szabályszerű, gazdaságos, hatékony és eredményes felhasználásának ellenőrzése.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? A nemzetiségi ________ használatába kell átadni a helyi önkormányzat tulajdonában levő, de a nemzetiségi önkormányzat feladatés hatásköre ellátásához szükséges vagyontárgyakat (pl. irodahelyiség).</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? Ezzel biztosítja az adott szolgáltatáshoz való ________ hozzáférés lehetőségét és finanszírozását.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Az Ákr. biztosítja, hogy a közigazgatási eljárásban ________ szóban és írásban mindenki használhassa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? Eljáró ________, mely esetben az érdemi döntés meghozatala a feladata.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A hatáskör azt ________ meg, hogy egy ügyben milyen típusú és szintű szerv jogosult és egyben köteles döntést hozni.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? Ezeket nem ________ határozatoknak nevezzük. a) Az egyszerűsített határozatokban a jogorvoslatra való figyelmeztetés és a határozat indokolása mellőzhető.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Feladata, hogy az ________ tartózkodási helyét 15 napon belül lehetőség szerint felkutassa, és a határozatot számára átadja.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A közigazgatási döntésekkel ________ jogorvoslatok típusai a következők: a) az ügyfél kérelme alapján kezdeményezett eljárások; b) a hivatalból lefolytatható döntés-felülvizsgálati eljárások.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Ezeket a ________ egyedi ügyben hozott hatósági határozatoknak nevezzük.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? A módosítás-visszavonási ________ lefolytatására a hatóság csak egy alkalommal, a határozat közlésétől számított egy éven belül jogosult.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? A jog fogalma – A jog ________ más normarendszerekhez Főbb társadalmi normarendszerek • Jog • Erkölcs • Szokás • Vallás 1.1.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A jog fogalma • ________ (jogalanyok) viselkedésére vonatkozó • az állam által alkotott, de /vagy/ legalább az állam által elismert és • az állam által végső soron kikényszerített • kötelező magatartási szabályok összessége.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A jog fogalma – A jog ________ funkciói • Konfliktusfeloldás • Reguláció • Integráció • Nevelő, szociális funkció • Hatalmi, ideológiai funkció 1.1.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Az Ákr. rendelkezései szerint ________ joggal rendelkezik az ügyfél, valamint az, akire nézve a határozat rendelkezést tartalmaz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? Ugyancsak ________ bevételnek minősül az adóbeszedés során kivetett bírságok és késedelmi pótlékok összege is.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? A fővárosi ________ és a kerületi önkormányzatokat megillető bevételek megosztási arányáról külön törvény rendelkezik.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Ha az ügyfél nem ________ eljárási képességgel, vagy ügyei vitelében akadályozott, képviseletet vehet igénybe.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A támogató ________ jogosultsága azonban korlátozott, az általa támogatott személy helyett például nyilatkozattételre nem jogosult.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? AZ ÜGYFÉL JOGAI A ________ ELJÁRÁSBAN – Az ügyfél a következő főbb jogokkal rendelkezik az eljárás során.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? A jog fogalma – A ________ normarendszerek A társadalmi normák (normarendszerek) • célja az ismétlődő társadalmi jelenségek befolyásolása = szabályozás • előírják az általánosan követendőt és a helyesnek vélt magatartást • Közös sajátosságaik: a) Tartósság igénye: időben tartósan érvényesülnek.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A jog fogalma – A jog ________ más normarendszerekhez Főbb társadalmi normarendszerek A vallás • A vallási norma, mint magatartásszabály általában a mindennapi életben beolvad a jogba, az erkölcsbe vagy a szokásba • Ezek közül valamelyik normájaként jelenik meg 1.1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? A jog fogalma – A ________ szemben támasztott követelmények • Általános • Közzétett = nyilvános, megismerhető • Jövőbeli cselekvésre irányuló • Világos, egyértelmű • Ellentmondásmentes • Lehetségest követel • Bizonyos stabilitással rendelkezik • A kinyilvánított szabály és a hivatalos cselekvés egyezést mutat.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Anyagi jogi norma – Alaki jogi norma (________ norma) 1.4 A jogviszony Fogalma: a jogviszony a jog által szabályozott társadalmi viszony.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A zálogjog, a ________ jogok. d) Kötelmi jog: szerződések közös szabályai (általános rész) és egyes szerződések (különös rész).</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? Végintézkedésen ________ és a törvényen alapuló öröklés rendje. f) A szellemi alkotások joga: szerzői jog (a szerző személyhez fűződő és vagyoni jogai).</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Kártérítési ________. e) Öröklési jog: a meghalt személy jogutódlása.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? 2.1 A jogforrások ________ és típusai M A G Y A R O R S Z Á G ALKOTMÁNYOZÁS Országgyűlés Alaptörvény I.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Iparjogvédelem (________ megoldások, grafikailag ábrázolható jelzések alkotóinak jogai, szabadalmak, formatervezési minták, védjegyek).</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? 2.1 A jogforrások ________ – a kormányrendelet Alaptörvény 15. cikk • (3) Feladatkörében eljárva a Kormány törvényben nem szabályozott tárgykörben, illetve törvényben kapott felhatalmazás alapján rendeletet alkot.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A jogforrások ________ – MNB rendelet Alaptörvény 41. cikk (5) A Magyar Nemzeti Bank elnöke törvényben kapott felhatalmazás alapján, törvényben meghatározott feladatkörében rendeletet ad ki, amely törvénnyel nem lehet ellentétes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? A felek közös megegyezéssel el is ________ a jogszabályi rendelkezésektől, amíg valamilyen imperatív jellegű jogszabályba nem ütközik magatartásuk.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Alanyainak a ________ széles döntési jellemző. szabadságot biztosítanak.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Mikortól? – ________ lépés • A jogszabály saját maga határozza meg • Más jogszabály határozza meg Meddig?</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Az állam - 3.1 Az állam fogalma - Az állam ________ Államszervezet – egy adott állam szerveinek összessége, amely révén az állam gyakorolja hatalmát, teljesíti céljait, ellátja feladatait.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A tisztviselő ________ annak a döntésnek a hatékony végrehajtása, amit a politikus hozott /Woodrow Wilson/ = a kormányzás és a közigazgatás szétválasztása.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A közigazgatás ________ Negatív fogalommeghatározás : mi nem a közigazgatás? • Magáncselekvések – Közcselekvések - Az igazgatási tevékenység (szervezeti tevékenység) végezhető magán (pl. üzleti) és állami szervezeti keretek között (= közigazgatás) • Közcselekvések, ami nem közigazgatás - törvényalkotás - igazságszolgáltatás - politika - kormányzás 1.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A közigazgatás ________ Negatív definíció A közigazgatás: az állam saját jogrendjének uralma alatt végbemenő azon állami ténykedés, amely az igazságszolgáltatás céljaitól különböző összes egyéb állami cél megvalósítását szolgálja. – Otto Mayer /1846 – 1924/ 1.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A közigazgatási jog fogalma és ________ Közjog (pl.) Magánjog (pl.) Alkotmányjog Polgári jog Közigazgatási jog Családjog Pénzügyi jog Kereskedelmi (gazdasági) Büntetőjog jog Büntetővégrehajtási jog Eljárásjogok Vegyes jogágak (pl.): munkajog, agrárjog 2.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A közigazgatási jog fogalma és ________ – a közigazgatási jog forrásai • Alaptörvény (?) • Törvények - A közigazgatás szervezete Jellemző: - Eljárási törvények • Rendeleti jog túlsúlya - Ágazati törvények • Nem jogszabályi jog • Rendeletek túlsúlya - Eredeti • Heterogenitás - Származékos - Önkormányzati rendeletek (!) • Alacsonyabb szintű jogforrások 3.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A közigazgatás, mint ________ 4.2 Közigazgatási szerv, közigazgatási szervezet A szervezetrendszer • A jogi szabályozás sem a szervezetrendszer, sem a rendszer fogalmát nem határozza meg.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? A közigazgatás, mint ________ 4.2 Közigazgatási szerv, közigazgatási szervezet • A közigazgatási szerv önállósága (jogi értelemben) = jogosult önállóan cselekedni. • Az önálló cselekvést az önálló hatáskör teszi lehetővé.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? A rendszer ________ fogalma: egymással funkcionálisan kapcsolatban álló, a környezettől e kapcsolatok és a kapcsolatrendszernek a környezet számára végzett funkciója által elhatároltható elemek összessége. • A közigazgatás szervezet és egyben rendszer. • Szervezetként az államszervezet része.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? Szakmai ________ elvek 2.1 Különös hatáskör – általános hatáskör 2.2 Ágazati elv – funkcionális elv 3.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? Rendszerként az állam ________ a része. • A közigazgatás viszonylag önállónak nevezhető rendszerekből áll (a közigazgatás alrendszerei).</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? Jogi személyiséggel nem rendelkező ________ Akkor képes jogokat szerezni és kötelezettségeket vállalni, ha jogszabály így rendelkezik = polgári jogi jogalanyisággal ruházza fel.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? 7. § (1) bek. • Minden közigazgatási szerv, amely ________ szerv, egyúttal polgárjogi jogi személyiséggel is rendelkezik, de nem minden közigazgatási szerv költségvetési szerv 2.2 2.2 Egyéb: külön – általában az adott szervet létrehozó - jogszabály rendelkezhet arról, hogy egy szerv polgárjogi jogi személy. - Pl.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? A közigazgatási jog alanyai - Kinek, ________ a magatartását szabályozza a jog?</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A közigazgatási jog alanyai Cél: a közigazgatási jog ________ a megismertetése Közigazgatási jogi jogalanyiság Polgári jogi jogalanyiság 6.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? Az ember, mint jogalany ________ személy „Minden ember jogképes: jogai és kötelezettségei lehetnek.” – Ptk.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? A szervezeti jog ________: viszonylag elkülönült joganyag a közigazgatási jogon belül, a közigazgatási jog egyik részterülete.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Melyik kifejezés hiányzik? Település • Az ________ területe településekre tagozódik. • Az ország teljes területe, valamennyi pontja közigazgatásilag egy (valamely) településhez tartozik, ami lehet - község, ezen belül nagyközség [Mötv.</t>
-  </si>
-  <si>
-    <t>Melyik kifejezés hiányzik? A közigazgatás ________ joga A közigazgatási szerveket és szervezetüket, valamint feladatés hatáskörüket a jogi szabályozás, elsősorban jogszabályok hozzák létre és alakítják.</t>
+    <t>Ennek központi ________ a munkamegosztás, mely a közigazgatási szervek által elvégzendő feladatok és az ellátásukra hivatott szervezetek tagolását jelenti.</t>
+  </si>
+  <si>
+    <t>A NAV hatásköre ________ kiterjed az adóhátralék bankszámláról történő letiltására, adóbírság kivetésére.</t>
+  </si>
+  <si>
+    <t>Jegyezzük meg jól tehát, hogy ________ nélkül egy közigazgatási szerv feladatait nem képes hatékonyan ellátni!  Az illetékesség az adott hatóság földrajzi értelemben vett működési területét határozza meg.</t>
+  </si>
+  <si>
+    <t>A KÖZIGAZGATÁSI SZERV MUNKASZERVEZETE A közigazgatási ________ jellemzője önálló munkaszervezet, hivatal működtetése, amelynek élén egyszemélyi felelős vezető (hivatalvezető) áll.</t>
+  </si>
+  <si>
+    <t>A közintézetek ________ mindenekelőtt a tulajdonosi jogokat gyakorló (alapító) fenntartóval szemben biztosítja a jogi szabályozás.</t>
+  </si>
+  <si>
+    <t>Ezáltal a ________ hatásköre lesz a szolgáltatási jogviszony keretében az intézeti ellátottal összefüggésben döntéseket hozni, és ezek végrehatásáról gondoskodni.</t>
+  </si>
+  <si>
+    <t>Ezen belül a vezetőknek is ________ további vezetői és a beosztottaknak is lehetnek beosztottjaik, ugyanakkor aki nem vezető és nem beosztott, az nem tartozik a rendszerbe: kívülálló (ilyen például az ügyfél).</t>
+  </si>
+  <si>
+    <t>A centralizáció mint ________ azt jelenti, hogy egy meghatározott szerv a közigazgatás szervezetének csúcsán helyezkedik el, s az irányítás innen történik.</t>
+  </si>
+  <si>
+    <t>A kirendeltség nem ________ önálló feladatés hatáskörrel rendelkező területi szervnek, csak az adott hatóság területileg kihelyezett belső szervezeti egységének.</t>
+  </si>
+  <si>
+    <t>Az integráció ________, a részeknek egymáshoz illeszkedését jelenti, bizonyos értelemben a közigazgatás hierarchikusságát és centralizáltságát finomító, működését egységesítő elv.</t>
+  </si>
+  <si>
+    <t>B) IRÁNYÍTÁS – Az ________ hierarchikus, alá-fölérendeltségi kapcsolatban álló közigazgatási szervek közötti hatalmi viszonyt irányításnak nevezzük.</t>
+  </si>
+  <si>
+    <t>Az ellenőrzési ________ önálló gyakorlására nemcsak szervek közötti ún. belső viszonyban, hanem közigazgatási szerv és ügyfél között is találunk példákat (ezt nevezzük külső ellenőrzésnek).</t>
+  </si>
+  <si>
+    <t>Megjegyezzük, hogy egyes ________ feladatok ellátása csak névlegesen valósul meg járási szinten, ugyanis számos ügykörben nem minden járási hivatal rendelkezik hatáskörrel.</t>
+  </si>
+  <si>
+    <t>A HELYI SZINT Magyarország ________ a települések típusai a következők: község, nagyközség, város, járásszékhely város, megyei jogú város, főváros és 23 kerülete.</t>
+  </si>
+  <si>
+    <t>Magyarországon – sok más ________ államhoz hasonlóan – a közigazgatásinak tekinthető feladatokat alapvetően az állam két szervezeti alrendszere, államigazgatási és önkormányzati szervek valósítják meg.</t>
+  </si>
+  <si>
+    <t>Ebben a részben ________ az egyes alrendszerek működésének főbb kapcsolódási pontjait.</t>
+  </si>
+  <si>
+    <t>Lényeges elem ________ a szolgáltató jellegű közigazgatás számára az ügyfél-közeliség érvényesülése.</t>
+  </si>
+  <si>
+    <t>A középszinten belül a ________ igazgatás párhuzamos felépítésű, azaz önkormányzati és államigazgatási szervek egyaránt megtalálhatóak.</t>
+  </si>
+  <si>
+    <t>Miniszterelnöknek ________ minden olyan személy, aki  büntetlen előéletű,  rendelkezik magyar állampolgársággal, és  az országgyűlési képviselők választásán passzív választójoga van (azaz választható).</t>
+  </si>
+  <si>
+    <t>Ez azt jelenti, hogy a kormányon belül csak a ________ az Országgyűlés által közvetlenül választott politikai vezető, vagyis a miniszterelnöknek van kormánya, nem pedig a kormánynak miniszterelnöke.</t>
+  </si>
+  <si>
+    <t>A miniszter a ________ előírt feladatés hatáskörében önállóan jár el, és ezért felelősséggel tartozik (pl. az Országgyűlésben interpellálható).</t>
+  </si>
+  <si>
+    <t>Ez azt jelenti, hogy a miniszterelnök ________ függ, elfogadja-e azt, vagy sem.</t>
+  </si>
+  <si>
+    <t>A szakpolitikai ________ feladata az adott minisztériumhoz tartozó egyes szakterületi érdekek érvényesítése.</t>
+  </si>
+  <si>
+    <t>A járási ________ az a büntetlen előéletű, cselekvőképes és nagykorú magyar állampolgár nevezhető ki, aki felsőfokú végzettséggel és legalább 5 év közigazgatási gyakorlattal rendelkezik.</t>
+  </si>
+  <si>
+    <t>A bizalomvesztés miatt ________ tisztviselő jogosult végkielégítésre és 2 hónap felmentési idő letöltésére. c) Alkalmatlanság.</t>
+  </si>
+  <si>
+    <t>Vannak ________ a közigazgatásban, akik elvileg különböző területeken is képesek megállni a helyüket, őket nevezzük generalistáknak, ellentétben az egy területre szakosodott specialistákkal.</t>
+  </si>
+  <si>
+    <t>Ebbe a körbe tartozik a politikai ________ és főtanácsadók fizetésének megállapítása a központi államigazgatásban.  Vezetői munkakörök létesítése.</t>
+  </si>
+  <si>
+    <t>A fokozott ________ abban áll, hogy több bűncselekmény, mint például az emberölés vagy az emberrablás súlyosabban minősül, ha hivatalos személy sérelmére követik el.</t>
+  </si>
+  <si>
+    <t>Azt jelenti, hogy a beosztott ________ a vezető által vallott értékekkel, célokkal, és munkáját ezek alapján végzi.</t>
+  </si>
+  <si>
+    <t>A törvény úgy ________, hogy a tisztviselő köteles felettese utasításait végrehajtani.</t>
+  </si>
+  <si>
+    <t>TÖRVÉNYESSÉGI ________ JOGKÖRÖK – A megyei kormányhivatal vezetőjének feladata a helyi és nemzetiségi önkormányzatok törvényességi felügyelete.</t>
+  </si>
+  <si>
+    <t>Ezen felül speciális ________ minősül a főváros, ahol a koncentrált lakosságszám miatt kerületi hivatalok alakultak.</t>
+  </si>
+  <si>
+    <t>Ilyen szervnek ________ a Gazdasági Versenyhivatal Versenytanácsa, vagy a Közbeszerzési Döntőbizottság.</t>
+  </si>
+  <si>
+    <t>Ilyen a Nemzeti ________ Testület (feladata a Magyar Szabványok /MSZ/ előírásainak meghatározása és közzététele).</t>
+  </si>
+  <si>
+    <t>A gazdasági ________ feladata, hogy előmozdítsák a gazdaság fejlődését és szerveződését, a piaci magatartás tisztességét, a gazdasági tevékenységet folytatók általános, együttes érdekeinek érvényesítését.</t>
+  </si>
+  <si>
+    <t>Az elnökség ________ a küldöttgyűlések közötti időszakban a gazdasági kamara működésének irányítása.</t>
+  </si>
+  <si>
+    <t>A KORMÁNY ________ HATÁSKÖRE A kormány a maga feladatkörében rendeleteket bocsát ki, és normatív határozatokat hoz, amelyeket a miniszterelnök ír alá.</t>
+  </si>
+  <si>
+    <t>A MINISZTEREK ________ HATÁSKÖRE A kormány tagjai jogalkotási hatáskörrel rendelkeznek, feladatuk ellátása körében rendeleteket adhatnak ki.</t>
+  </si>
+  <si>
+    <t>Amennyiben a ________ határidő eredménytelenül letelt, a kormányhivatal vezetője jogosult közvetlenül is összehívni a képviselő-testület ülését.</t>
+  </si>
+  <si>
+    <t>A közmeghallgatás ________ ülésnek minősül, ezért azon a települési képviselő-testület tagjai határozatképes létszámban kötelesek megjelenni.</t>
+  </si>
+  <si>
+    <t>A HELYI NÉPSZAVAZÁS Helyi ________ minősül területi hatáskör alapján az a referendum, melyet egy településen vagy településrészen bonyolítanak le.</t>
+  </si>
+  <si>
+    <t>Az önkormányzati ________ részletesen rendezi az első két területszervezési kérdés kezdeményezésének a feltételeit, a végleges döntés pedig a köztársasági elnök hatáskörébe tartozik.</t>
+  </si>
+  <si>
+    <t>Természetesen a „________ felhasználás” elsősorban az önkormányzatok kötelező és fakultatív feladatainak ellátását jelenti, hiszen a vállalkozói tevékenység nem veszélyeztetheti ezek finanszírozását.</t>
+  </si>
+  <si>
+    <t>Feladata a helyi ________ rendelkezésére álló források szabályszerű, gazdaságos, hatékony és eredményes felhasználásának ellenőrzése.</t>
+  </si>
+  <si>
+    <t>Ugyancsak ________ bevételnek minősül az adóbeszedés során kivetett bírságok és késedelmi pótlékok összege is.</t>
+  </si>
+  <si>
+    <t>A fővárosi ________ és a kerületi önkormányzatokat megillető bevételek megosztási arányáról külön törvény rendelkezik.</t>
+  </si>
+  <si>
+    <t>A nemzetiségi ________ használatába kell átadni a helyi önkormányzat tulajdonában levő, de a nemzetiségi önkormányzat feladatés hatásköre ellátásához szükséges vagyontárgyakat (pl. irodahelyiség).</t>
+  </si>
+  <si>
+    <t>Ezzel biztosítja az adott szolgáltatáshoz való ________ hozzáférés lehetőségét és finanszírozását.</t>
+  </si>
+  <si>
+    <t>Ha az ügyfél nem ________ eljárási képességgel, vagy ügyei vitelében akadályozott, képviseletet vehet igénybe.</t>
+  </si>
+  <si>
+    <t>A támogató ________ jogosultsága azonban korlátozott, az általa támogatott személy helyett például nyilatkozattételre nem jogosult.</t>
+  </si>
+  <si>
+    <t>AZ ÜGYFÉL JOGAI A ________ ELJÁRÁSBAN – Az ügyfél a következő főbb jogokkal rendelkezik az eljárás során.</t>
+  </si>
+  <si>
+    <t>Az Ákr. biztosítja, hogy a közigazgatási eljárásban ________ szóban és írásban mindenki használhassa.</t>
+  </si>
+  <si>
+    <t>Eljáró ________, mely esetben az érdemi döntés meghozatala a feladata.</t>
+  </si>
+  <si>
+    <t>A hatáskör azt ________ meg, hogy egy ügyben milyen típusú és szintű szerv jogosult és egyben köteles döntést hozni.</t>
+  </si>
+  <si>
+    <t>Ezeket nem ________ határozatoknak nevezzük. a) Az egyszerűsített határozatokban a jogorvoslatra való figyelmeztetés és a határozat indokolása mellőzhető.</t>
+  </si>
+  <si>
+    <t>Feladata, hogy az ________ tartózkodási helyét 15 napon belül lehetőség szerint felkutassa, és a határozatot számára átadja.</t>
+  </si>
+  <si>
+    <t>A közigazgatási döntésekkel ________ jogorvoslatok típusai a következők: a) az ügyfél kérelme alapján kezdeményezett eljárások; b) a hivatalból lefolytatható döntés-felülvizsgálati eljárások.</t>
+  </si>
+  <si>
+    <t>Ezeket a ________ egyedi ügyben hozott hatósági határozatoknak nevezzük.</t>
+  </si>
+  <si>
+    <t>Az Ákr. rendelkezései szerint ________ joggal rendelkezik az ügyfél, valamint az, akire nézve a határozat rendelkezést tartalmaz.</t>
+  </si>
+  <si>
+    <t>A módosítás-visszavonási ________ lefolytatására a hatóság csak egy alkalommal, a határozat közlésétől számított egy éven belül jogosult.</t>
+  </si>
+  <si>
+    <t>A jog fogalma – A jog ________ funkciói • Konfliktusfeloldás • Reguláció • Integráció • Nevelő, szociális funkció • Hatalmi, ideológiai funkció 1.1.</t>
+  </si>
+  <si>
+    <t>A jog fogalma – A jog ________ más normarendszerekhez Főbb társadalmi normarendszerek • Jog • Erkölcs • Szokás • Vallás 1.1.</t>
+  </si>
+  <si>
+    <t>A jog fogalma • ________ (jogalanyok) viselkedésére vonatkozó • az állam által alkotott, de /vagy/ legalább az állam által elismert és • az állam által végső soron kikényszerített • kötelező magatartási szabályok összessége.</t>
+  </si>
+  <si>
+    <t>A jog fogalma – A ________ normarendszerek A társadalmi normák (normarendszerek) • célja az ismétlődő társadalmi jelenségek befolyásolása = szabályozás • előírják az általánosan követendőt és a helyesnek vélt magatartást • Közös sajátosságaik: a) Tartósság igénye: időben tartósan érvényesülnek.</t>
+  </si>
+  <si>
+    <t>A jog fogalma – A jog ________ más normarendszerekhez Főbb társadalmi normarendszerek A vallás • A vallási norma, mint magatartásszabály általában a mindennapi életben beolvad a jogba, az erkölcsbe vagy a szokásba • Ezek közül valamelyik normájaként jelenik meg 1.1.</t>
+  </si>
+  <si>
+    <t>A jog fogalma – A ________ szemben támasztott követelmények • Általános • Közzétett = nyilvános, megismerhető • Jövőbeli cselekvésre irányuló • Világos, egyértelmű • Ellentmondásmentes • Lehetségest követel • Bizonyos stabilitással rendelkezik • A kinyilvánított szabály és a hivatalos cselekvés egyezést mutat.</t>
+  </si>
+  <si>
+    <t>Anyagi jogi norma – Alaki jogi norma (________ norma) 1.4 A jogviszony Fogalma: a jogviszony a jog által szabályozott társadalmi viszony.</t>
+  </si>
+  <si>
+    <t>A zálogjog, a ________ jogok. d) Kötelmi jog: szerződések közös szabályai (általános rész) és egyes szerződések (különös rész).</t>
+  </si>
+  <si>
+    <t>Kártérítési ________. e) Öröklési jog: a meghalt személy jogutódlása.</t>
+  </si>
+  <si>
+    <t>Végintézkedésen ________ és a törvényen alapuló öröklés rendje. f) A szellemi alkotások joga: szerzői jog (a szerző személyhez fűződő és vagyoni jogai).</t>
+  </si>
+  <si>
+    <t>Iparjogvédelem (________ megoldások, grafikailag ábrázolható jelzések alkotóinak jogai, szabadalmak, formatervezési minták, védjegyek).</t>
+  </si>
+  <si>
+    <t>2.1 A jogforrások ________ és típusai M A G Y A R O R S Z Á G ALKOTMÁNYOZÁS Országgyűlés Alaptörvény I.</t>
+  </si>
+  <si>
+    <t>2.1 A jogforrások ________ – a kormányrendelet Alaptörvény 15. cikk • (3) Feladatkörében eljárva a Kormány törvényben nem szabályozott tárgykörben, illetve törvényben kapott felhatalmazás alapján rendeletet alkot.</t>
+  </si>
+  <si>
+    <t>A jogforrások ________ – MNB rendelet Alaptörvény 41. cikk (5) A Magyar Nemzeti Bank elnöke törvényben kapott felhatalmazás alapján, törvényben meghatározott feladatkörében rendeletet ad ki, amely törvénnyel nem lehet ellentétes.</t>
+  </si>
+  <si>
+    <t>Alanyainak a ________ széles döntési jellemző. szabadságot biztosítanak.</t>
+  </si>
+  <si>
+    <t>A felek közös megegyezéssel el is ________ a jogszabályi rendelkezésektől, amíg valamilyen imperatív jellegű jogszabályba nem ütközik magatartásuk.</t>
+  </si>
+  <si>
+    <t>2.1 A jogforrások ________ – A közjogi szervezetszabályozó eszközök A jogalkotásról szóló 2010. évi CXXX. törvény (Jat.) 1. § (1) bek.</t>
+  </si>
+  <si>
+    <t>E törvény ________ a) a jogszabályokra, valamint b) a normatív határozatra és normatív utasításra (a továbbiakban együtt: közjogi szervezetszabályozó eszköz) terjed ki.</t>
+  </si>
+  <si>
+    <t>A közjogi ________ eszközben jogszabály rendelkezése nem ismételhető meg.</t>
+  </si>
+  <si>
+    <t>2.1 A jogforrások – Az EU jog ________ • A közösségi jog – sui generis jogrend = különbözik a tagállamok jogrendszerétől és a nemzetközi közjogtól.</t>
+  </si>
+  <si>
+    <t>A közösségi ________ nemcsak a tagállamok, hanem az uniós természetes és jogi személyek is alanyai.</t>
+  </si>
+  <si>
+    <t>Mikortól? – ________ lépés • A jogszabály saját maga határozza meg • Más jogszabály határozza meg Meddig?</t>
+  </si>
+  <si>
+    <t>2.2 A jogszabályok ________ A jogszabály hatálya - a jogszabály alkalmazhatósága.</t>
+  </si>
+  <si>
+    <t>Négy típusa a) ________ (földrajzi) hatály b) személyi (alanyi) hatály c) Időbeli hatály d) tárgyi hatály (alkalmazási kör). - Jat.</t>
+  </si>
+  <si>
+    <t>Fejezet 2.2 A ________ hatálya - A jogszabály területi hatálya – Hol kell/lehet alkalmazni?</t>
+  </si>
+  <si>
+    <t>Helyi jogszabályok - Jat 6. § (1) – • A ________ területi hatálya Magyarország területére, az önkormányzati rendelet területi hatálya a helyi önkormányzat közigazgatási területére terjed ki.</t>
+  </si>
+  <si>
+    <t>Az állam - 3.1 Az állam fogalma Az állam ________ (Georg Jellinek – Általános államtan) – az állam közjogi fogalmának ismérvei – az államiság feltételei: 1.</t>
+  </si>
+  <si>
+    <t>Az állam - 3.1 Az állam fogalma – ________ Államforma – Kormányforma - Államszerkezet • Államforma – a közhatalom gyakorlásának módja 1.</t>
+  </si>
+  <si>
+    <t>Az állam - 3.1 Az állam fogalma - ________ Kormányforma – a törvényhozó és végrehajtó hatalom viszonya, a kormányzati hatalom gyakorlása 1.</t>
+  </si>
+  <si>
+    <t>Az állam - 3.1 Az állam fogalma - ________ népesség - állampolgárság Állampolgárság szabályozási kérdései - Keletkezés 1.</t>
+  </si>
+  <si>
+    <t>Az állam - 3.1 Az állam fogalma - Az állam ________ Államszervezet – egy adott állam szerveinek összessége, amely révén az állam gyakorolja hatalmát, teljesíti céljait, ellátja feladatait.</t>
+  </si>
+  <si>
+    <t>A tisztviselő ________ annak a döntésnek a hatékony végrehajtása, amit a politikus hozott /Woodrow Wilson/ = a kormányzás és a közigazgatás szétválasztása.</t>
+  </si>
+  <si>
+    <t>A közigazgatás ________ Negatív fogalommeghatározás : mi nem a közigazgatás? • Magáncselekvések – Közcselekvések - Az igazgatási tevékenység (szervezeti tevékenység) végezhető magán (pl. üzleti) és állami szervezeti keretek között (= közigazgatás) • Közcselekvések, ami nem közigazgatás - törvényalkotás - igazságszolgáltatás - politika - kormányzás 1.</t>
+  </si>
+  <si>
+    <t>A közigazgatás ________ Negatív definíció A közigazgatás: az állam saját jogrendjének uralma alatt végbemenő azon állami ténykedés, amely az igazságszolgáltatás céljaitól különböző összes egyéb állami cél megvalósítását szolgálja. – Otto Mayer /1846 – 1924/ 1.</t>
+  </si>
+  <si>
+    <t>A közigazgatási jog fogalma és ________ Közjog (pl.) Magánjog (pl.) Alkotmányjog Polgári jog Közigazgatási jog Családjog Pénzügyi jog Kereskedelmi (gazdasági) Büntetőjog jog Büntetővégrehajtási jog Eljárásjogok Vegyes jogágak (pl.): munkajog, agrárjog 2.</t>
+  </si>
+  <si>
+    <t>A közigazgatási jog fogalma és ________ – a közigazgatási jog forrásai • Alaptörvény (?) • Törvények - A közigazgatás szervezete Jellemző: - Eljárási törvények • Rendeleti jog túlsúlya - Ágazati törvények • Nem jogszabályi jog • Rendeletek túlsúlya - Eredeti • Heterogenitás - Származékos - Önkormányzati rendeletek (!) • Alacsonyabb szintű jogforrások 3.</t>
+  </si>
+  <si>
+    <t>A közigazgatás, mint ________ 4.2 Közigazgatási szerv, közigazgatási szervezet A szervezetrendszer • A jogi szabályozás sem a szervezetrendszer, sem a rendszer fogalmát nem határozza meg.</t>
+  </si>
+  <si>
+    <t>A közigazgatás, mint ________ 4.2 Közigazgatási szerv, közigazgatási szervezet • A közigazgatási szerv önállósága (jogi értelemben) = jogosult önállóan cselekedni. • Az önálló cselekvést az önálló hatáskör teszi lehetővé.</t>
+  </si>
+  <si>
+    <t>A rendszer ________ fogalma: egymással funkcionálisan kapcsolatban álló, a környezettől e kapcsolatok és a kapcsolatrendszernek a környezet számára végzett funkciója által elhatároltható elemek összessége. • A közigazgatás szervezet és egyben rendszer. • Szervezetként az államszervezet része.</t>
+  </si>
+  <si>
+    <t>Szakmai ________ elvek 2.1 Különös hatáskör – általános hatáskör 2.2 Ágazati elv – funkcionális elv 3.</t>
+  </si>
+  <si>
+    <t>Rendszerként az állam ________ a része. • A közigazgatás viszonylag önállónak nevezhető rendszerekből áll (a közigazgatás alrendszerei).</t>
+  </si>
+  <si>
+    <t>Jogi személyiséggel nem rendelkező ________ Akkor képes jogokat szerezni és kötelezettségeket vállalni, ha jogszabály így rendelkezik = polgári jogi jogalanyisággal ruházza fel.</t>
+  </si>
+  <si>
+    <t>7. § (1) bek. • Minden közigazgatási szerv, amely ________ szerv, egyúttal polgárjogi jogi személyiséggel is rendelkezik, de nem minden közigazgatási szerv költségvetési szerv 2.2 2.2 Egyéb: külön – általában az adott szervet létrehozó - jogszabály rendelkezhet arról, hogy egy szerv polgárjogi jogi személy. - Pl.</t>
+  </si>
+  <si>
+    <t>A közigazgatási jog alanyai - Kinek, ________ a magatartását szabályozza a jog?</t>
+  </si>
+  <si>
+    <t>A közigazgatási jog alanyai Cél: a közigazgatási jog ________ a megismertetése Közigazgatási jogi jogalanyiság Polgári jogi jogalanyiság 6.</t>
+  </si>
+  <si>
+    <t>Az ember, mint jogalany ________ személy „Minden ember jogképes: jogai és kötelezettségei lehetnek.” – Ptk.</t>
+  </si>
+  <si>
+    <t>A szervezeti jog ________: viszonylag elkülönült joganyag a közigazgatási jogon belül, a közigazgatási jog egyik részterülete.</t>
+  </si>
+  <si>
+    <t>Település • Az ________ területe településekre tagozódik. • Az ország teljes területe, valamennyi pontja közigazgatásilag egy (valamely) településhez tartozik, ami lehet - község, ezen belül nagyközség [Mötv.</t>
+  </si>
+  <si>
+    <t>A közigazgatás ________ joga A közigazgatási szerveket és szervezetüket, valamint feladatés hatáskörüket a jogi szabályozás, elsősorban jogszabályok hozzák létre és alakítják.</t>
+  </si>
+  <si>
+    <t>A közigazgatás ________ joga szabályozza a közigazgatási szervek formáit, a szervek belső felépítésének rendjét, külső – akár a közigazgatáson belüli, akár a közigazgatáson kívüli – kapcsolati rendszerét.</t>
+  </si>
+  <si>
+    <t>A közigazgatás ________ joga A közigazgatás szervezetrendszerét meghatározó joganyag A közigazgatási szervek csoportosítása szervezeti jogi szempontból A közigazgatás két nagy alrendszere: 1.</t>
+  </si>
+  <si>
+    <t>A 2012. szeptember 1-jén ________ lépett nemzeti felsőoktatásról szóló törvény biztosítja az intézményalapítás szabadságát.</t>
+  </si>
+  <si>
+    <t>A rektor ________ és képviseli az intézményt, egyben a szenátus elnöke is, így hatásköre a szenátus döntéseinek előkészítésére és végrehajtására is kiterjed.</t>
+  </si>
+  <si>
+    <t>A kancellár ________ és felmentésére a miniszterelnök jogosult.</t>
+  </si>
+  <si>
+    <t>A kancellári ________ e döntések érvényességének, illetve hatálybalépésének feltétele, tehát a kancellár széleskörű vétójoggal rendelkezik egyes döntések meghozatala során.</t>
+  </si>
+  <si>
+    <t>Az igazgatási ________ a szervezetek (köztük a közigazgatási szerveknek is) olyan tudatos, tervszerű tevékenysége, amely biztosítja a szervezet céljainak eléréséhez szükséges személyi és dologi feltételeket, valamint a munka összhangját.</t>
+  </si>
+  <si>
+    <t>KÖZIGAZGATÁSI SZERV ÖNÁLLÓ ________ EGYSÉGE – A közigazgatási szerv önálló szervezeti egysége ezzel szemben kizárólag közigazgatási jogképességgel rendelkezik, azaz önálló feladatköre van, amelynek részeként döntéseket hozhat, és azok betartatására nézve intézkedéseket tehet.</t>
+  </si>
+  <si>
+    <t>Ez utóbbi ________ ún. utólagos normakontroll eljárás indítványozására jogosult. (B) ÁLLAMI SZÁMVEVŐSZÉK – Az ÁSZ kizárólag az Országgyűlésnek alárendelt legfőbb pénzügyi ellenőrző szerv, ellenőrzéseit célszerűségi, eredményességi és törvényességi szempontok szerint végzi.</t>
+  </si>
+  <si>
+    <t>A közigazgatási ügyekben ________ bíróságok hatásköre arra terjed ki, hogy az ügyfél keresete alapján megvizsgálják egy egyedi hatósági ügyben hozott közigazgatási határozat (döntés) jogszerűségét, és törvénysértés esetén megsemmisítsék vagy megváltoztassák azt.</t>
+  </si>
+  <si>
+    <t>Az Önkormányzati ________ jogosult az önkormányzat képviselő-testülete (közgyűlése) által elfogadott rendeletet megsemmisíteni, ha az magasabb szintű jogszabállyal ellentétes, vagy megállapíthatja a helyi önkormányzat jogalkotási kötelezettségének elmulasztását is.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1434,6 +1445,13 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0D0D0D"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
       <charset val="238"/>
     </font>
@@ -1458,11 +1476,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -3060,8 +3079,8 @@
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>343</v>
       </c>
       <c r="B2" t="s">
@@ -3142,7 +3161,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="B12" t="s">
         <v>254</v>
@@ -3150,7 +3169,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B13" t="s">
         <v>255</v>
@@ -3158,7 +3177,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B14" t="s">
         <v>256</v>
@@ -3166,7 +3185,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B15" t="s">
         <v>257</v>
@@ -3174,7 +3193,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B16" t="s">
         <v>258</v>
@@ -3182,7 +3201,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B17" t="s">
         <v>259</v>
@@ -3190,7 +3209,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B18" t="s">
         <v>260</v>
@@ -3198,7 +3217,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B19" t="s">
         <v>261</v>
@@ -3206,7 +3225,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B20" t="s">
         <v>262</v>
@@ -3214,7 +3233,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B21" t="s">
         <v>263</v>
@@ -3222,7 +3241,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B22" t="s">
         <v>264</v>
@@ -3230,7 +3249,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B23" t="s">
         <v>265</v>
@@ -3238,7 +3257,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B24" t="s">
         <v>266</v>
@@ -3246,7 +3265,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B25" t="s">
         <v>267</v>
@@ -3310,7 +3329,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>401</v>
+        <v>374</v>
       </c>
       <c r="B33" t="s">
         <v>275</v>
@@ -3318,7 +3337,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B34" t="s">
         <v>252</v>
@@ -3326,7 +3345,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B35" t="s">
         <v>276</v>
@@ -3334,7 +3353,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B36" t="s">
         <v>277</v>
@@ -3342,7 +3361,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="B37" t="s">
         <v>278</v>
@@ -3350,7 +3369,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="B38" t="s">
         <v>279</v>
@@ -3358,7 +3377,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="B39" t="s">
         <v>279</v>
@@ -3366,7 +3385,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="B40" t="s">
         <v>280</v>
@@ -3374,7 +3393,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>406</v>
+        <v>382</v>
       </c>
       <c r="B41" t="s">
         <v>281</v>
@@ -3382,7 +3401,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="B42" t="s">
         <v>282</v>
@@ -3390,7 +3409,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>408</v>
+        <v>384</v>
       </c>
       <c r="B43" t="s">
         <v>283</v>
@@ -3398,7 +3417,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>409</v>
+        <v>385</v>
       </c>
       <c r="B44" t="s">
         <v>284</v>
@@ -3406,7 +3425,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="B45" t="s">
         <v>285</v>
@@ -3414,7 +3433,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>425</v>
+        <v>387</v>
       </c>
       <c r="B46" t="s">
         <v>286</v>
@@ -3422,7 +3441,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>426</v>
+        <v>388</v>
       </c>
       <c r="B47" t="s">
         <v>287</v>
@@ -3430,7 +3449,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>411</v>
+        <v>389</v>
       </c>
       <c r="B48" t="s">
         <v>285</v>
@@ -3438,7 +3457,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>412</v>
+        <v>390</v>
       </c>
       <c r="B49" t="s">
         <v>288</v>
@@ -3446,7 +3465,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>427</v>
+        <v>391</v>
       </c>
       <c r="B50" t="s">
         <v>273</v>
@@ -3454,7 +3473,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>428</v>
+        <v>392</v>
       </c>
       <c r="B51" t="s">
         <v>289</v>
@@ -3462,7 +3481,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>429</v>
+        <v>393</v>
       </c>
       <c r="B52" t="s">
         <v>290</v>
@@ -3470,7 +3489,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="B53" t="s">
         <v>291</v>
@@ -3478,7 +3497,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="B54" t="s">
         <v>292</v>
@@ -3486,7 +3505,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="B55" t="s">
         <v>293</v>
@@ -3494,7 +3513,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="B56" t="s">
         <v>294</v>
@@ -3502,7 +3521,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="B57" t="s">
         <v>295</v>
@@ -3510,7 +3529,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="B58" t="s">
         <v>296</v>
@@ -3518,7 +3537,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="B59" t="s">
         <v>297</v>
@@ -3526,7 +3545,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>424</v>
+        <v>401</v>
       </c>
       <c r="B60" t="s">
         <v>298</v>
@@ -3534,7 +3553,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="B61" t="s">
         <v>299</v>
@@ -3542,7 +3561,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="B62" t="s">
         <v>300</v>
@@ -3550,7 +3569,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="B63" t="s">
         <v>301</v>
@@ -3558,7 +3577,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="B64" t="s">
         <v>302</v>
@@ -3566,7 +3585,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="B65" t="s">
         <v>300</v>
@@ -3574,7 +3593,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="B66" t="s">
         <v>301</v>
@@ -3582,7 +3601,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="B67" t="s">
         <v>303</v>
@@ -3590,7 +3609,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="B68" t="s">
         <v>304</v>
@@ -3598,7 +3617,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="B69" t="s">
         <v>305</v>
@@ -3606,7 +3625,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>436</v>
+        <v>411</v>
       </c>
       <c r="B70" t="s">
         <v>306</v>
@@ -3614,7 +3633,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>435</v>
+        <v>412</v>
       </c>
       <c r="B71" t="s">
         <v>307</v>
@@ -3622,7 +3641,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>438</v>
+        <v>413</v>
       </c>
       <c r="B72" t="s">
         <v>308</v>
@@ -3630,7 +3649,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>437</v>
+        <v>414</v>
       </c>
       <c r="B73" t="s">
         <v>309</v>
@@ -3638,7 +3657,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="B74" t="s">
         <v>310</v>
@@ -3646,7 +3665,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="B75" t="s">
         <v>310</v>
@@ -3654,7 +3673,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="B76" t="s">
         <v>311</v>
@@ -3662,7 +3681,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>441</v>
+        <v>418</v>
       </c>
       <c r="B77" t="s">
         <v>312</v>
@@ -3670,7 +3689,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>388</v>
+        <v>419</v>
       </c>
       <c r="B78" t="s">
         <v>310</v>
@@ -3678,7 +3697,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>389</v>
+        <v>420</v>
       </c>
       <c r="B79" t="s">
         <v>313</v>
@@ -3686,7 +3705,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>390</v>
+        <v>421</v>
       </c>
       <c r="B80" t="s">
         <v>314</v>
@@ -3694,7 +3713,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>391</v>
+        <v>422</v>
       </c>
       <c r="B81" t="s">
         <v>315</v>
@@ -3702,7 +3721,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>392</v>
+        <v>423</v>
       </c>
       <c r="B82" t="s">
         <v>316</v>
@@ -3710,7 +3729,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="B83" t="s">
         <v>317</v>
@@ -3718,7 +3737,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>393</v>
+        <v>425</v>
       </c>
       <c r="B84" t="s">
         <v>313</v>
@@ -3726,7 +3745,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>394</v>
+        <v>426</v>
       </c>
       <c r="B85" t="s">
         <v>318</v>
@@ -3734,7 +3753,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>395</v>
+        <v>427</v>
       </c>
       <c r="B86" t="s">
         <v>311</v>
@@ -3742,7 +3761,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>396</v>
+        <v>428</v>
       </c>
       <c r="B87" t="s">
         <v>319</v>
@@ -3750,7 +3769,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>397</v>
+        <v>429</v>
       </c>
       <c r="B88" t="s">
         <v>309</v>
@@ -3758,7 +3777,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
       <c r="B89" t="s">
         <v>320</v>
@@ -3766,7 +3785,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>399</v>
+        <v>431</v>
       </c>
       <c r="B90" t="s">
         <v>321</v>
@@ -3774,7 +3793,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="B91" t="s">
         <v>322</v>
@@ -3782,7 +3801,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="B92" t="s">
         <v>323</v>
@@ -3790,7 +3809,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="B93" t="s">
         <v>278</v>
@@ -3798,7 +3817,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="B94" t="s">
         <v>309</v>
@@ -3806,7 +3825,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="B95" t="s">
         <v>309</v>
@@ -3814,7 +3833,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="B96" t="s">
         <v>324</v>
@@ -3822,7 +3841,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="B97" t="s">
         <v>324</v>
@@ -3830,7 +3849,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="B98" t="s">
         <v>325</v>
@@ -3838,7 +3857,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="B99" t="s">
         <v>325</v>
@@ -3846,7 +3865,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="B100" t="s">
         <v>326</v>
@@ -3854,7 +3873,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="B101" t="s">
         <v>327</v>
@@ -3862,7 +3881,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="B102" t="s">
         <v>328</v>
@@ -3870,7 +3889,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="B103" t="s">
         <v>325</v>
@@ -3878,7 +3897,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="B104" t="s">
         <v>329</v>
@@ -3886,7 +3905,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="B105" t="s">
         <v>330</v>
@@ -3894,7 +3913,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="B106" t="s">
         <v>331</v>
@@ -3902,7 +3921,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="B107" t="s">
         <v>332</v>
@@ -3910,7 +3929,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="B108" t="s">
         <v>309</v>
@@ -3918,7 +3937,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="B109" t="s">
         <v>333</v>
@@ -3926,7 +3945,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="B110" t="s">
         <v>334</v>
@@ -3934,7 +3953,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>377</v>
+        <v>452</v>
       </c>
       <c r="B111" t="s">
         <v>334</v>
@@ -3942,7 +3961,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>378</v>
+        <v>453</v>
       </c>
       <c r="B112" t="s">
         <v>334</v>
@@ -3950,7 +3969,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>379</v>
+        <v>454</v>
       </c>
       <c r="B113" t="s">
         <v>317</v>
@@ -3958,7 +3977,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>380</v>
+        <v>455</v>
       </c>
       <c r="B114" t="s">
         <v>335</v>
@@ -3966,7 +3985,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>381</v>
+        <v>456</v>
       </c>
       <c r="B115" t="s">
         <v>336</v>
@@ -3974,7 +3993,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>382</v>
+        <v>457</v>
       </c>
       <c r="B116" t="s">
         <v>337</v>
@@ -3982,7 +4001,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>383</v>
+        <v>458</v>
       </c>
       <c r="B117" t="s">
         <v>338</v>
@@ -3990,7 +4009,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>384</v>
+        <v>459</v>
       </c>
       <c r="B118" t="s">
         <v>339</v>
@@ -3998,7 +4017,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>385</v>
+        <v>460</v>
       </c>
       <c r="B119" t="s">
         <v>340</v>
@@ -4006,7 +4025,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>386</v>
+        <v>461</v>
       </c>
       <c r="B120" t="s">
         <v>341</v>
@@ -4014,7 +4033,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>387</v>
+        <v>462</v>
       </c>
       <c r="B121" t="s">
         <v>342</v>
@@ -4022,5 +4041,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/studyflow.xlsx
+++ b/studyflow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\puszt\Downloads\StudyFlow_GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1000054D-D5F7-4897-84C3-69149FB44BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC0A148-3672-468E-9C40-17A22043FAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="484">
   <si>
     <t>pantry</t>
   </si>
@@ -772,661 +772,724 @@
     <t xml:space="preserve">repeatedly </t>
   </si>
   <si>
-    <t>kategóriája</t>
-  </si>
-  <si>
-    <t>például</t>
-  </si>
-  <si>
-    <t>hatáskör</t>
-  </si>
-  <si>
-    <t>szervek</t>
-  </si>
-  <si>
-    <t>autonómiáját</t>
-  </si>
-  <si>
-    <t>közintézetnek</t>
-  </si>
-  <si>
-    <t>lehetnek</t>
-  </si>
-  <si>
-    <t>központosítás</t>
-  </si>
-  <si>
-    <t>minősül</t>
-  </si>
-  <si>
-    <t>egységesülést</t>
-  </si>
-  <si>
-    <t>egymással</t>
-  </si>
-  <si>
-    <t>funkció</t>
-  </si>
-  <si>
-    <t>hatósági</t>
-  </si>
-  <si>
-    <t>területén</t>
-  </si>
-  <si>
-    <t>európai</t>
-  </si>
-  <si>
-    <t>áttekintjük</t>
-  </si>
-  <si>
-    <t>ugyanis</t>
-  </si>
-  <si>
-    <t>megyei</t>
-  </si>
-  <si>
-    <t>javasolható</t>
-  </si>
-  <si>
-    <t>miniszterelnök</t>
-  </si>
-  <si>
-    <t>jogszabályban</t>
-  </si>
-  <si>
-    <t>mérlegelésétől</t>
-  </si>
-  <si>
-    <t>államtitkárok</t>
-  </si>
-  <si>
-    <t>hivatalvezetőnek</t>
-  </si>
-  <si>
-    <t>felmentett</t>
-  </si>
-  <si>
-    <t>tisztviselők</t>
-  </si>
-  <si>
-    <t>tanácsadók</t>
-  </si>
-  <si>
-    <t>védelem</t>
-  </si>
-  <si>
-    <t>azonosul</t>
-  </si>
-  <si>
-    <t>rendelkezik</t>
-  </si>
-  <si>
-    <t>FELÜGYELETI</t>
-  </si>
-  <si>
-    <t>járásnak</t>
-  </si>
-  <si>
-    <t>Szabványügyi</t>
-  </si>
-  <si>
-    <t>kamarák</t>
-  </si>
-  <si>
-    <t>feladata</t>
-  </si>
-  <si>
-    <t>JOGALKOTÁSI</t>
-  </si>
-  <si>
-    <t>megadott</t>
-  </si>
-  <si>
-    <t>képviselő-testületi</t>
-  </si>
-  <si>
-    <t>népszavazásnak</t>
-  </si>
-  <si>
-    <t>törvény</t>
-  </si>
-  <si>
-    <t>szabad</t>
-  </si>
-  <si>
-    <t>önkormányzat</t>
-  </si>
-  <si>
-    <t>osztott</t>
-  </si>
-  <si>
-    <t>önkormányzatot</t>
-  </si>
-  <si>
-    <t>egyenlő</t>
-  </si>
-  <si>
-    <t>képviseleti</t>
-  </si>
-  <si>
-    <t>HATÓSÁGI</t>
-  </si>
-  <si>
-    <t>anyanyelvét</t>
-  </si>
-  <si>
-    <t>hatóságként</t>
-  </si>
-  <si>
-    <t>mutatja</t>
-  </si>
-  <si>
-    <t>alakszerű</t>
-  </si>
-  <si>
-    <t>ügyfél</t>
-  </si>
-  <si>
-    <t>összefüggő</t>
-  </si>
-  <si>
-    <t>döntéseket</t>
-  </si>
-  <si>
-    <t>fellebbezési</t>
-  </si>
-  <si>
-    <t>eljárás</t>
-  </si>
-  <si>
-    <t>társadalmi</t>
-  </si>
-  <si>
-    <t>viszonya</t>
-  </si>
-  <si>
-    <t>személyek</t>
-  </si>
-  <si>
-    <t>joggal</t>
-  </si>
-  <si>
-    <t>eljárási</t>
-  </si>
-  <si>
-    <t>használati</t>
-  </si>
-  <si>
-    <t>felelősség</t>
-  </si>
-  <si>
-    <t>alapuló</t>
-  </si>
-  <si>
-    <t>műszaki</t>
-  </si>
-  <si>
-    <t>fogalma</t>
-  </si>
-  <si>
-    <t>típusai</t>
-  </si>
-  <si>
-    <t>jogszabályok</t>
-  </si>
-  <si>
-    <t>térhetnek</t>
-  </si>
-  <si>
-    <t>hatálya</t>
-  </si>
-  <si>
-    <t>szervezetszabályozó</t>
-  </si>
-  <si>
-    <t>forrásai</t>
-  </si>
-  <si>
-    <t>jognak</t>
-  </si>
-  <si>
-    <t>hatályba</t>
-  </si>
-  <si>
-    <t>területi</t>
-  </si>
-  <si>
-    <t>jogszabály</t>
-  </si>
-  <si>
-    <t>Államforma</t>
-  </si>
-  <si>
-    <t>kormányforma</t>
-  </si>
-  <si>
-    <t>Államalkotó</t>
-  </si>
-  <si>
-    <t>szervezete</t>
-  </si>
-  <si>
-    <t>jellemzői</t>
-  </si>
-  <si>
-    <t>szervezet</t>
-  </si>
-  <si>
-    <t>szociológiai</t>
-  </si>
-  <si>
-    <t>munkamegosztási</t>
-  </si>
-  <si>
-    <t>szervezetrendszerének</t>
-  </si>
-  <si>
-    <t>költségvetési</t>
-  </si>
-  <si>
-    <t>kiknek</t>
-  </si>
-  <si>
-    <t>alanyainak</t>
-  </si>
-  <si>
-    <t>természetes</t>
-  </si>
-  <si>
-    <t>ország</t>
-  </si>
-  <si>
-    <t>szervezeti</t>
-  </si>
-  <si>
-    <t>vezeti</t>
-  </si>
-  <si>
-    <t>megbízására</t>
-  </si>
-  <si>
-    <t>egyetértés</t>
-  </si>
-  <si>
-    <t>tevékenység</t>
-  </si>
-  <si>
-    <t>SZERVEZETI</t>
-  </si>
-  <si>
-    <t>esetben</t>
-  </si>
-  <si>
-    <t>eljáró</t>
-  </si>
-  <si>
-    <t>Tanács</t>
-  </si>
-  <si>
-    <t>Ennek központi ________ a munkamegosztás, mely a közigazgatási szervek által elvégzendő feladatok és az ellátásukra hivatott szervezetek tagolását jelenti.</t>
-  </si>
-  <si>
-    <t>A NAV hatásköre ________ kiterjed az adóhátralék bankszámláról történő letiltására, adóbírság kivetésére.</t>
-  </si>
-  <si>
-    <t>Jegyezzük meg jól tehát, hogy ________ nélkül egy közigazgatási szerv feladatait nem képes hatékonyan ellátni!  Az illetékesség az adott hatóság földrajzi értelemben vett működési területét határozza meg.</t>
-  </si>
-  <si>
-    <t>A KÖZIGAZGATÁSI SZERV MUNKASZERVEZETE A közigazgatási ________ jellemzője önálló munkaszervezet, hivatal működtetése, amelynek élén egyszemélyi felelős vezető (hivatalvezető) áll.</t>
-  </si>
-  <si>
-    <t>A közintézetek ________ mindenekelőtt a tulajdonosi jogokat gyakorló (alapító) fenntartóval szemben biztosítja a jogi szabályozás.</t>
-  </si>
-  <si>
-    <t>Ezáltal a ________ hatásköre lesz a szolgáltatási jogviszony keretében az intézeti ellátottal összefüggésben döntéseket hozni, és ezek végrehatásáról gondoskodni.</t>
-  </si>
-  <si>
-    <t>Ezen belül a vezetőknek is ________ további vezetői és a beosztottaknak is lehetnek beosztottjaik, ugyanakkor aki nem vezető és nem beosztott, az nem tartozik a rendszerbe: kívülálló (ilyen például az ügyfél).</t>
-  </si>
-  <si>
-    <t>A centralizáció mint ________ azt jelenti, hogy egy meghatározott szerv a közigazgatás szervezetének csúcsán helyezkedik el, s az irányítás innen történik.</t>
-  </si>
-  <si>
-    <t>A kirendeltség nem ________ önálló feladatés hatáskörrel rendelkező területi szervnek, csak az adott hatóság területileg kihelyezett belső szervezeti egységének.</t>
-  </si>
-  <si>
-    <t>Az integráció ________, a részeknek egymáshoz illeszkedését jelenti, bizonyos értelemben a közigazgatás hierarchikusságát és centralizáltságát finomító, működését egységesítő elv.</t>
-  </si>
-  <si>
-    <t>B) IRÁNYÍTÁS – Az ________ hierarchikus, alá-fölérendeltségi kapcsolatban álló közigazgatási szervek közötti hatalmi viszonyt irányításnak nevezzük.</t>
-  </si>
-  <si>
-    <t>Az ellenőrzési ________ önálló gyakorlására nemcsak szervek közötti ún. belső viszonyban, hanem közigazgatási szerv és ügyfél között is találunk példákat (ezt nevezzük külső ellenőrzésnek).</t>
-  </si>
-  <si>
-    <t>Megjegyezzük, hogy egyes ________ feladatok ellátása csak névlegesen valósul meg járási szinten, ugyanis számos ügykörben nem minden járási hivatal rendelkezik hatáskörrel.</t>
-  </si>
-  <si>
-    <t>A HELYI SZINT Magyarország ________ a települések típusai a következők: község, nagyközség, város, járásszékhely város, megyei jogú város, főváros és 23 kerülete.</t>
-  </si>
-  <si>
-    <t>Magyarországon – sok más ________ államhoz hasonlóan – a közigazgatásinak tekinthető feladatokat alapvetően az állam két szervezeti alrendszere, államigazgatási és önkormányzati szervek valósítják meg.</t>
-  </si>
-  <si>
-    <t>Ebben a részben ________ az egyes alrendszerek működésének főbb kapcsolódási pontjait.</t>
-  </si>
-  <si>
-    <t>Lényeges elem ________ a szolgáltató jellegű közigazgatás számára az ügyfél-közeliség érvényesülése.</t>
-  </si>
-  <si>
-    <t>A középszinten belül a ________ igazgatás párhuzamos felépítésű, azaz önkormányzati és államigazgatási szervek egyaránt megtalálhatóak.</t>
-  </si>
-  <si>
-    <t>Miniszterelnöknek ________ minden olyan személy, aki  büntetlen előéletű,  rendelkezik magyar állampolgársággal, és  az országgyűlési képviselők választásán passzív választójoga van (azaz választható).</t>
-  </si>
-  <si>
-    <t>Ez azt jelenti, hogy a kormányon belül csak a ________ az Országgyűlés által közvetlenül választott politikai vezető, vagyis a miniszterelnöknek van kormánya, nem pedig a kormánynak miniszterelnöke.</t>
-  </si>
-  <si>
-    <t>A miniszter a ________ előírt feladatés hatáskörében önállóan jár el, és ezért felelősséggel tartozik (pl. az Országgyűlésben interpellálható).</t>
-  </si>
-  <si>
-    <t>Ez azt jelenti, hogy a miniszterelnök ________ függ, elfogadja-e azt, vagy sem.</t>
-  </si>
-  <si>
-    <t>A szakpolitikai ________ feladata az adott minisztériumhoz tartozó egyes szakterületi érdekek érvényesítése.</t>
-  </si>
-  <si>
-    <t>A járási ________ az a büntetlen előéletű, cselekvőképes és nagykorú magyar állampolgár nevezhető ki, aki felsőfokú végzettséggel és legalább 5 év közigazgatási gyakorlattal rendelkezik.</t>
-  </si>
-  <si>
-    <t>A bizalomvesztés miatt ________ tisztviselő jogosult végkielégítésre és 2 hónap felmentési idő letöltésére. c) Alkalmatlanság.</t>
-  </si>
-  <si>
-    <t>Vannak ________ a közigazgatásban, akik elvileg különböző területeken is képesek megállni a helyüket, őket nevezzük generalistáknak, ellentétben az egy területre szakosodott specialistákkal.</t>
-  </si>
-  <si>
-    <t>Ebbe a körbe tartozik a politikai ________ és főtanácsadók fizetésének megállapítása a központi államigazgatásban.  Vezetői munkakörök létesítése.</t>
-  </si>
-  <si>
-    <t>A fokozott ________ abban áll, hogy több bűncselekmény, mint például az emberölés vagy az emberrablás súlyosabban minősül, ha hivatalos személy sérelmére követik el.</t>
-  </si>
-  <si>
-    <t>Azt jelenti, hogy a beosztott ________ a vezető által vallott értékekkel, célokkal, és munkáját ezek alapján végzi.</t>
-  </si>
-  <si>
-    <t>A törvény úgy ________, hogy a tisztviselő köteles felettese utasításait végrehajtani.</t>
-  </si>
-  <si>
-    <t>TÖRVÉNYESSÉGI ________ JOGKÖRÖK – A megyei kormányhivatal vezetőjének feladata a helyi és nemzetiségi önkormányzatok törvényességi felügyelete.</t>
-  </si>
-  <si>
-    <t>Ezen felül speciális ________ minősül a főváros, ahol a koncentrált lakosságszám miatt kerületi hivatalok alakultak.</t>
-  </si>
-  <si>
-    <t>Ilyen szervnek ________ a Gazdasági Versenyhivatal Versenytanácsa, vagy a Közbeszerzési Döntőbizottság.</t>
-  </si>
-  <si>
-    <t>Ilyen a Nemzeti ________ Testület (feladata a Magyar Szabványok /MSZ/ előírásainak meghatározása és közzététele).</t>
-  </si>
-  <si>
-    <t>A gazdasági ________ feladata, hogy előmozdítsák a gazdaság fejlődését és szerveződését, a piaci magatartás tisztességét, a gazdasági tevékenységet folytatók általános, együttes érdekeinek érvényesítését.</t>
-  </si>
-  <si>
-    <t>Az elnökség ________ a küldöttgyűlések közötti időszakban a gazdasági kamara működésének irányítása.</t>
-  </si>
-  <si>
-    <t>A KORMÁNY ________ HATÁSKÖRE A kormány a maga feladatkörében rendeleteket bocsát ki, és normatív határozatokat hoz, amelyeket a miniszterelnök ír alá.</t>
-  </si>
-  <si>
-    <t>A MINISZTEREK ________ HATÁSKÖRE A kormány tagjai jogalkotási hatáskörrel rendelkeznek, feladatuk ellátása körében rendeleteket adhatnak ki.</t>
-  </si>
-  <si>
-    <t>Amennyiben a ________ határidő eredménytelenül letelt, a kormányhivatal vezetője jogosult közvetlenül is összehívni a képviselő-testület ülését.</t>
-  </si>
-  <si>
-    <t>A közmeghallgatás ________ ülésnek minősül, ezért azon a települési képviselő-testület tagjai határozatképes létszámban kötelesek megjelenni.</t>
-  </si>
-  <si>
-    <t>A HELYI NÉPSZAVAZÁS Helyi ________ minősül területi hatáskör alapján az a referendum, melyet egy településen vagy településrészen bonyolítanak le.</t>
-  </si>
-  <si>
-    <t>Az önkormányzati ________ részletesen rendezi az első két területszervezési kérdés kezdeményezésének a feltételeit, a végleges döntés pedig a köztársasági elnök hatáskörébe tartozik.</t>
-  </si>
-  <si>
-    <t>Természetesen a „________ felhasználás” elsősorban az önkormányzatok kötelező és fakultatív feladatainak ellátását jelenti, hiszen a vállalkozói tevékenység nem veszélyeztetheti ezek finanszírozását.</t>
-  </si>
-  <si>
-    <t>Feladata a helyi ________ rendelkezésére álló források szabályszerű, gazdaságos, hatékony és eredményes felhasználásának ellenőrzése.</t>
-  </si>
-  <si>
-    <t>Ugyancsak ________ bevételnek minősül az adóbeszedés során kivetett bírságok és késedelmi pótlékok összege is.</t>
-  </si>
-  <si>
-    <t>A fővárosi ________ és a kerületi önkormányzatokat megillető bevételek megosztási arányáról külön törvény rendelkezik.</t>
-  </si>
-  <si>
-    <t>A nemzetiségi ________ használatába kell átadni a helyi önkormányzat tulajdonában levő, de a nemzetiségi önkormányzat feladatés hatásköre ellátásához szükséges vagyontárgyakat (pl. irodahelyiség).</t>
-  </si>
-  <si>
-    <t>Ezzel biztosítja az adott szolgáltatáshoz való ________ hozzáférés lehetőségét és finanszírozását.</t>
-  </si>
-  <si>
-    <t>Ha az ügyfél nem ________ eljárási képességgel, vagy ügyei vitelében akadályozott, képviseletet vehet igénybe.</t>
-  </si>
-  <si>
-    <t>A támogató ________ jogosultsága azonban korlátozott, az általa támogatott személy helyett például nyilatkozattételre nem jogosult.</t>
-  </si>
-  <si>
-    <t>AZ ÜGYFÉL JOGAI A ________ ELJÁRÁSBAN – Az ügyfél a következő főbb jogokkal rendelkezik az eljárás során.</t>
-  </si>
-  <si>
-    <t>Az Ákr. biztosítja, hogy a közigazgatási eljárásban ________ szóban és írásban mindenki használhassa.</t>
-  </si>
-  <si>
-    <t>Eljáró ________, mely esetben az érdemi döntés meghozatala a feladata.</t>
-  </si>
-  <si>
-    <t>A hatáskör azt ________ meg, hogy egy ügyben milyen típusú és szintű szerv jogosult és egyben köteles döntést hozni.</t>
-  </si>
-  <si>
-    <t>Ezeket nem ________ határozatoknak nevezzük. a) Az egyszerűsített határozatokban a jogorvoslatra való figyelmeztetés és a határozat indokolása mellőzhető.</t>
-  </si>
-  <si>
-    <t>Feladata, hogy az ________ tartózkodási helyét 15 napon belül lehetőség szerint felkutassa, és a határozatot számára átadja.</t>
-  </si>
-  <si>
-    <t>A közigazgatási döntésekkel ________ jogorvoslatok típusai a következők: a) az ügyfél kérelme alapján kezdeményezett eljárások; b) a hivatalból lefolytatható döntés-felülvizsgálati eljárások.</t>
-  </si>
-  <si>
-    <t>Ezeket a ________ egyedi ügyben hozott hatósági határozatoknak nevezzük.</t>
-  </si>
-  <si>
-    <t>Az Ákr. rendelkezései szerint ________ joggal rendelkezik az ügyfél, valamint az, akire nézve a határozat rendelkezést tartalmaz.</t>
-  </si>
-  <si>
-    <t>A módosítás-visszavonási ________ lefolytatására a hatóság csak egy alkalommal, a határozat közlésétől számított egy éven belül jogosult.</t>
-  </si>
-  <si>
-    <t>A jog fogalma – A jog ________ funkciói • Konfliktusfeloldás • Reguláció • Integráció • Nevelő, szociális funkció • Hatalmi, ideológiai funkció 1.1.</t>
-  </si>
-  <si>
-    <t>A jog fogalma – A jog ________ más normarendszerekhez Főbb társadalmi normarendszerek • Jog • Erkölcs • Szokás • Vallás 1.1.</t>
-  </si>
-  <si>
-    <t>A jog fogalma • ________ (jogalanyok) viselkedésére vonatkozó • az állam által alkotott, de /vagy/ legalább az állam által elismert és • az állam által végső soron kikényszerített • kötelező magatartási szabályok összessége.</t>
-  </si>
-  <si>
-    <t>A jog fogalma – A ________ normarendszerek A társadalmi normák (normarendszerek) • célja az ismétlődő társadalmi jelenségek befolyásolása = szabályozás • előírják az általánosan követendőt és a helyesnek vélt magatartást • Közös sajátosságaik: a) Tartósság igénye: időben tartósan érvényesülnek.</t>
-  </si>
-  <si>
-    <t>A jog fogalma – A jog ________ más normarendszerekhez Főbb társadalmi normarendszerek A vallás • A vallási norma, mint magatartásszabály általában a mindennapi életben beolvad a jogba, az erkölcsbe vagy a szokásba • Ezek közül valamelyik normájaként jelenik meg 1.1.</t>
-  </si>
-  <si>
-    <t>A jog fogalma – A ________ szemben támasztott követelmények • Általános • Közzétett = nyilvános, megismerhető • Jövőbeli cselekvésre irányuló • Világos, egyértelmű • Ellentmondásmentes • Lehetségest követel • Bizonyos stabilitással rendelkezik • A kinyilvánított szabály és a hivatalos cselekvés egyezést mutat.</t>
-  </si>
-  <si>
-    <t>Anyagi jogi norma – Alaki jogi norma (________ norma) 1.4 A jogviszony Fogalma: a jogviszony a jog által szabályozott társadalmi viszony.</t>
-  </si>
-  <si>
-    <t>A zálogjog, a ________ jogok. d) Kötelmi jog: szerződések közös szabályai (általános rész) és egyes szerződések (különös rész).</t>
-  </si>
-  <si>
-    <t>Kártérítési ________. e) Öröklési jog: a meghalt személy jogutódlása.</t>
-  </si>
-  <si>
-    <t>Végintézkedésen ________ és a törvényen alapuló öröklés rendje. f) A szellemi alkotások joga: szerzői jog (a szerző személyhez fűződő és vagyoni jogai).</t>
-  </si>
-  <si>
-    <t>Iparjogvédelem (________ megoldások, grafikailag ábrázolható jelzések alkotóinak jogai, szabadalmak, formatervezési minták, védjegyek).</t>
-  </si>
-  <si>
-    <t>2.1 A jogforrások ________ és típusai M A G Y A R O R S Z Á G ALKOTMÁNYOZÁS Országgyűlés Alaptörvény I.</t>
-  </si>
-  <si>
-    <t>2.1 A jogforrások ________ – a kormányrendelet Alaptörvény 15. cikk • (3) Feladatkörében eljárva a Kormány törvényben nem szabályozott tárgykörben, illetve törvényben kapott felhatalmazás alapján rendeletet alkot.</t>
-  </si>
-  <si>
-    <t>A jogforrások ________ – MNB rendelet Alaptörvény 41. cikk (5) A Magyar Nemzeti Bank elnöke törvényben kapott felhatalmazás alapján, törvényben meghatározott feladatkörében rendeletet ad ki, amely törvénnyel nem lehet ellentétes.</t>
-  </si>
-  <si>
-    <t>Alanyainak a ________ széles döntési jellemző. szabadságot biztosítanak.</t>
-  </si>
-  <si>
-    <t>A felek közös megegyezéssel el is ________ a jogszabályi rendelkezésektől, amíg valamilyen imperatív jellegű jogszabályba nem ütközik magatartásuk.</t>
-  </si>
-  <si>
-    <t>2.1 A jogforrások ________ – A közjogi szervezetszabályozó eszközök A jogalkotásról szóló 2010. évi CXXX. törvény (Jat.) 1. § (1) bek.</t>
-  </si>
-  <si>
-    <t>E törvény ________ a) a jogszabályokra, valamint b) a normatív határozatra és normatív utasításra (a továbbiakban együtt: közjogi szervezetszabályozó eszköz) terjed ki.</t>
-  </si>
-  <si>
-    <t>A közjogi ________ eszközben jogszabály rendelkezése nem ismételhető meg.</t>
-  </si>
-  <si>
-    <t>2.1 A jogforrások – Az EU jog ________ • A közösségi jog – sui generis jogrend = különbözik a tagállamok jogrendszerétől és a nemzetközi közjogtól.</t>
-  </si>
-  <si>
-    <t>A közösségi ________ nemcsak a tagállamok, hanem az uniós természetes és jogi személyek is alanyai.</t>
-  </si>
-  <si>
-    <t>Mikortól? – ________ lépés • A jogszabály saját maga határozza meg • Más jogszabály határozza meg Meddig?</t>
-  </si>
-  <si>
-    <t>2.2 A jogszabályok ________ A jogszabály hatálya - a jogszabály alkalmazhatósága.</t>
-  </si>
-  <si>
-    <t>Négy típusa a) ________ (földrajzi) hatály b) személyi (alanyi) hatály c) Időbeli hatály d) tárgyi hatály (alkalmazási kör). - Jat.</t>
-  </si>
-  <si>
-    <t>Fejezet 2.2 A ________ hatálya - A jogszabály területi hatálya – Hol kell/lehet alkalmazni?</t>
-  </si>
-  <si>
-    <t>Helyi jogszabályok - Jat 6. § (1) – • A ________ területi hatálya Magyarország területére, az önkormányzati rendelet területi hatálya a helyi önkormányzat közigazgatási területére terjed ki.</t>
-  </si>
-  <si>
-    <t>Az állam - 3.1 Az állam fogalma Az állam ________ (Georg Jellinek – Általános államtan) – az állam közjogi fogalmának ismérvei – az államiság feltételei: 1.</t>
-  </si>
-  <si>
-    <t>Az állam - 3.1 Az állam fogalma – ________ Államforma – Kormányforma - Államszerkezet • Államforma – a közhatalom gyakorlásának módja 1.</t>
-  </si>
-  <si>
-    <t>Az állam - 3.1 Az állam fogalma - ________ Kormányforma – a törvényhozó és végrehajtó hatalom viszonya, a kormányzati hatalom gyakorlása 1.</t>
-  </si>
-  <si>
-    <t>Az állam - 3.1 Az állam fogalma - ________ népesség - állampolgárság Állampolgárság szabályozási kérdései - Keletkezés 1.</t>
-  </si>
-  <si>
-    <t>Az állam - 3.1 Az állam fogalma - Az állam ________ Államszervezet – egy adott állam szerveinek összessége, amely révén az állam gyakorolja hatalmát, teljesíti céljait, ellátja feladatait.</t>
-  </si>
-  <si>
-    <t>A tisztviselő ________ annak a döntésnek a hatékony végrehajtása, amit a politikus hozott /Woodrow Wilson/ = a kormányzás és a közigazgatás szétválasztása.</t>
-  </si>
-  <si>
-    <t>A közigazgatás ________ Negatív fogalommeghatározás : mi nem a közigazgatás? • Magáncselekvések – Közcselekvések - Az igazgatási tevékenység (szervezeti tevékenység) végezhető magán (pl. üzleti) és állami szervezeti keretek között (= közigazgatás) • Közcselekvések, ami nem közigazgatás - törvényalkotás - igazságszolgáltatás - politika - kormányzás 1.</t>
-  </si>
-  <si>
-    <t>A közigazgatás ________ Negatív definíció A közigazgatás: az állam saját jogrendjének uralma alatt végbemenő azon állami ténykedés, amely az igazságszolgáltatás céljaitól különböző összes egyéb állami cél megvalósítását szolgálja. – Otto Mayer /1846 – 1924/ 1.</t>
-  </si>
-  <si>
-    <t>A közigazgatási jog fogalma és ________ Közjog (pl.) Magánjog (pl.) Alkotmányjog Polgári jog Közigazgatási jog Családjog Pénzügyi jog Kereskedelmi (gazdasági) Büntetőjog jog Büntetővégrehajtási jog Eljárásjogok Vegyes jogágak (pl.): munkajog, agrárjog 2.</t>
-  </si>
-  <si>
-    <t>A közigazgatási jog fogalma és ________ – a közigazgatási jog forrásai • Alaptörvény (?) • Törvények - A közigazgatás szervezete Jellemző: - Eljárási törvények • Rendeleti jog túlsúlya - Ágazati törvények • Nem jogszabályi jog • Rendeletek túlsúlya - Eredeti • Heterogenitás - Származékos - Önkormányzati rendeletek (!) • Alacsonyabb szintű jogforrások 3.</t>
-  </si>
-  <si>
-    <t>A közigazgatás, mint ________ 4.2 Közigazgatási szerv, közigazgatási szervezet A szervezetrendszer • A jogi szabályozás sem a szervezetrendszer, sem a rendszer fogalmát nem határozza meg.</t>
-  </si>
-  <si>
-    <t>A közigazgatás, mint ________ 4.2 Közigazgatási szerv, közigazgatási szervezet • A közigazgatási szerv önállósága (jogi értelemben) = jogosult önállóan cselekedni. • Az önálló cselekvést az önálló hatáskör teszi lehetővé.</t>
-  </si>
-  <si>
-    <t>A rendszer ________ fogalma: egymással funkcionálisan kapcsolatban álló, a környezettől e kapcsolatok és a kapcsolatrendszernek a környezet számára végzett funkciója által elhatároltható elemek összessége. • A közigazgatás szervezet és egyben rendszer. • Szervezetként az államszervezet része.</t>
-  </si>
-  <si>
-    <t>Szakmai ________ elvek 2.1 Különös hatáskör – általános hatáskör 2.2 Ágazati elv – funkcionális elv 3.</t>
-  </si>
-  <si>
-    <t>Rendszerként az állam ________ a része. • A közigazgatás viszonylag önállónak nevezhető rendszerekből áll (a közigazgatás alrendszerei).</t>
-  </si>
-  <si>
-    <t>Jogi személyiséggel nem rendelkező ________ Akkor képes jogokat szerezni és kötelezettségeket vállalni, ha jogszabály így rendelkezik = polgári jogi jogalanyisággal ruházza fel.</t>
-  </si>
-  <si>
-    <t>7. § (1) bek. • Minden közigazgatási szerv, amely ________ szerv, egyúttal polgárjogi jogi személyiséggel is rendelkezik, de nem minden közigazgatási szerv költségvetési szerv 2.2 2.2 Egyéb: külön – általában az adott szervet létrehozó - jogszabály rendelkezhet arról, hogy egy szerv polgárjogi jogi személy. - Pl.</t>
-  </si>
-  <si>
-    <t>A közigazgatási jog alanyai - Kinek, ________ a magatartását szabályozza a jog?</t>
-  </si>
-  <si>
-    <t>A közigazgatási jog alanyai Cél: a közigazgatási jog ________ a megismertetése Közigazgatási jogi jogalanyiság Polgári jogi jogalanyiság 6.</t>
-  </si>
-  <si>
-    <t>Az ember, mint jogalany ________ személy „Minden ember jogképes: jogai és kötelezettségei lehetnek.” – Ptk.</t>
-  </si>
-  <si>
-    <t>A szervezeti jog ________: viszonylag elkülönült joganyag a közigazgatási jogon belül, a közigazgatási jog egyik részterülete.</t>
-  </si>
-  <si>
-    <t>Település • Az ________ területe településekre tagozódik. • Az ország teljes területe, valamennyi pontja közigazgatásilag egy (valamely) településhez tartozik, ami lehet - község, ezen belül nagyközség [Mötv.</t>
-  </si>
-  <si>
-    <t>A közigazgatás ________ joga A közigazgatási szerveket és szervezetüket, valamint feladatés hatáskörüket a jogi szabályozás, elsősorban jogszabályok hozzák létre és alakítják.</t>
-  </si>
-  <si>
-    <t>A közigazgatás ________ joga szabályozza a közigazgatási szervek formáit, a szervek belső felépítésének rendjét, külső – akár a közigazgatáson belüli, akár a közigazgatáson kívüli – kapcsolati rendszerét.</t>
-  </si>
-  <si>
-    <t>A közigazgatás ________ joga A közigazgatás szervezetrendszerét meghatározó joganyag A közigazgatási szervek csoportosítása szervezeti jogi szempontból A közigazgatás két nagy alrendszere: 1.</t>
-  </si>
-  <si>
-    <t>A 2012. szeptember 1-jén ________ lépett nemzeti felsőoktatásról szóló törvény biztosítja az intézményalapítás szabadságát.</t>
-  </si>
-  <si>
-    <t>A rektor ________ és képviseli az intézményt, egyben a szenátus elnöke is, így hatásköre a szenátus döntéseinek előkészítésére és végrehajtására is kiterjed.</t>
-  </si>
-  <si>
-    <t>A kancellár ________ és felmentésére a miniszterelnök jogosult.</t>
-  </si>
-  <si>
-    <t>A kancellári ________ e döntések érvényességének, illetve hatálybalépésének feltétele, tehát a kancellár széleskörű vétójoggal rendelkezik egyes döntések meghozatala során.</t>
-  </si>
-  <si>
-    <t>Az igazgatási ________ a szervezetek (köztük a közigazgatási szerveknek is) olyan tudatos, tervszerű tevékenysége, amely biztosítja a szervezet céljainak eléréséhez szükséges személyi és dologi feltételeket, valamint a munka összhangját.</t>
-  </si>
-  <si>
-    <t>KÖZIGAZGATÁSI SZERV ÖNÁLLÓ ________ EGYSÉGE – A közigazgatási szerv önálló szervezeti egysége ezzel szemben kizárólag közigazgatási jogképességgel rendelkezik, azaz önálló feladatköre van, amelynek részeként döntéseket hozhat, és azok betartatására nézve intézkedéseket tehet.</t>
-  </si>
-  <si>
-    <t>Ez utóbbi ________ ún. utólagos normakontroll eljárás indítványozására jogosult. (B) ÁLLAMI SZÁMVEVŐSZÉK – Az ÁSZ kizárólag az Országgyűlésnek alárendelt legfőbb pénzügyi ellenőrző szerv, ellenőrzéseit célszerűségi, eredményességi és törvényességi szempontok szerint végzi.</t>
-  </si>
-  <si>
-    <t>A közigazgatási ügyekben ________ bíróságok hatásköre arra terjed ki, hogy az ügyfél keresete alapján megvizsgálják egy egyedi hatósági ügyben hozott közigazgatási határozat (döntés) jogszerűségét, és törvénysértés esetén megsemmisítsék vagy megváltoztassák azt.</t>
-  </si>
-  <si>
-    <t>Az Önkormányzati ________ jogosult az önkormányzat képviselő-testülete (közgyűlése) által elfogadott rendeletet megsemmisíteni, ha az magasabb szintű jogszabállyal ellentétes, vagy megállapíthatja a helyi önkormányzat jogalkotási kötelezettségének elmulasztását is.</t>
+    <t>Mi a közigazgatás?</t>
+  </si>
+  <si>
+    <t>Jog által szabályozott, közfeladatok ellátására irányuló, közhatalmi jogosítványokkal is rendelkező igazgatási tevékenység.</t>
+  </si>
+  <si>
+    <t>Mi a közigazgatás két alapvető alrendszere?</t>
+  </si>
+  <si>
+    <t>Az államigazgatás és az önkormányzati igazgatás.</t>
+  </si>
+  <si>
+    <t>Mi a külső igazgatás?</t>
+  </si>
+  <si>
+    <t>A közigazgatási szervezeten kívüli ügyfelekre, személyekre és szervezetekre irányuló igazgatás.</t>
+  </si>
+  <si>
+    <t>Mi a belső igazgatás?</t>
+  </si>
+  <si>
+    <t>A közigazgatási szervezet belső működésének, munkamegosztásának és együttműködésének megszervezése.</t>
+  </si>
+  <si>
+    <t>Mi a koordináció szerepe?</t>
+  </si>
+  <si>
+    <t>A szakosodott szervezetek és szervezeti egységek munkájának összehangolása.</t>
+  </si>
+  <si>
+    <t>Mi a jog kettős szerepe a közigazgatásban?</t>
+  </si>
+  <si>
+    <t>A közhatalom gyakorlásának eszköze és egyúttal korlátja.</t>
+  </si>
+  <si>
+    <t>Melyek a közigazgatási jog fő szabályozási területei?</t>
+  </si>
+  <si>
+    <t>A szervezeti jog, az eljárási jog és az ágazati szakigazgatás joga.</t>
+  </si>
+  <si>
+    <t>Mely szervezetek alkotják a közigazgatás öt pillérét a jegyzet szerint?</t>
+  </si>
+  <si>
+    <t>Az államigazgatási szervek, a helyi, köztestületi és nemzetiségi önkormányzatok, valamint a közintézetek és közalapítványok.</t>
+  </si>
+  <si>
+    <t>Miben különbözik a közvállalat a közintézettől?</t>
+  </si>
+  <si>
+    <t>A közvállalat jellemzően gazdasági, a közintézet humán közszolgáltatást lát el.</t>
+  </si>
+  <si>
+    <t>Mi a hatalmi jellegű igazgatási feladat egyik formája?</t>
+  </si>
+  <si>
+    <t>A hatósági döntéshozatal és a döntés végrehajtásának kikényszerítése.</t>
+  </si>
+  <si>
+    <t>Mit jelent az önálló közigazgatási szerv?</t>
+  </si>
+  <si>
+    <t>Szervezetileg elkülönült, jogi személyiséggel és saját feladat- és hatáskörrel rendelkező közigazgatási szerv.</t>
+  </si>
+  <si>
+    <t>Milyen jogképességekkel rendelkezik az önálló közigazgatási szerv a tananyag szerint?</t>
+  </si>
+  <si>
+    <t>Közigazgatási, polgári jogi, pénzügyi és közszolgálati munkáltatói jogképességgel.</t>
+  </si>
+  <si>
+    <t>Miben tér el az önálló szervezeti egység az önálló közigazgatási szervtől?</t>
+  </si>
+  <si>
+    <t>Az önálló szervezeti egységnek saját közigazgatási jogképessége lehet, de nincs teljes polgári jogi, pénzügyi és munkáltatói jogképessége.</t>
+  </si>
+  <si>
+    <t>Van-e önálló döntési jogköre a közigazgatási szerv belső osztályának?</t>
+  </si>
+  <si>
+    <t>Nincs; a szerv vagy az önálló szervezeti egység vezetőjének nevében jár el.</t>
+  </si>
+  <si>
+    <t>Mi a statútum?</t>
+  </si>
+  <si>
+    <t>A közigazgatási szervet létrehozó, feladatait és jogállását meghatározó jogszabály.</t>
+  </si>
+  <si>
+    <t>Mi a feladatkör?</t>
+  </si>
+  <si>
+    <t>Azoknak a közfeladatoknak és tevékenységeknek az összessége, amelyek ellátására a szerv létrejött.</t>
+  </si>
+  <si>
+    <t>Mi a hatáskör?</t>
+  </si>
+  <si>
+    <t>A szerv jogszabályban biztosított döntési és intézkedési jogosultságainak, illetve kötelezettségeinek köre.</t>
+  </si>
+  <si>
+    <t>Mi az illetékesség?</t>
+  </si>
+  <si>
+    <t>A hatóság földrajzilag meghatározott működési és eljárási területe.</t>
+  </si>
+  <si>
+    <t>Ki áll a közigazgatási hivatal munkaszervezetének élén?</t>
+  </si>
+  <si>
+    <t>Az egyszemélyi felelős vezető, a hivatalvezető.</t>
+  </si>
+  <si>
+    <t>Mi a közintézet elsődleges feladata?</t>
+  </si>
+  <si>
+    <t>Humán jellegű közszolgáltatás, például oktatás, egészségügy vagy szociális ellátás nyújtása.</t>
+  </si>
+  <si>
+    <t>Mit jelent a közintézet szakmai autonómiája?</t>
+  </si>
+  <si>
+    <t>A szakmai feladatok ellátásában jogszabály által biztosított önállóságot.</t>
+  </si>
+  <si>
+    <t>Milyen jogosítványai vannak a közintézet fenntartójának?</t>
+  </si>
+  <si>
+    <t>Többek között a vezető kinevezése, a költségvetés meghatározása, az ellenőrzés és az SZMSZ jóváhagyása.</t>
+  </si>
+  <si>
+    <t>Ki a felsőoktatási intézmény vezetője?</t>
+  </si>
+  <si>
+    <t>A rektor.</t>
+  </si>
+  <si>
+    <t>Melyik a felsőoktatási intézmény alapvető testületi döntéshozó szerve?</t>
+  </si>
+  <si>
+    <t>A szenátus.</t>
+  </si>
+  <si>
+    <t>Mi a kancellár fő feladata a bemutatott állami egyetemi modellben?</t>
+  </si>
+  <si>
+    <t>Az intézmény gazdasági, üzemeltetési és működtetési feladatainak irányítása.</t>
+  </si>
+  <si>
+    <t>Mi a konzisztórium szerepe a tananyagban?</t>
+  </si>
+  <si>
+    <t>Az állami felsőoktatási intézmény stratégiai és gazdálkodási döntéseinek szakmai támogatása és ellenőrzése.</t>
+  </si>
+  <si>
+    <t>Ki vezeti az egyetemi kart?</t>
+  </si>
+  <si>
+    <t>A dékán.</t>
+  </si>
+  <si>
+    <t>Mi a közérdekű vagyonkezelő alapítvány felsőoktatási szerepe?</t>
+  </si>
+  <si>
+    <t>Felsőoktatási intézmény fenntartói jogainak gyakorlása és működési, fejlesztési feltételeinek biztosítása.</t>
+  </si>
+  <si>
+    <t>Mi a centralizáció a közigazgatásban?</t>
+  </si>
+  <si>
+    <t>A döntési és irányítási jogkörök központi szervekhez összpontosítása.</t>
+  </si>
+  <si>
+    <t>Mi a decentralizáció lényege?</t>
+  </si>
+  <si>
+    <t>Közigazgatási feladatok és döntési jogosultságok önálló, nem központi szervekhez telepítése.</t>
+  </si>
+  <si>
+    <t>Mi a dekoncentráció?</t>
+  </si>
+  <si>
+    <t>Központi államigazgatási feladatok területi államigazgatási szervek útján történő ellátása.</t>
+  </si>
+  <si>
+    <t>Mit jelent a hierarchia a közigazgatásban?</t>
+  </si>
+  <si>
+    <t>A szervek közötti alá-fölérendeltségi, irányítási és utasítási kapcsolatot.</t>
+  </si>
+  <si>
+    <t>Mi a törvényesség követelménye a közigazgatásban?</t>
+  </si>
+  <si>
+    <t>A közigazgatási szervek csak a jogszabályok keretei között járhatnak el.</t>
+  </si>
+  <si>
+    <t>Mi az irányítás és a felügyelet közötti alapvető különbség?</t>
+  </si>
+  <si>
+    <t>Az irányítás szélesebb beavatkozási jogosultság, a felügyelet jellemzően ellenőrzésre és meghatározott intézkedésekre korlátozódik.</t>
+  </si>
+  <si>
+    <t>Mi a hatékonyság követelménye?</t>
+  </si>
+  <si>
+    <t>A közfeladatok eredményes ellátása a rendelkezésre álló erőforrások célszerű felhasználásával.</t>
+  </si>
+  <si>
+    <t>Mit jelent a szakszerűség a közigazgatásban?</t>
+  </si>
+  <si>
+    <t>A feladatok jogi és szakmai követelményeknek megfelelő ellátását.</t>
+  </si>
+  <si>
+    <t>Mi a közszolgálati jogviszony keletkezésének jellemző módja?</t>
+  </si>
+  <si>
+    <t>A kinevezés és annak elfogadása.</t>
+  </si>
+  <si>
+    <t>Mi a köztisztviselő és a kormánytisztviselő alapvető szervezeti különbsége a jegyzet szerint?</t>
+  </si>
+  <si>
+    <t>A kormánytisztviselő jellemzően államigazgatási, a köztisztviselő önkormányzati hivatali feladatokat lát el.</t>
+  </si>
+  <si>
+    <t>Milyen általános kötelesség terheli a közszolgálati tisztviselőt?</t>
+  </si>
+  <si>
+    <t>A törvényes, pártatlan, szakszerű feladatellátás és a hivatali titok megőrzése.</t>
+  </si>
+  <si>
+    <t>Köteles-e a tisztviselő minden utasítást végrehajtani?</t>
+  </si>
+  <si>
+    <t>Nem; a jogellenes utasításokkal kapcsolatban a jogszabályi kivételek és eljárási szabályok irányadók.</t>
+  </si>
+  <si>
+    <t>Mi az összeférhetetlenségi szabályok célja?</t>
+  </si>
+  <si>
+    <t>A közérdekű, pártatlan feladatellátás biztosítása és az érdekütközések megelőzése.</t>
+  </si>
+  <si>
+    <t>Mi a fegyelmi felelősség lényege?</t>
+  </si>
+  <si>
+    <t>A közszolgálati kötelezettség vétkes megszegéséhez kapcsolódó jogkövetkezmény.</t>
+  </si>
+  <si>
+    <t>Mi a Kormány alapvető államszervezeti szerepe?</t>
+  </si>
+  <si>
+    <t>A végrehajtó hatalom általános szerve és a közigazgatás központi irányítója.</t>
+  </si>
+  <si>
+    <t>Mi a minisztérium alapvető feladata?</t>
+  </si>
+  <si>
+    <t>A miniszter feladatkörébe tartozó ágazati kormányzati és igazgatási feladatok ellátása.</t>
+  </si>
+  <si>
+    <t>Mi a miniszter feladata?</t>
+  </si>
+  <si>
+    <t>A rábízott ágazat szakpolitikai irányítása és a jogszabályban meghatározott kormányzati feladatok ellátása.</t>
+  </si>
+  <si>
+    <t>Mi a központi hivatal?</t>
+  </si>
+  <si>
+    <t>Központi államigazgatási szerv, amely meghatározott szakigazgatási feladatokat lát el.</t>
+  </si>
+  <si>
+    <t>Mire szolgál a területi államigazgatás?</t>
+  </si>
+  <si>
+    <t>Az államigazgatási feladatok területi szintű végrehajtására és ügyintézésére.</t>
+  </si>
+  <si>
+    <t>Mi a fővárosi és vármegyei kormányhivatal alapvető szerepe?</t>
+  </si>
+  <si>
+    <t>Általános hatáskörű területi államigazgatási feladatok ellátása és összehangolása.</t>
+  </si>
+  <si>
+    <t>Mi a járási hivatal?</t>
+  </si>
+  <si>
+    <t>A fővárosi vagy vármegyei kormányhivatal helyi szinten működő szervezeti egysége.</t>
+  </si>
+  <si>
+    <t>Mi a NAV alapvető feladata?</t>
+  </si>
+  <si>
+    <t>Az állami adó- és vámigazgatási feladatok ellátása.</t>
+  </si>
+  <si>
+    <t>Mi a helyi önkormányzás lényege?</t>
+  </si>
+  <si>
+    <t>A helyi közügyek intézése és a helyi közhatalom gyakorlása a törvény keretei között.</t>
+  </si>
+  <si>
+    <t>Mi a helyi önkormányzat legfőbb döntéshozó szerve?</t>
+  </si>
+  <si>
+    <t>A képviselő-testület.</t>
+  </si>
+  <si>
+    <t>Ki vezeti és képviseli a települési önkormányzatot?</t>
+  </si>
+  <si>
+    <t>A polgármester.</t>
+  </si>
+  <si>
+    <t>Mi a jegyző alapvető feladata?</t>
+  </si>
+  <si>
+    <t>Az önkormányzati hivatal szakmai vezetése és a jogszabályban meghatározott igazgatási feladatok ellátása.</t>
+  </si>
+  <si>
+    <t>Mi az önkormányzati rendelet?</t>
+  </si>
+  <si>
+    <t>A helyi önkormányzat képviselő-testülete által alkotott jogszabály.</t>
+  </si>
+  <si>
+    <t>Mi az önkormányzati határozat?</t>
+  </si>
+  <si>
+    <t>A képviselő-testület vagy más jogosult önkormányzati szerv egyedi, illetve szervezeti döntése.</t>
+  </si>
+  <si>
+    <t>Mire szolgál a polgármesteri hivatal?</t>
+  </si>
+  <si>
+    <t>Az önkormányzati működés és a hatósági ügyintézés szakmai, ügyviteli támogatására.</t>
+  </si>
+  <si>
+    <t>Mi a köztestület?</t>
+  </si>
+  <si>
+    <t>Törvény alapján létrejövő, önkormányzattal és nyilvántartott tagsággal rendelkező közfeladatot ellátó szervezet.</t>
+  </si>
+  <si>
+    <t>Mi a nemzetiségi önkormányzat alapvető rendeltetése?</t>
+  </si>
+  <si>
+    <t>A nemzetiségi közösség kulturális autonómiájának és közösségi jogainak képviselete.</t>
+  </si>
+  <si>
+    <t>Mi a törvényességi felügyelet célja az önkormányzatok felett?</t>
+  </si>
+  <si>
+    <t>Az önkormányzati működés jogszerűségének ellenőrzése, nem a helyi célszerűségi döntések átvétele.</t>
+  </si>
+  <si>
+    <t>Mit nevezünk jogalkotásnak?</t>
+  </si>
+  <si>
+    <t>Általánosan kötelező magatartási szabályok jogszabályi formában történő megalkotását.</t>
+  </si>
+  <si>
+    <t>Melyik Magyarország legmagasabb szintű jogforrása?</t>
+  </si>
+  <si>
+    <t>Az Alaptörvény.</t>
+  </si>
+  <si>
+    <t>Ki alkot törvényt Magyarországon?</t>
+  </si>
+  <si>
+    <t>Az Országgyűlés.</t>
+  </si>
+  <si>
+    <t>Milyen jogszabályt alkothat a Kormány?</t>
+  </si>
+  <si>
+    <t>Kormányrendeletet.</t>
+  </si>
+  <si>
+    <t>Milyen jogszabályt alkothat a miniszter?</t>
+  </si>
+  <si>
+    <t>Miniszteri rendeletet, jogszabályi felhatalmazás és feladatköre keretei között.</t>
+  </si>
+  <si>
+    <t>Milyen jogszabályt alkothat a helyi önkormányzat képviselő-testülete?</t>
+  </si>
+  <si>
+    <t>Önkormányzati rendeletet.</t>
+  </si>
+  <si>
+    <t>Mi a jogforrási hierarchia lényege?</t>
+  </si>
+  <si>
+    <t>Az alacsonyabb szintű jogszabály nem lehet ellentétes a magasabb szintűvel.</t>
+  </si>
+  <si>
+    <t>Mi a jogszabály kihirdetésének szerepe?</t>
+  </si>
+  <si>
+    <t>A jogszabály hivatalos közzététele, amely a hatálybalépés jogi előfeltétele.</t>
+  </si>
+  <si>
+    <t>Mi a jogszabály hatálya?</t>
+  </si>
+  <si>
+    <t>Annak meghatározása, hogy a jogszabály mikor, hol, kikre és milyen ügyekre alkalmazandó.</t>
+  </si>
+  <si>
+    <t>Mit jelent a visszaható hatály tilalma?</t>
+  </si>
+  <si>
+    <t>A jogszabály főszabály szerint nem állapíthat meg utólag hátrányos kötelezettséget a hatálybalépése előtti időre.</t>
+  </si>
+  <si>
+    <t>Mi a közjog és a magánjog alapvető különbsége?</t>
+  </si>
+  <si>
+    <t>A közjog a közhatalmi viszonyokat, a magánjog főként a mellérendelt jogalanyok viszonyait szabályozza.</t>
+  </si>
+  <si>
+    <t>Mi a közigazgatási hatósági ügy?</t>
+  </si>
+  <si>
+    <t>Olyan ügy, amelyben a hatóság jogot vagy kötelezettséget állapít meg, adatot igazol, nyilvántartást vezet vagy hatósági ellenőrzést végez.</t>
+  </si>
+  <si>
+    <t>Ki az ügyfél a hatósági eljárásban?</t>
+  </si>
+  <si>
+    <t>Akinek jogát vagy jogos érdekét az ügy közvetlenül érinti, illetve akire a jogszabály ügyféli jogállást állapít meg.</t>
+  </si>
+  <si>
+    <t>Mi az Ákr. szerepe?</t>
+  </si>
+  <si>
+    <t>Az általános közigazgatási rendtartás a közigazgatási hatósági eljárás alapvető szabályait tartalmazza.</t>
+  </si>
+  <si>
+    <t>Hogyan indulhat hatósági eljárás?</t>
+  </si>
+  <si>
+    <t>Kérelemre vagy hivatalból.</t>
+  </si>
+  <si>
+    <t>Mi a kérelemre induló eljárás?</t>
+  </si>
+  <si>
+    <t>Olyan hatósági eljárás, amelyet az ügyfél kérelme indít meg.</t>
+  </si>
+  <si>
+    <t>Mi a hivatalból induló eljárás?</t>
+  </si>
+  <si>
+    <t>Olyan hatósági eljárás, amelyet a hatóság saját kezdeményezésére vagy jogszabályi kötelezettség alapján indít.</t>
+  </si>
+  <si>
+    <t>Mi a tényállás tisztázásának célja?</t>
+  </si>
+  <si>
+    <t>A döntéshez szükséges releváns tények és bizonyítékok feltárása.</t>
+  </si>
+  <si>
+    <t>Milyen eszközökkel történhet a bizonyítás a hatósági eljárásban?</t>
+  </si>
+  <si>
+    <t>Például okirattal, tanúvallomással, szakértői véleménnyel, szemlével vagy ügyféli nyilatkozattal.</t>
+  </si>
+  <si>
+    <t>Mikor van szükség szakértőre a hatósági eljárásban?</t>
+  </si>
+  <si>
+    <t>Ha a jelentős tény vagy körülmény megítéléséhez különleges szakértelem szükséges.</t>
+  </si>
+  <si>
+    <t>Mi a hatósági ellenőrzés célja?</t>
+  </si>
+  <si>
+    <t>A jogszabályokban és hatósági döntésekben előírt kötelezettségek teljesítésének vizsgálata.</t>
+  </si>
+  <si>
+    <t>Mi a hiánypótlás rendeltetése?</t>
+  </si>
+  <si>
+    <t>A hiányos kérelem vagy mellékletei jogszabály szerint pótolható hiányainak megszüntetése.</t>
+  </si>
+  <si>
+    <t>Mi az ügyintézési határidő?</t>
+  </si>
+  <si>
+    <t>Az az időtartam, amelyen belül a hatóságnak az eljárási kötelezettségét teljesítenie kell.</t>
+  </si>
+  <si>
+    <t>Mi a határozat a hatósági eljárásban?</t>
+  </si>
+  <si>
+    <t>Az ügy érdemében hozott hatósági döntés.</t>
+  </si>
+  <si>
+    <t>Mi a végzés a hatósági eljárásban?</t>
+  </si>
+  <si>
+    <t>Jellemzően az eljárás során felmerülő eljárási kérdésben hozott döntés.</t>
+  </si>
+  <si>
+    <t>Mit tartalmaz a hatósági döntés indokolása?</t>
+  </si>
+  <si>
+    <t>A megállapított tényállást, a bizonyítékok értékelését és a döntés jogi indokait.</t>
+  </si>
+  <si>
+    <t>Mi a döntés közlésének jelentősége?</t>
+  </si>
+  <si>
+    <t>A döntés címzett általi hivatalos megismerhetővé tétele és egyes joghatások, határidők megindulása.</t>
+  </si>
+  <si>
+    <t>Mi a jogorvoslat célja?</t>
+  </si>
+  <si>
+    <t>A hatósági döntés jogszerűségének felülvizsgálata és az esetleges jogsérelem orvoslása.</t>
+  </si>
+  <si>
+    <t>Mi a fellebbezés?</t>
+  </si>
+  <si>
+    <t>A törvény által megengedett esetben igénybe vehető közigazgatási jogorvoslat a döntéssel szemben.</t>
+  </si>
+  <si>
+    <t>Mi a közigazgatási per rendeltetése?</t>
+  </si>
+  <si>
+    <t>A közigazgatási tevékenység bírósági jogszerűségi kontrollja.</t>
+  </si>
+  <si>
+    <t>Mit jelent a véglegesség a hatósági döntésnél?</t>
+  </si>
+  <si>
+    <t>A döntés a közigazgatási eljárás keretében már nem változtatható meg rendes jogorvoslattal az adott szabályok szerint.</t>
+  </si>
+  <si>
+    <t>Mi a végrehajtás a hatósági eljárásban?</t>
+  </si>
+  <si>
+    <t>A végrehajtható hatósági döntésben foglalt kötelezettség állami kényszerrel történő érvényesítése.</t>
+  </si>
+  <si>
+    <t>Mi az államháztartás?</t>
+  </si>
+  <si>
+    <t>Az állam és az önkormányzati alrendszer közpénzügyi gazdálkodásának rendszere.</t>
+  </si>
+  <si>
+    <t>Mi a költségvetés?</t>
+  </si>
+  <si>
+    <t>Meghatározott időszakra tervezett bevételek és kiadások pénzügyi terve.</t>
+  </si>
+  <si>
+    <t>Mi a költségvetési szerv?</t>
+  </si>
+  <si>
+    <t>Jogszabályban meghatározott közfeladat ellátására létrehozott, költségvetési gazdálkodást folytató jogi személy.</t>
+  </si>
+  <si>
+    <t>Mi a közszolgáltatás?</t>
+  </si>
+  <si>
+    <t>Közérdekű szükséglet kielégítésére szervezett vagy biztosított szolgáltatás.</t>
+  </si>
+  <si>
+    <t>Mi a közfeladat és a közszolgáltatás viszonya?</t>
+  </si>
+  <si>
+    <t>A közszolgáltatás a közfeladatok ellátásának egyik lehetséges formája.</t>
+  </si>
+  <si>
+    <t>Mi a közbeszerzés rendeltetése?</t>
+  </si>
+  <si>
+    <t>A közpénzből megvalósuló beszerzések szabályozott és versenyen alapuló lebonyolítása.</t>
+  </si>
+  <si>
+    <t>Mi a jog fogalma általános értelemben?</t>
+  </si>
+  <si>
+    <t>Az állam által elismert vagy alkotott és végső soron állami kényszerrel biztosított magatartási szabályok rendszere.</t>
+  </si>
+  <si>
+    <t>Mi a jogrendszer?</t>
+  </si>
+  <si>
+    <t>Egy adott államban, adott időpontban hatályos jogszabályok összessége.</t>
+  </si>
+  <si>
+    <t>Mi a jogi norma?</t>
+  </si>
+  <si>
+    <t>Általános magatartási szabály, amelyhez a jogrend jogkövetkezményt kapcsol.</t>
+  </si>
+  <si>
+    <t>Mi a kógens jogi norma?</t>
+  </si>
+  <si>
+    <t>Olyan kötelező szabály, amelytől a jogalanyok nem térhetnek el.</t>
+  </si>
+  <si>
+    <t>Mi a diszpozitív jogi norma?</t>
+  </si>
+  <si>
+    <t>Olyan szabály, amelytől a felek jogszerűen eltérhetnek, ha a jog megengedi.</t>
+  </si>
+  <si>
+    <t>Mi a jogi norma hipotézise?</t>
+  </si>
+  <si>
+    <t>A szabály alkalmazásának feltételeit leíró tényállási rész.</t>
+  </si>
+  <si>
+    <t>Mi a jogi norma diszpozíciója?</t>
+  </si>
+  <si>
+    <t>A követendő, megengedett vagy tiltott magatartást meghatározó rész.</t>
+  </si>
+  <si>
+    <t>Mi a jogi norma szankciója?</t>
+  </si>
+  <si>
+    <t>A norma megsértéséhez vagy alkalmazásához kapcsolódó jogkövetkezmény.</t>
+  </si>
+  <si>
+    <t>Melyek az Európai Unió elsődleges jogforrásai?</t>
+  </si>
+  <si>
+    <t>Az alapító és módosító szerződések, valamint az elsődleges joghoz tartozó egyéb dokumentumok.</t>
+  </si>
+  <si>
+    <t>Mi az uniós rendelet fő sajátossága?</t>
+  </si>
+  <si>
+    <t>Általános hatályú, teljes egészében kötelező és közvetlenül alkalmazandó a tagállamokban.</t>
+  </si>
+  <si>
+    <t>Mi az uniós irányelv fő sajátossága?</t>
+  </si>
+  <si>
+    <t>Az elérendő eredmény tekintetében kötelező, de a végrehajtás formáját és eszközeit főszabály szerint a tagállam választja meg.</t>
+  </si>
+  <si>
+    <t>Mi az állam három klasszikus alkotóeleme?</t>
+  </si>
+  <si>
+    <t>A népesség, az államterület és a főhatalom.</t>
+  </si>
+  <si>
+    <t>Mit jelent az állami szuverenitás?</t>
+  </si>
+  <si>
+    <t>Az állam legfőbb, önálló közhatalmát a területén és függetlenségét a nemzetközi kapcsolatokban.</t>
+  </si>
+  <si>
+    <t>Mi a jogállamiság alapvető követelménye?</t>
+  </si>
+  <si>
+    <t>A közhatalom joghoz kötött, ellenőrizhető és az alapjogokat tiszteletben tartó gyakorlása.</t>
+  </si>
+  <si>
+    <t>Mi a hatalommegosztás lényege?</t>
+  </si>
+  <si>
+    <t>A törvényhozó, végrehajtó és bírói hatalmi funkciók elkülönítése és kölcsönös korlátozása.</t>
+  </si>
+  <si>
+    <t>Mi az Országgyűlés legfontosabb jogalkotási feladata?</t>
+  </si>
+  <si>
+    <t>Törvények megalkotása és az Alaptörvényben meghatározott alkotmányozó hatáskör gyakorlása.</t>
+  </si>
+  <si>
+    <t>Mi a köztársasági elnök alapvető közjogi szerepe?</t>
+  </si>
+  <si>
+    <t>Magyarország államfője, aki kifejezi a nemzet egységét és őrködik az államszervezet demokratikus működése felett.</t>
+  </si>
+  <si>
+    <t>Mi az Alkotmánybíróság fő feladata?</t>
+  </si>
+  <si>
+    <t>Az Alaptörvény védelme és az alkotmányossági kontroll gyakorlása.</t>
+  </si>
+  <si>
+    <t>Mi a bíróságok alapvető feladata?</t>
+  </si>
+  <si>
+    <t>Az igazságszolgáltatás és a jogviták jogszabályok szerinti eldöntése.</t>
+  </si>
+  <si>
+    <t>Mi az ügyészség alkotmányos alapfeladata?</t>
+  </si>
+  <si>
+    <t>A közérdek és a törvényesség védelme, valamint a büntető igazságszolgáltatásban meghatározott feladatok ellátása.</t>
+  </si>
+  <si>
+    <t>Mi az alapvető jogok biztosának szerepe?</t>
+  </si>
+  <si>
+    <t>Az alapvető jogokkal kapcsolatos visszásságok vizsgálata és orvoslásuk kezdeményezése.</t>
+  </si>
+  <si>
+    <t>Mi a természetes személy a jogban?</t>
+  </si>
+  <si>
+    <t>Az ember mint jogok és kötelezettségek lehetséges alanya.</t>
   </si>
 </sst>
 </file>
@@ -3081,794 +3144,794 @@
   <sheetData>
     <row r="2" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>343</v>
+        <v>244</v>
       </c>
       <c r="B2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>344</v>
+        <v>246</v>
       </c>
       <c r="B3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>345</v>
+        <v>248</v>
       </c>
       <c r="B4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>346</v>
+        <v>250</v>
       </c>
       <c r="B5" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>347</v>
+        <v>252</v>
       </c>
       <c r="B6" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>348</v>
+        <v>254</v>
       </c>
       <c r="B7" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>349</v>
+        <v>256</v>
       </c>
       <c r="B8" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>350</v>
+        <v>258</v>
       </c>
       <c r="B9" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>351</v>
+        <v>260</v>
       </c>
       <c r="B10" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>352</v>
+        <v>262</v>
       </c>
       <c r="B11" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>353</v>
+        <v>264</v>
       </c>
       <c r="B12" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>354</v>
+        <v>266</v>
       </c>
       <c r="B13" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>355</v>
+        <v>268</v>
       </c>
       <c r="B14" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>356</v>
+        <v>270</v>
       </c>
       <c r="B15" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>357</v>
+        <v>272</v>
       </c>
       <c r="B16" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>358</v>
+        <v>274</v>
       </c>
       <c r="B17" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>359</v>
+        <v>276</v>
       </c>
       <c r="B18" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>360</v>
+        <v>278</v>
       </c>
       <c r="B19" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>361</v>
+        <v>280</v>
       </c>
       <c r="B20" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>362</v>
+        <v>282</v>
       </c>
       <c r="B21" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>363</v>
+        <v>284</v>
       </c>
       <c r="B22" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>364</v>
+        <v>286</v>
       </c>
       <c r="B23" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>365</v>
+        <v>288</v>
       </c>
       <c r="B24" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>366</v>
+        <v>290</v>
       </c>
       <c r="B25" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>367</v>
+        <v>292</v>
       </c>
       <c r="B26" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>368</v>
+        <v>294</v>
       </c>
       <c r="B27" t="s">
-        <v>269</v>
+        <v>295</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>369</v>
+        <v>296</v>
       </c>
       <c r="B28" t="s">
-        <v>270</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>370</v>
+        <v>298</v>
       </c>
       <c r="B29" t="s">
-        <v>271</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>371</v>
+        <v>300</v>
       </c>
       <c r="B30" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>372</v>
+        <v>302</v>
       </c>
       <c r="B31" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>373</v>
+        <v>304</v>
       </c>
       <c r="B32" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>374</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s">
-        <v>275</v>
+        <v>307</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>375</v>
+        <v>308</v>
       </c>
       <c r="B34" t="s">
-        <v>252</v>
+        <v>309</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>376</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s">
-        <v>276</v>
+        <v>311</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>377</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>378</v>
+        <v>314</v>
       </c>
       <c r="B37" t="s">
-        <v>278</v>
+        <v>315</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>379</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s">
-        <v>279</v>
+        <v>317</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>380</v>
+        <v>318</v>
       </c>
       <c r="B39" t="s">
-        <v>279</v>
+        <v>319</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>381</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s">
-        <v>280</v>
+        <v>321</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>382</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s">
-        <v>281</v>
+        <v>323</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>383</v>
+        <v>324</v>
       </c>
       <c r="B42" t="s">
-        <v>282</v>
+        <v>325</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>384</v>
+        <v>326</v>
       </c>
       <c r="B43" t="s">
-        <v>283</v>
+        <v>327</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>385</v>
+        <v>328</v>
       </c>
       <c r="B44" t="s">
-        <v>284</v>
+        <v>329</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="B45" t="s">
-        <v>285</v>
+        <v>331</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>387</v>
+        <v>332</v>
       </c>
       <c r="B46" t="s">
-        <v>286</v>
+        <v>333</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>388</v>
+        <v>334</v>
       </c>
       <c r="B47" t="s">
-        <v>287</v>
+        <v>335</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>389</v>
+        <v>336</v>
       </c>
       <c r="B48" t="s">
-        <v>285</v>
+        <v>337</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>390</v>
+        <v>338</v>
       </c>
       <c r="B49" t="s">
-        <v>288</v>
+        <v>339</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>391</v>
+        <v>340</v>
       </c>
       <c r="B50" t="s">
-        <v>273</v>
+        <v>341</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>392</v>
+        <v>342</v>
       </c>
       <c r="B51" t="s">
-        <v>289</v>
+        <v>343</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>393</v>
+        <v>344</v>
       </c>
       <c r="B52" t="s">
-        <v>290</v>
+        <v>345</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>394</v>
+        <v>346</v>
       </c>
       <c r="B53" t="s">
-        <v>291</v>
+        <v>347</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>395</v>
+        <v>348</v>
       </c>
       <c r="B54" t="s">
-        <v>292</v>
+        <v>349</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>396</v>
+        <v>350</v>
       </c>
       <c r="B55" t="s">
-        <v>293</v>
+        <v>351</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>397</v>
+        <v>352</v>
       </c>
       <c r="B56" t="s">
-        <v>294</v>
+        <v>353</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>398</v>
+        <v>354</v>
       </c>
       <c r="B57" t="s">
-        <v>295</v>
+        <v>355</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>399</v>
+        <v>356</v>
       </c>
       <c r="B58" t="s">
-        <v>296</v>
+        <v>357</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>400</v>
+        <v>358</v>
       </c>
       <c r="B59" t="s">
-        <v>297</v>
+        <v>359</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>401</v>
+        <v>360</v>
       </c>
       <c r="B60" t="s">
-        <v>298</v>
+        <v>361</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>402</v>
+        <v>362</v>
       </c>
       <c r="B61" t="s">
-        <v>299</v>
+        <v>363</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>403</v>
+        <v>364</v>
       </c>
       <c r="B62" t="s">
-        <v>300</v>
+        <v>365</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>404</v>
+        <v>366</v>
       </c>
       <c r="B63" t="s">
-        <v>301</v>
+        <v>367</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>405</v>
+        <v>368</v>
       </c>
       <c r="B64" t="s">
-        <v>302</v>
+        <v>369</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>406</v>
+        <v>370</v>
       </c>
       <c r="B65" t="s">
-        <v>300</v>
+        <v>371</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>407</v>
+        <v>372</v>
       </c>
       <c r="B66" t="s">
-        <v>301</v>
+        <v>373</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>408</v>
+        <v>374</v>
       </c>
       <c r="B67" t="s">
-        <v>303</v>
+        <v>375</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>409</v>
+        <v>376</v>
       </c>
       <c r="B68" t="s">
-        <v>304</v>
+        <v>377</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>410</v>
+        <v>378</v>
       </c>
       <c r="B69" t="s">
-        <v>305</v>
+        <v>379</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="B70" t="s">
-        <v>306</v>
+        <v>381</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>412</v>
+        <v>382</v>
       </c>
       <c r="B71" t="s">
-        <v>307</v>
+        <v>383</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>413</v>
+        <v>384</v>
       </c>
       <c r="B72" t="s">
-        <v>308</v>
+        <v>385</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>414</v>
+        <v>386</v>
       </c>
       <c r="B73" t="s">
-        <v>309</v>
+        <v>387</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>415</v>
+        <v>388</v>
       </c>
       <c r="B74" t="s">
-        <v>310</v>
+        <v>389</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="B75" t="s">
-        <v>310</v>
+        <v>391</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>417</v>
+        <v>392</v>
       </c>
       <c r="B76" t="s">
-        <v>311</v>
+        <v>393</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>418</v>
+        <v>394</v>
       </c>
       <c r="B77" t="s">
-        <v>312</v>
+        <v>395</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>419</v>
+        <v>396</v>
       </c>
       <c r="B78" t="s">
-        <v>310</v>
+        <v>397</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>420</v>
+        <v>398</v>
       </c>
       <c r="B79" t="s">
-        <v>313</v>
+        <v>399</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="B80" t="s">
-        <v>314</v>
+        <v>401</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="B81" t="s">
-        <v>315</v>
+        <v>403</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c r="B82" t="s">
-        <v>316</v>
+        <v>405</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="B83" t="s">
-        <v>317</v>
+        <v>407</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="B84" t="s">
-        <v>313</v>
+        <v>409</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="B85" t="s">
-        <v>318</v>
+        <v>411</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="B86" t="s">
-        <v>311</v>
+        <v>413</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="B87" t="s">
-        <v>319</v>
+        <v>415</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="B88" t="s">
-        <v>309</v>
+        <v>417</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="B89" t="s">
-        <v>320</v>
+        <v>419</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="B90" t="s">
-        <v>321</v>
+        <v>421</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="B91" t="s">
-        <v>322</v>
+        <v>423</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="B92" t="s">
-        <v>323</v>
+        <v>425</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="B93" t="s">
-        <v>278</v>
+        <v>427</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="B94" t="s">
-        <v>309</v>
+        <v>429</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="B95" t="s">
-        <v>309</v>
+        <v>431</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B96" t="s">
-        <v>324</v>
+        <v>433</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B97" t="s">
-        <v>324</v>
+        <v>435</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B98" t="s">
-        <v>325</v>
+        <v>437</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B99" t="s">
-        <v>325</v>
+        <v>439</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>440</v>
+      </c>
+      <c r="B100" t="s">
         <v>441</v>
-      </c>
-      <c r="B100" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -3876,167 +3939,167 @@
         <v>442</v>
       </c>
       <c r="B101" t="s">
-        <v>327</v>
+        <v>443</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B102" t="s">
-        <v>328</v>
+        <v>445</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B103" t="s">
-        <v>325</v>
+        <v>447</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B104" t="s">
-        <v>329</v>
+        <v>449</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B105" t="s">
-        <v>330</v>
+        <v>451</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B106" t="s">
-        <v>331</v>
+        <v>453</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="B107" t="s">
-        <v>332</v>
+        <v>455</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="B108" t="s">
-        <v>309</v>
+        <v>457</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B109" t="s">
-        <v>333</v>
+        <v>459</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="B110" t="s">
-        <v>334</v>
+        <v>461</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B111" t="s">
-        <v>334</v>
+        <v>463</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="B112" t="s">
-        <v>334</v>
+        <v>465</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="B113" t="s">
-        <v>317</v>
+        <v>467</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="B114" t="s">
-        <v>335</v>
+        <v>469</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="B115" t="s">
-        <v>336</v>
+        <v>471</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="B116" t="s">
-        <v>337</v>
+        <v>473</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="B117" t="s">
-        <v>338</v>
+        <v>475</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>459</v>
+        <v>476</v>
       </c>
       <c r="B118" t="s">
-        <v>339</v>
+        <v>477</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>460</v>
+        <v>478</v>
       </c>
       <c r="B119" t="s">
-        <v>340</v>
+        <v>479</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="B120" t="s">
-        <v>341</v>
+        <v>481</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="B121" t="s">
-        <v>342</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>

--- a/studyflow.xlsx
+++ b/studyflow.xlsx
@@ -8,14 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\puszt\Downloads\StudyFlow_GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC0A148-3672-468E-9C40-17A22043FAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F9B4AF-9FD7-42B5-98B4-0288FE2B3120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10.26." sheetId="2" r:id="rId1"/>
     <sheet name="words" sheetId="1" r:id="rId2"/>
     <sheet name="jog" sheetId="3" r:id="rId3"/>
+    <sheet name="jog20" sheetId="4" r:id="rId4"/>
+    <sheet name="jog40" sheetId="5" r:id="rId5"/>
+    <sheet name="jog60" sheetId="6" r:id="rId6"/>
+    <sheet name="jog80" sheetId="7" r:id="rId7"/>
+    <sheet name="jog100" sheetId="8" r:id="rId8"/>
+    <sheet name="jog120" sheetId="9" r:id="rId9"/>
+    <sheet name="jog1fele" sheetId="10" r:id="rId10"/>
+    <sheet name="jog2fele" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="484">
   <si>
     <t>pantry</t>
   </si>
@@ -2271,6 +2279,986 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BF00E4D-C189-459B-B4A9-E8056EA51161}">
+  <dimension ref="A2:B61"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>252</v>
+      </c>
+      <c r="B6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>258</v>
+      </c>
+      <c r="B9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>260</v>
+      </c>
+      <c r="B10" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>262</v>
+      </c>
+      <c r="B11" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B12" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>266</v>
+      </c>
+      <c r="B13" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>268</v>
+      </c>
+      <c r="B14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>270</v>
+      </c>
+      <c r="B15" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>272</v>
+      </c>
+      <c r="B16" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>274</v>
+      </c>
+      <c r="B17" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>276</v>
+      </c>
+      <c r="B18" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>278</v>
+      </c>
+      <c r="B19" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>280</v>
+      </c>
+      <c r="B20" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>282</v>
+      </c>
+      <c r="B21" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>284</v>
+      </c>
+      <c r="B22" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>286</v>
+      </c>
+      <c r="B23" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>288</v>
+      </c>
+      <c r="B24" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>290</v>
+      </c>
+      <c r="B25" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>292</v>
+      </c>
+      <c r="B26" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>294</v>
+      </c>
+      <c r="B27" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>296</v>
+      </c>
+      <c r="B28" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>298</v>
+      </c>
+      <c r="B29" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>300</v>
+      </c>
+      <c r="B30" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>302</v>
+      </c>
+      <c r="B31" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>304</v>
+      </c>
+      <c r="B32" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>306</v>
+      </c>
+      <c r="B33" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>308</v>
+      </c>
+      <c r="B34" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>310</v>
+      </c>
+      <c r="B35" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>312</v>
+      </c>
+      <c r="B36" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>314</v>
+      </c>
+      <c r="B37" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>316</v>
+      </c>
+      <c r="B38" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>318</v>
+      </c>
+      <c r="B39" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>320</v>
+      </c>
+      <c r="B40" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>322</v>
+      </c>
+      <c r="B41" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>324</v>
+      </c>
+      <c r="B42" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>326</v>
+      </c>
+      <c r="B43" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>328</v>
+      </c>
+      <c r="B44" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>330</v>
+      </c>
+      <c r="B45" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>332</v>
+      </c>
+      <c r="B46" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>334</v>
+      </c>
+      <c r="B47" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>336</v>
+      </c>
+      <c r="B48" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>338</v>
+      </c>
+      <c r="B49" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>340</v>
+      </c>
+      <c r="B50" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>342</v>
+      </c>
+      <c r="B51" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>344</v>
+      </c>
+      <c r="B52" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>346</v>
+      </c>
+      <c r="B53" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>348</v>
+      </c>
+      <c r="B54" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>350</v>
+      </c>
+      <c r="B55" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>352</v>
+      </c>
+      <c r="B56" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>354</v>
+      </c>
+      <c r="B57" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>356</v>
+      </c>
+      <c r="B58" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>358</v>
+      </c>
+      <c r="B59" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>360</v>
+      </c>
+      <c r="B60" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>362</v>
+      </c>
+      <c r="B61" t="s">
+        <v>363</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C090F96-9CDD-49BD-8779-317424E9E475}">
+  <dimension ref="A2:B61"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B4" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>370</v>
+      </c>
+      <c r="B5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>372</v>
+      </c>
+      <c r="B6" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>374</v>
+      </c>
+      <c r="B7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>376</v>
+      </c>
+      <c r="B8" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>378</v>
+      </c>
+      <c r="B9" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>380</v>
+      </c>
+      <c r="B10" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>382</v>
+      </c>
+      <c r="B11" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>384</v>
+      </c>
+      <c r="B12" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>386</v>
+      </c>
+      <c r="B13" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>388</v>
+      </c>
+      <c r="B14" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>390</v>
+      </c>
+      <c r="B15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>392</v>
+      </c>
+      <c r="B16" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>394</v>
+      </c>
+      <c r="B17" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>396</v>
+      </c>
+      <c r="B18" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>398</v>
+      </c>
+      <c r="B19" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>400</v>
+      </c>
+      <c r="B20" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>402</v>
+      </c>
+      <c r="B21" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>404</v>
+      </c>
+      <c r="B22" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>406</v>
+      </c>
+      <c r="B23" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>408</v>
+      </c>
+      <c r="B24" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>410</v>
+      </c>
+      <c r="B25" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>412</v>
+      </c>
+      <c r="B26" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>414</v>
+      </c>
+      <c r="B27" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>416</v>
+      </c>
+      <c r="B28" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>418</v>
+      </c>
+      <c r="B29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>420</v>
+      </c>
+      <c r="B30" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>422</v>
+      </c>
+      <c r="B31" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>424</v>
+      </c>
+      <c r="B32" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>426</v>
+      </c>
+      <c r="B33" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>428</v>
+      </c>
+      <c r="B34" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>430</v>
+      </c>
+      <c r="B35" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>432</v>
+      </c>
+      <c r="B36" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>434</v>
+      </c>
+      <c r="B37" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>436</v>
+      </c>
+      <c r="B38" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>438</v>
+      </c>
+      <c r="B39" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>440</v>
+      </c>
+      <c r="B40" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>442</v>
+      </c>
+      <c r="B41" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>444</v>
+      </c>
+      <c r="B42" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>446</v>
+      </c>
+      <c r="B43" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>448</v>
+      </c>
+      <c r="B44" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>450</v>
+      </c>
+      <c r="B45" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>452</v>
+      </c>
+      <c r="B46" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>454</v>
+      </c>
+      <c r="B47" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>456</v>
+      </c>
+      <c r="B48" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>458</v>
+      </c>
+      <c r="B49" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>460</v>
+      </c>
+      <c r="B50" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>462</v>
+      </c>
+      <c r="B51" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>464</v>
+      </c>
+      <c r="B52" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>466</v>
+      </c>
+      <c r="B53" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>468</v>
+      </c>
+      <c r="B54" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>470</v>
+      </c>
+      <c r="B55" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>472</v>
+      </c>
+      <c r="B56" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>474</v>
+      </c>
+      <c r="B57" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>476</v>
+      </c>
+      <c r="B58" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>478</v>
+      </c>
+      <c r="B59" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>480</v>
+      </c>
+      <c r="B60" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>482</v>
+      </c>
+      <c r="B61" t="s">
+        <v>483</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:B109"/>
@@ -4106,4 +5094,1028 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B96E3CE-A9D2-4243-AC51-8C45478D2580}">
+  <dimension ref="A2:B21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>252</v>
+      </c>
+      <c r="B6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>258</v>
+      </c>
+      <c r="B9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>260</v>
+      </c>
+      <c r="B10" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>262</v>
+      </c>
+      <c r="B11" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B12" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>266</v>
+      </c>
+      <c r="B13" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>268</v>
+      </c>
+      <c r="B14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>270</v>
+      </c>
+      <c r="B15" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>272</v>
+      </c>
+      <c r="B16" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>274</v>
+      </c>
+      <c r="B17" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>276</v>
+      </c>
+      <c r="B18" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>278</v>
+      </c>
+      <c r="B19" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>280</v>
+      </c>
+      <c r="B20" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>282</v>
+      </c>
+      <c r="B21" t="s">
+        <v>283</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5DDB651-E63A-4E8D-A6CC-1E45493C5B1E}">
+  <dimension ref="A2:B21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>292</v>
+      </c>
+      <c r="B6" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>294</v>
+      </c>
+      <c r="B7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>296</v>
+      </c>
+      <c r="B8" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>300</v>
+      </c>
+      <c r="B10" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>302</v>
+      </c>
+      <c r="B11" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>304</v>
+      </c>
+      <c r="B12" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>306</v>
+      </c>
+      <c r="B13" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>308</v>
+      </c>
+      <c r="B14" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>310</v>
+      </c>
+      <c r="B15" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>312</v>
+      </c>
+      <c r="B16" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>314</v>
+      </c>
+      <c r="B17" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>316</v>
+      </c>
+      <c r="B18" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>318</v>
+      </c>
+      <c r="B19" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>320</v>
+      </c>
+      <c r="B20" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>322</v>
+      </c>
+      <c r="B21" t="s">
+        <v>323</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8FC0AD1-1F61-41E3-BFDA-3510B08E1A8F}">
+  <dimension ref="A2:B21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>328</v>
+      </c>
+      <c r="B4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>330</v>
+      </c>
+      <c r="B5" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>332</v>
+      </c>
+      <c r="B6" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>334</v>
+      </c>
+      <c r="B7" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B8" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>338</v>
+      </c>
+      <c r="B9" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>340</v>
+      </c>
+      <c r="B10" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>342</v>
+      </c>
+      <c r="B11" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>344</v>
+      </c>
+      <c r="B12" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>346</v>
+      </c>
+      <c r="B13" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>348</v>
+      </c>
+      <c r="B14" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>350</v>
+      </c>
+      <c r="B15" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>352</v>
+      </c>
+      <c r="B16" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>354</v>
+      </c>
+      <c r="B17" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>356</v>
+      </c>
+      <c r="B18" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>358</v>
+      </c>
+      <c r="B19" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>360</v>
+      </c>
+      <c r="B20" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>362</v>
+      </c>
+      <c r="B21" t="s">
+        <v>363</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F34B0B-FA87-4603-AD25-82A4DED671D2}">
+  <dimension ref="A2:B21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B4" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>370</v>
+      </c>
+      <c r="B5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>372</v>
+      </c>
+      <c r="B6" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>374</v>
+      </c>
+      <c r="B7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>376</v>
+      </c>
+      <c r="B8" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>378</v>
+      </c>
+      <c r="B9" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>380</v>
+      </c>
+      <c r="B10" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>382</v>
+      </c>
+      <c r="B11" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>384</v>
+      </c>
+      <c r="B12" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>386</v>
+      </c>
+      <c r="B13" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>388</v>
+      </c>
+      <c r="B14" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>390</v>
+      </c>
+      <c r="B15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>392</v>
+      </c>
+      <c r="B16" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>394</v>
+      </c>
+      <c r="B17" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>396</v>
+      </c>
+      <c r="B18" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>398</v>
+      </c>
+      <c r="B19" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>400</v>
+      </c>
+      <c r="B20" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>402</v>
+      </c>
+      <c r="B21" t="s">
+        <v>403</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25BB3695-9438-4ACA-BB8B-AB2C476420B3}">
+  <dimension ref="A2:B21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B5" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>412</v>
+      </c>
+      <c r="B6" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>414</v>
+      </c>
+      <c r="B7" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>416</v>
+      </c>
+      <c r="B8" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>418</v>
+      </c>
+      <c r="B9" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>420</v>
+      </c>
+      <c r="B10" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>422</v>
+      </c>
+      <c r="B11" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>424</v>
+      </c>
+      <c r="B12" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>426</v>
+      </c>
+      <c r="B13" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>428</v>
+      </c>
+      <c r="B14" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>430</v>
+      </c>
+      <c r="B15" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>432</v>
+      </c>
+      <c r="B16" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>434</v>
+      </c>
+      <c r="B17" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>436</v>
+      </c>
+      <c r="B18" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>438</v>
+      </c>
+      <c r="B19" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>440</v>
+      </c>
+      <c r="B20" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B21" t="s">
+        <v>443</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FADF83DE-805B-4407-8A23-567AD5AFE8C5}">
+  <dimension ref="A2:B21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B3" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>448</v>
+      </c>
+      <c r="B4" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B5" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>452</v>
+      </c>
+      <c r="B6" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>454</v>
+      </c>
+      <c r="B7" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>456</v>
+      </c>
+      <c r="B8" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>458</v>
+      </c>
+      <c r="B9" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B10" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>462</v>
+      </c>
+      <c r="B11" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>464</v>
+      </c>
+      <c r="B12" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>466</v>
+      </c>
+      <c r="B13" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>468</v>
+      </c>
+      <c r="B14" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>470</v>
+      </c>
+      <c r="B15" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>472</v>
+      </c>
+      <c r="B16" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>474</v>
+      </c>
+      <c r="B17" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>476</v>
+      </c>
+      <c r="B18" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>478</v>
+      </c>
+      <c r="B19" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>480</v>
+      </c>
+      <c r="B20" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>482</v>
+      </c>
+      <c r="B21" t="s">
+        <v>483</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>